--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -882,50 +882,32 @@
       <c r="H6" s="40" t="n"/>
       <c r="I6" s="40" t="n"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="27">
-      <c r="A7" s="41" t="inlineStr">
+    <row r="7" ht="12.75" customHeight="1" s="27">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>보장기간</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n"/>
+      <c r="D7" s="40" t="n"/>
+      <c r="E7" s="40" t="n"/>
+      <c r="F7" s="40" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="40" t="n"/>
+      <c r="I7" s="40" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="27">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>▶  월 납입 보험료</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n"/>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="42" t="n"/>
-      <c r="F7" s="42" t="n"/>
-      <c r="G7" s="42" t="n"/>
-      <c r="H7" s="42" t="n"/>
-      <c r="I7" s="42">
-        <f>SUM(C7:H7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="43" t="inlineStr">
+    </row>
+    <row r="9" ht="11.25" customHeight="1" s="27">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="9" ht="11.25" customHeight="1" s="27">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>사망</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>일반사망</t>
-        </is>
-      </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="n"/>
-      <c r="H9" s="46" t="n"/>
-      <c r="I9" s="46">
-        <f>SUM(C9:H9)</f>
-        <v/>
       </c>
     </row>
     <row r="10" ht="11.25" customHeight="1" s="27">
@@ -936,7 +918,7 @@
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
-          <t>질병사망</t>
+          <t>일반사망</t>
         </is>
       </c>
       <c r="C10" s="46" t="n"/>
@@ -946,7 +928,7 @@
       <c r="G10" s="46" t="n"/>
       <c r="H10" s="46" t="n"/>
       <c r="I10" s="46">
-        <f>SUM(C10:H10)</f>
+        <f>SUM(C9:H9)</f>
         <v/>
       </c>
     </row>
@@ -958,7 +940,7 @@
       </c>
       <c r="B11" s="45" t="inlineStr">
         <is>
-          <t>암사망</t>
+          <t>질병사망</t>
         </is>
       </c>
       <c r="C11" s="46" t="n"/>
@@ -968,7 +950,7 @@
       <c r="G11" s="46" t="n"/>
       <c r="H11" s="46" t="n"/>
       <c r="I11" s="46">
-        <f>SUM(C11:H11)</f>
+        <f>SUM(C10:H10)</f>
         <v/>
       </c>
     </row>
@@ -980,7 +962,7 @@
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>암사망</t>
         </is>
       </c>
       <c r="C12" s="46" t="n"/>
@@ -990,19 +972,19 @@
       <c r="G12" s="46" t="n"/>
       <c r="H12" s="46" t="n"/>
       <c r="I12" s="46">
-        <f>SUM(C12:H12)</f>
+        <f>SUM(C11:H11)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="11.25" customHeight="1" s="27">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>장해</t>
+          <t>사망</t>
         </is>
       </c>
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>상해후유장해(100%)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="C13" s="46" t="n"/>
@@ -1012,7 +994,7 @@
       <c r="G13" s="46" t="n"/>
       <c r="H13" s="46" t="n"/>
       <c r="I13" s="46">
-        <f>SUM(C13:H13)</f>
+        <f>SUM(C12:H12)</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1006,7 @@
       </c>
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>상해후유장해(3%)</t>
+          <t>상해후유장해(100%)</t>
         </is>
       </c>
       <c r="C14" s="46" t="n"/>
@@ -1034,7 +1016,7 @@
       <c r="G14" s="46" t="n"/>
       <c r="H14" s="46" t="n"/>
       <c r="I14" s="46">
-        <f>SUM(C14:H14)</f>
+        <f>SUM(C13:H13)</f>
         <v/>
       </c>
     </row>
@@ -1046,7 +1028,7 @@
       </c>
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>질병후유장해(100%)</t>
+          <t>상해후유장해(3%)</t>
         </is>
       </c>
       <c r="C15" s="46" t="n"/>
@@ -1056,37 +1038,37 @@
       <c r="G15" s="46" t="n"/>
       <c r="H15" s="46" t="n"/>
       <c r="I15" s="46">
+        <f>SUM(C14:H14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="27">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>장해</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>질병후유장해(100%)</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="46" t="n"/>
+      <c r="G16" s="46" t="n"/>
+      <c r="H16" s="46" t="n"/>
+      <c r="I16" s="46">
         <f>SUM(C15:H15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="27">
-      <c r="A16" s="43" t="inlineStr">
+    <row r="17" ht="11.25" customHeight="1" s="27">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
-      </c>
-    </row>
-    <row r="17" ht="11.25" customHeight="1" s="27">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>암진단</t>
-        </is>
-      </c>
-      <c r="B17" s="45" t="inlineStr">
-        <is>
-          <t>일반암 진단비</t>
-        </is>
-      </c>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-      <c r="H17" s="46" t="n"/>
-      <c r="I17" s="46">
-        <f>SUM(C17:H17)</f>
-        <v/>
       </c>
     </row>
     <row r="18" ht="11.25" customHeight="1" s="27">
@@ -1097,7 +1079,7 @@
       </c>
       <c r="B18" s="45" t="inlineStr">
         <is>
-          <t>고액암 진단비</t>
+          <t>일반암 진단비</t>
         </is>
       </c>
       <c r="C18" s="46" t="n"/>
@@ -1107,7 +1089,7 @@
       <c r="G18" s="46" t="n"/>
       <c r="H18" s="46" t="n"/>
       <c r="I18" s="46">
-        <f>SUM(C18:H18)</f>
+        <f>SUM(C17:H17)</f>
         <v/>
       </c>
     </row>
@@ -1119,7 +1101,7 @@
       </c>
       <c r="B19" s="45" t="inlineStr">
         <is>
-          <t>소액암 진단비</t>
+          <t>고액암 진단비</t>
         </is>
       </c>
       <c r="C19" s="46" t="n"/>
@@ -1129,19 +1111,19 @@
       <c r="G19" s="46" t="n"/>
       <c r="H19" s="46" t="n"/>
       <c r="I19" s="46">
-        <f>SUM(C19:H19)</f>
+        <f>SUM(C18:H18)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="11.25" customHeight="1" s="27">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>말기진단</t>
+          <t>암진단</t>
         </is>
       </c>
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>말기간질환 진단비</t>
+          <t>소액암 진단비</t>
         </is>
       </c>
       <c r="C20" s="46" t="n"/>
@@ -1151,7 +1133,7 @@
       <c r="G20" s="46" t="n"/>
       <c r="H20" s="46" t="n"/>
       <c r="I20" s="46">
-        <f>SUM(C20:H20)</f>
+        <f>SUM(C19:H19)</f>
         <v/>
       </c>
     </row>
@@ -1163,7 +1145,7 @@
       </c>
       <c r="B21" s="45" t="inlineStr">
         <is>
-          <t>말기폐질환 진단비</t>
+          <t>말기간질환 진단비</t>
         </is>
       </c>
       <c r="C21" s="46" t="n"/>
@@ -1173,7 +1155,7 @@
       <c r="G21" s="46" t="n"/>
       <c r="H21" s="46" t="n"/>
       <c r="I21" s="46">
-        <f>SUM(C21:H21)</f>
+        <f>SUM(C20:H20)</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1167,7 @@
       </c>
       <c r="B22" s="45" t="inlineStr">
         <is>
-          <t>말기신부전증 진단비</t>
+          <t>말기폐질환 진단비</t>
         </is>
       </c>
       <c r="C22" s="46" t="n"/>
@@ -1195,37 +1177,37 @@
       <c r="G22" s="46" t="n"/>
       <c r="H22" s="46" t="n"/>
       <c r="I22" s="46">
+        <f>SUM(C21:H21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="27">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>말기진단</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>말기신부전증 진단비</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
+      <c r="E23" s="46" t="n"/>
+      <c r="F23" s="46" t="n"/>
+      <c r="G23" s="46" t="n"/>
+      <c r="H23" s="46" t="n"/>
+      <c r="I23" s="46">
         <f>SUM(C22:H22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="27">
-      <c r="A23" s="43" t="inlineStr">
+    <row r="24" ht="11.25" customHeight="1" s="27">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
         </is>
-      </c>
-    </row>
-    <row r="24" ht="11.25" customHeight="1" s="27">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>암치료</t>
-        </is>
-      </c>
-      <c r="B24" s="45" t="inlineStr">
-        <is>
-          <t>상급병원암주요치료비(수술)</t>
-        </is>
-      </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
-      <c r="H24" s="46" t="n"/>
-      <c r="I24" s="46">
-        <f>SUM(C24:H24)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="11.25" customHeight="1" s="27">
@@ -1236,7 +1218,7 @@
       </c>
       <c r="B25" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(수술)</t>
         </is>
       </c>
       <c r="C25" s="46" t="n"/>
@@ -1246,7 +1228,7 @@
       <c r="G25" s="46" t="n"/>
       <c r="H25" s="46" t="n"/>
       <c r="I25" s="46">
-        <f>SUM(C25:H25)</f>
+        <f>SUM(C24:H24)</f>
         <v/>
       </c>
     </row>
@@ -1258,7 +1240,7 @@
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(방사선)</t>
         </is>
       </c>
       <c r="C26" s="46" t="n"/>
@@ -1268,7 +1250,7 @@
       <c r="G26" s="46" t="n"/>
       <c r="H26" s="46" t="n"/>
       <c r="I26" s="46">
-        <f>SUM(C26:H26)</f>
+        <f>SUM(C25:H25)</f>
         <v/>
       </c>
     </row>
@@ -1280,7 +1262,7 @@
       </c>
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>상급병원암주요치료비(약물)</t>
         </is>
       </c>
       <c r="C27" s="46" t="n"/>
@@ -1290,7 +1272,7 @@
       <c r="G27" s="46" t="n"/>
       <c r="H27" s="46" t="n"/>
       <c r="I27" s="46">
-        <f>SUM(C27:H27)</f>
+        <f>SUM(C26:H26)</f>
         <v/>
       </c>
     </row>
@@ -1302,7 +1284,7 @@
       </c>
       <c r="B28" s="45" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>상급병원암주요치료비(복합)</t>
         </is>
       </c>
       <c r="C28" s="46" t="n"/>
@@ -1312,7 +1294,7 @@
       <c r="G28" s="46" t="n"/>
       <c r="H28" s="46" t="n"/>
       <c r="I28" s="46">
-        <f>SUM(C28:H28)</f>
+        <f>SUM(C27:H27)</f>
         <v/>
       </c>
     </row>
@@ -1324,7 +1306,7 @@
       </c>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>항암방사선치료</t>
+          <t>종합병원비급여암주요치료비</t>
         </is>
       </c>
       <c r="C29" s="46" t="n"/>
@@ -1334,7 +1316,7 @@
       <c r="G29" s="46" t="n"/>
       <c r="H29" s="46" t="n"/>
       <c r="I29" s="46">
-        <f>SUM(C29:H29)</f>
+        <f>SUM(C28:H28)</f>
         <v/>
       </c>
     </row>
@@ -1346,7 +1328,7 @@
       </c>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>항암세기조절방사선치료</t>
+          <t>항암방사선치료</t>
         </is>
       </c>
       <c r="C30" s="46" t="n"/>
@@ -1356,7 +1338,7 @@
       <c r="G30" s="46" t="n"/>
       <c r="H30" s="46" t="n"/>
       <c r="I30" s="46">
-        <f>SUM(C30:H30)</f>
+        <f>SUM(C29:H29)</f>
         <v/>
       </c>
     </row>
@@ -1368,7 +1350,7 @@
       </c>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>항암양성자방사선치료</t>
+          <t>항암세기조절방사선치료</t>
         </is>
       </c>
       <c r="C31" s="46" t="n"/>
@@ -1378,7 +1360,7 @@
       <c r="G31" s="46" t="n"/>
       <c r="H31" s="46" t="n"/>
       <c r="I31" s="46">
-        <f>SUM(C31:H31)</f>
+        <f>SUM(C30:H30)</f>
         <v/>
       </c>
     </row>
@@ -1390,7 +1372,7 @@
       </c>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>항암약물치료</t>
+          <t>항암양성자방사선치료</t>
         </is>
       </c>
       <c r="C32" s="46" t="n"/>
@@ -1400,7 +1382,7 @@
       <c r="G32" s="46" t="n"/>
       <c r="H32" s="46" t="n"/>
       <c r="I32" s="46">
-        <f>SUM(C32:H32)</f>
+        <f>SUM(C31:H31)</f>
         <v/>
       </c>
     </row>
@@ -1412,7 +1394,7 @@
       </c>
       <c r="B33" s="45" t="inlineStr">
         <is>
-          <t>표적항암약물 허가치료</t>
+          <t>항암약물치료</t>
         </is>
       </c>
       <c r="C33" s="46" t="n"/>
@@ -1422,7 +1404,7 @@
       <c r="G33" s="46" t="n"/>
       <c r="H33" s="46" t="n"/>
       <c r="I33" s="46">
-        <f>SUM(C33:H33)</f>
+        <f>SUM(C32:H32)</f>
         <v/>
       </c>
     </row>
@@ -1432,9 +1414,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B34" s="47" t="inlineStr">
-        <is>
-          <t>CAR-T 항암약물 허가치료</t>
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>표적항암약물 허가치료</t>
         </is>
       </c>
       <c r="C34" s="46" t="n"/>
@@ -1444,7 +1426,7 @@
       <c r="G34" s="46" t="n"/>
       <c r="H34" s="46" t="n"/>
       <c r="I34" s="46">
-        <f>SUM(C34:H34)</f>
+        <f>SUM(C33:H33)</f>
         <v/>
       </c>
     </row>
@@ -1454,9 +1436,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
-        <is>
-          <t>항암호르몬약물 허가치료</t>
+      <c r="B35" s="47" t="inlineStr">
+        <is>
+          <t>CAR-T 항암약물 허가치료</t>
         </is>
       </c>
       <c r="C35" s="46" t="n"/>
@@ -1466,7 +1448,7 @@
       <c r="G35" s="46" t="n"/>
       <c r="H35" s="46" t="n"/>
       <c r="I35" s="46">
-        <f>SUM(C35:H35)</f>
+        <f>SUM(C34:H34)</f>
         <v/>
       </c>
     </row>
@@ -1478,7 +1460,7 @@
       </c>
       <c r="B36" s="45" t="inlineStr">
         <is>
-          <t>항암중입자방사선치료</t>
+          <t>항암호르몬약물 허가치료</t>
         </is>
       </c>
       <c r="C36" s="46" t="n"/>
@@ -1488,7 +1470,7 @@
       <c r="G36" s="46" t="n"/>
       <c r="H36" s="46" t="n"/>
       <c r="I36" s="46">
-        <f>SUM(C36:H36)</f>
+        <f>SUM(C35:H35)</f>
         <v/>
       </c>
     </row>
@@ -1500,7 +1482,7 @@
       </c>
       <c r="B37" s="45" t="inlineStr">
         <is>
-          <t>암직접치료상급종합병원통원</t>
+          <t>항암중입자방사선치료</t>
         </is>
       </c>
       <c r="C37" s="46" t="n"/>
@@ -1510,37 +1492,37 @@
       <c r="G37" s="46" t="n"/>
       <c r="H37" s="46" t="n"/>
       <c r="I37" s="46">
+        <f>SUM(C36:H36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="27">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>암치료</t>
+        </is>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>암직접치료상급종합병원통원</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
+      <c r="E38" s="46" t="n"/>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
+      <c r="I38" s="46">
         <f>SUM(C37:H37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="27">
-      <c r="A38" s="43" t="inlineStr">
+    <row r="39" ht="11.25" customHeight="1" s="27">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="39" ht="11.25" customHeight="1" s="27">
-      <c r="A39" s="44" t="inlineStr">
-        <is>
-          <t>심뇌</t>
-        </is>
-      </c>
-      <c r="B39" s="45" t="inlineStr">
-        <is>
-          <t>뇌혈관질환 진단</t>
-        </is>
-      </c>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="46" t="n"/>
-      <c r="G39" s="46" t="n"/>
-      <c r="H39" s="46" t="n"/>
-      <c r="I39" s="46">
-        <f>SUM(C39:H39)</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="11.25" customHeight="1" s="27">
@@ -1551,7 +1533,7 @@
       </c>
       <c r="B40" s="45" t="inlineStr">
         <is>
-          <t>뇌경색증진단</t>
+          <t>뇌혈관질환 진단</t>
         </is>
       </c>
       <c r="C40" s="46" t="n"/>
@@ -1561,7 +1543,7 @@
       <c r="G40" s="46" t="n"/>
       <c r="H40" s="46" t="n"/>
       <c r="I40" s="46">
-        <f>SUM(C40:H40)</f>
+        <f>SUM(C39:H39)</f>
         <v/>
       </c>
     </row>
@@ -1573,7 +1555,7 @@
       </c>
       <c r="B41" s="45" t="inlineStr">
         <is>
-          <t>뇌출혈 진단</t>
+          <t>뇌경색증진단</t>
         </is>
       </c>
       <c r="C41" s="46" t="n"/>
@@ -1583,7 +1565,7 @@
       <c r="G41" s="46" t="n"/>
       <c r="H41" s="46" t="n"/>
       <c r="I41" s="46">
-        <f>SUM(C41:H41)</f>
+        <f>SUM(C40:H40)</f>
         <v/>
       </c>
     </row>
@@ -1595,7 +1577,7 @@
       </c>
       <c r="B42" s="45" t="inlineStr">
         <is>
-          <t>급성심근경색 진단</t>
+          <t>뇌출혈 진단</t>
         </is>
       </c>
       <c r="C42" s="46" t="n"/>
@@ -1605,7 +1587,7 @@
       <c r="G42" s="46" t="n"/>
       <c r="H42" s="46" t="n"/>
       <c r="I42" s="46">
-        <f>SUM(C42:H42)</f>
+        <f>SUM(C41:H41)</f>
         <v/>
       </c>
     </row>
@@ -1617,7 +1599,7 @@
       </c>
       <c r="B43" s="45" t="inlineStr">
         <is>
-          <t>허혈심장질환 진단</t>
+          <t>급성심근경색 진단</t>
         </is>
       </c>
       <c r="C43" s="46" t="n"/>
@@ -1627,7 +1609,7 @@
       <c r="G43" s="46" t="n"/>
       <c r="H43" s="46" t="n"/>
       <c r="I43" s="46">
-        <f>SUM(C43:H43)</f>
+        <f>SUM(C42:H42)</f>
         <v/>
       </c>
     </row>
@@ -1639,7 +1621,7 @@
       </c>
       <c r="B44" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 수술 (연1회)</t>
+          <t>허혈심장질환 진단</t>
         </is>
       </c>
       <c r="C44" s="46" t="n"/>
@@ -1649,7 +1631,7 @@
       <c r="G44" s="46" t="n"/>
       <c r="H44" s="46" t="n"/>
       <c r="I44" s="46">
-        <f>SUM(C44:H44)</f>
+        <f>SUM(C43:H43)</f>
         <v/>
       </c>
     </row>
@@ -1661,7 +1643,7 @@
       </c>
       <c r="B45" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 혈전 용해 (연1회)</t>
+          <t>순환계질환 수술 (연1회)</t>
         </is>
       </c>
       <c r="C45" s="46" t="n"/>
@@ -1671,7 +1653,7 @@
       <c r="G45" s="46" t="n"/>
       <c r="H45" s="46" t="n"/>
       <c r="I45" s="46">
-        <f>SUM(C45:H45)</f>
+        <f>SUM(C44:H44)</f>
         <v/>
       </c>
     </row>
@@ -1683,7 +1665,7 @@
       </c>
       <c r="B46" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 혈전제거 (연1회)</t>
+          <t>순환계질환 혈전 용해 (연1회)</t>
         </is>
       </c>
       <c r="C46" s="46" t="n"/>
@@ -1693,7 +1675,7 @@
       <c r="G46" s="46" t="n"/>
       <c r="H46" s="46" t="n"/>
       <c r="I46" s="46">
-        <f>SUM(C46:H46)</f>
+        <f>SUM(C45:H45)</f>
         <v/>
       </c>
     </row>
@@ -1705,7 +1687,7 @@
       </c>
       <c r="B47" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 복합치료 (연1회)</t>
+          <t>순환계질환 혈전제거 (연1회)</t>
         </is>
       </c>
       <c r="C47" s="46" t="n"/>
@@ -1715,7 +1697,7 @@
       <c r="G47" s="46" t="n"/>
       <c r="H47" s="46" t="n"/>
       <c r="I47" s="46">
-        <f>SUM(C47:H47)</f>
+        <f>SUM(C46:H46)</f>
         <v/>
       </c>
     </row>
@@ -1727,7 +1709,7 @@
       </c>
       <c r="B48" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 중환자실 (연1회)</t>
+          <t>순환계질환 복합치료 (연1회)</t>
         </is>
       </c>
       <c r="C48" s="46" t="n"/>
@@ -1737,37 +1719,37 @@
       <c r="G48" s="46" t="n"/>
       <c r="H48" s="46" t="n"/>
       <c r="I48" s="46">
+        <f>SUM(C47:H47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="27">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>심뇌</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>순환계질환 중환자실 (연1회)</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="46" t="n"/>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="46" t="n"/>
+      <c r="I49" s="46">
         <f>SUM(C48:H48)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="27">
-      <c r="A49" s="43" t="inlineStr">
+    <row r="50" ht="11.25" customHeight="1" s="27">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="50" ht="11.25" customHeight="1" s="27">
-      <c r="A50" s="44" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B50" s="45" t="inlineStr">
-        <is>
-          <t>질병 수술비</t>
-        </is>
-      </c>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="46" t="n"/>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="46" t="n"/>
-      <c r="I50" s="46">
-        <f>SUM(C50:H50)</f>
-        <v/>
       </c>
     </row>
     <row r="51" ht="11.25" customHeight="1" s="27">
@@ -1778,7 +1760,7 @@
       </c>
       <c r="B51" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원질병수술</t>
+          <t>질병 수술비</t>
         </is>
       </c>
       <c r="C51" s="46" t="n"/>
@@ -1788,7 +1770,7 @@
       <c r="G51" s="46" t="n"/>
       <c r="H51" s="46" t="n"/>
       <c r="I51" s="46">
-        <f>SUM(C51:H51)</f>
+        <f>SUM(C50:H50)</f>
         <v/>
       </c>
     </row>
@@ -1800,7 +1782,7 @@
       </c>
       <c r="B52" s="45" t="inlineStr">
         <is>
-          <t>재해 수술비</t>
+          <t>상급종합병원질병수술</t>
         </is>
       </c>
       <c r="C52" s="46" t="n"/>
@@ -1810,7 +1792,7 @@
       <c r="G52" s="46" t="n"/>
       <c r="H52" s="46" t="n"/>
       <c r="I52" s="46">
-        <f>SUM(C52:H52)</f>
+        <f>SUM(C51:H51)</f>
         <v/>
       </c>
     </row>
@@ -1822,7 +1804,7 @@
       </c>
       <c r="B53" s="45" t="inlineStr">
         <is>
-          <t>암 수술비</t>
+          <t>재해 수술비</t>
         </is>
       </c>
       <c r="C53" s="46" t="n"/>
@@ -1832,7 +1814,7 @@
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="46" t="n"/>
       <c r="I53" s="46">
-        <f>SUM(C53:H53)</f>
+        <f>SUM(C52:H52)</f>
         <v/>
       </c>
     </row>
@@ -1844,7 +1826,7 @@
       </c>
       <c r="B54" s="45" t="inlineStr">
         <is>
-          <t>뇌출혈 수술</t>
+          <t>암 수술비</t>
         </is>
       </c>
       <c r="C54" s="46" t="n"/>
@@ -1854,7 +1836,7 @@
       <c r="G54" s="46" t="n"/>
       <c r="H54" s="46" t="n"/>
       <c r="I54" s="46">
-        <f>SUM(C54:H54)</f>
+        <f>SUM(C53:H53)</f>
         <v/>
       </c>
     </row>
@@ -1866,7 +1848,7 @@
       </c>
       <c r="B55" s="45" t="inlineStr">
         <is>
-          <t>급성심근경색 수술</t>
+          <t>뇌출혈 수술</t>
         </is>
       </c>
       <c r="C55" s="46" t="n"/>
@@ -1876,7 +1858,7 @@
       <c r="G55" s="46" t="n"/>
       <c r="H55" s="46" t="n"/>
       <c r="I55" s="46">
-        <f>SUM(C55:H55)</f>
+        <f>SUM(C54:H54)</f>
         <v/>
       </c>
     </row>
@@ -1886,9 +1868,9 @@
           <t>수술</t>
         </is>
       </c>
-      <c r="B56" s="47" t="inlineStr">
-        <is>
-          <t>1-5종 수술 1종</t>
+      <c r="B56" s="45" t="inlineStr">
+        <is>
+          <t>급성심근경색 수술</t>
         </is>
       </c>
       <c r="C56" s="46" t="n"/>
@@ -1898,7 +1880,7 @@
       <c r="G56" s="46" t="n"/>
       <c r="H56" s="46" t="n"/>
       <c r="I56" s="46">
-        <f>SUM(C56:H56)</f>
+        <f>SUM(C55:H55)</f>
         <v/>
       </c>
     </row>
@@ -1910,7 +1892,7 @@
       </c>
       <c r="B57" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 2종</t>
+          <t>1-5종 수술 1종</t>
         </is>
       </c>
       <c r="C57" s="46" t="n"/>
@@ -1920,7 +1902,7 @@
       <c r="G57" s="46" t="n"/>
       <c r="H57" s="46" t="n"/>
       <c r="I57" s="46">
-        <f>SUM(C57:H57)</f>
+        <f>SUM(C56:H56)</f>
         <v/>
       </c>
     </row>
@@ -1932,7 +1914,7 @@
       </c>
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 3종</t>
+          <t>1-5종 수술 2종</t>
         </is>
       </c>
       <c r="C58" s="46" t="n"/>
@@ -1942,7 +1924,7 @@
       <c r="G58" s="46" t="n"/>
       <c r="H58" s="46" t="n"/>
       <c r="I58" s="46">
-        <f>SUM(C58:H58)</f>
+        <f>SUM(C57:H57)</f>
         <v/>
       </c>
     </row>
@@ -1954,7 +1936,7 @@
       </c>
       <c r="B59" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 4종</t>
+          <t>1-5종 수술 3종</t>
         </is>
       </c>
       <c r="C59" s="46" t="n"/>
@@ -1964,7 +1946,7 @@
       <c r="G59" s="46" t="n"/>
       <c r="H59" s="46" t="n"/>
       <c r="I59" s="46">
-        <f>SUM(C59:H59)</f>
+        <f>SUM(C58:H58)</f>
         <v/>
       </c>
     </row>
@@ -1976,7 +1958,7 @@
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 5종</t>
+          <t>1-5종 수술 4종</t>
         </is>
       </c>
       <c r="C60" s="46" t="n"/>
@@ -1986,48 +1968,48 @@
       <c r="G60" s="46" t="n"/>
       <c r="H60" s="46" t="n"/>
       <c r="I60" s="46">
+        <f>SUM(C59:H59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="27">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B61" s="47" t="inlineStr">
+        <is>
+          <t>1-5종 수술 5종</t>
+        </is>
+      </c>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
+      <c r="E61" s="46" t="n"/>
+      <c r="F61" s="46" t="n"/>
+      <c r="G61" s="46" t="n"/>
+      <c r="H61" s="46" t="n"/>
+      <c r="I61" s="46">
         <f>SUM(C60:H60)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="27">
-      <c r="A61" s="43" t="inlineStr">
+    <row r="62" ht="11.25" customHeight="1" s="27">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="62" ht="11.25" customHeight="1" s="27">
-      <c r="A62" s="48" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B62" s="49" t="inlineStr">
-        <is>
-          <t>질병/상해 입원 실비</t>
-        </is>
-      </c>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
-      <c r="E62" s="46" t="n"/>
-      <c r="F62" s="46" t="n"/>
-      <c r="G62" s="46" t="n"/>
-      <c r="H62" s="46" t="n"/>
-      <c r="I62" s="46">
-        <f>SUM(C62:H62)</f>
-        <v/>
       </c>
     </row>
     <row r="63" ht="11.25" customHeight="1" s="27">
       <c r="A63" s="48" t="inlineStr">
         <is>
-          <t>통원</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B63" s="49" t="inlineStr">
         <is>
-          <t>질병/상해 통원 실비</t>
+          <t>질병/상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="46" t="n"/>
@@ -2037,19 +2019,19 @@
       <c r="G63" s="46" t="n"/>
       <c r="H63" s="46" t="n"/>
       <c r="I63" s="46">
-        <f>SUM(C63:H63)</f>
+        <f>SUM(C62:H62)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="11.25" customHeight="1" s="27">
-      <c r="A64" s="44" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B64" s="45" t="inlineStr">
-        <is>
-          <t>질병입원 일당</t>
+      <c r="A64" s="48" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>질병/상해 통원 실비</t>
         </is>
       </c>
       <c r="C64" s="46" t="n"/>
@@ -2059,7 +2041,7 @@
       <c r="G64" s="46" t="n"/>
       <c r="H64" s="46" t="n"/>
       <c r="I64" s="46">
-        <f>SUM(C64:H64)</f>
+        <f>SUM(C63:H63)</f>
         <v/>
       </c>
     </row>
@@ -2071,7 +2053,7 @@
       </c>
       <c r="B65" s="45" t="inlineStr">
         <is>
-          <t>재해입원 일당</t>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C65" s="46" t="n"/>
@@ -2081,7 +2063,7 @@
       <c r="G65" s="46" t="n"/>
       <c r="H65" s="46" t="n"/>
       <c r="I65" s="46">
-        <f>SUM(C65:H65)</f>
+        <f>SUM(C64:H64)</f>
         <v/>
       </c>
     </row>
@@ -2093,7 +2075,7 @@
       </c>
       <c r="B66" s="45" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C66" s="46" t="n"/>
@@ -2103,7 +2085,7 @@
       <c r="G66" s="46" t="n"/>
       <c r="H66" s="46" t="n"/>
       <c r="I66" s="46">
-        <f>SUM(C66:H66)</f>
+        <f>SUM(C65:H65)</f>
         <v/>
       </c>
     </row>
@@ -2115,7 +2097,7 @@
       </c>
       <c r="B67" s="45" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C67" s="46" t="n"/>
@@ -2125,7 +2107,7 @@
       <c r="G67" s="46" t="n"/>
       <c r="H67" s="46" t="n"/>
       <c r="I67" s="46">
-        <f>SUM(C67:H67)</f>
+        <f>SUM(C66:H66)</f>
         <v/>
       </c>
     </row>
@@ -2137,7 +2119,7 @@
       </c>
       <c r="B68" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C68" s="46" t="n"/>
@@ -2147,7 +2129,7 @@
       <c r="G68" s="46" t="n"/>
       <c r="H68" s="46" t="n"/>
       <c r="I68" s="46">
-        <f>SUM(C68:H68)</f>
+        <f>SUM(C67:H67)</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2141,7 @@
       </c>
       <c r="B69" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C69" s="46" t="n"/>
@@ -2169,7 +2151,7 @@
       <c r="G69" s="46" t="n"/>
       <c r="H69" s="46" t="n"/>
       <c r="I69" s="46">
-        <f>SUM(C69:H69)</f>
+        <f>SUM(C68:H68)</f>
         <v/>
       </c>
     </row>
@@ -2181,7 +2163,7 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C70" s="46" t="n"/>
@@ -2191,7 +2173,7 @@
       <c r="G70" s="46" t="n"/>
       <c r="H70" s="46" t="n"/>
       <c r="I70" s="46">
-        <f>SUM(C70:H70)</f>
+        <f>SUM(C69:H69)</f>
         <v/>
       </c>
     </row>
@@ -2203,7 +2185,7 @@
       </c>
       <c r="B71" s="45" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C71" s="46" t="n"/>
@@ -2213,7 +2195,7 @@
       <c r="G71" s="46" t="n"/>
       <c r="H71" s="46" t="n"/>
       <c r="I71" s="46">
-        <f>SUM(C71:H71)</f>
+        <f>SUM(C70:H70)</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +2207,7 @@
       </c>
       <c r="B72" s="45" t="inlineStr">
         <is>
-          <t>간병인사용일당 (상해)</t>
+          <t>간병인사용일당 (질병)</t>
         </is>
       </c>
       <c r="C72" s="46" t="n"/>
@@ -2235,115 +2217,122 @@
       <c r="G72" s="46" t="n"/>
       <c r="H72" s="46" t="n"/>
       <c r="I72" s="46">
+        <f>SUM(C71:H71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="27">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>간병인사용일당 (상해)</t>
+        </is>
+      </c>
+      <c r="C73" s="46" t="n"/>
+      <c r="D73" s="46" t="n"/>
+      <c r="E73" s="46" t="n"/>
+      <c r="F73" s="46" t="n"/>
+      <c r="G73" s="46" t="n"/>
+      <c r="H73" s="46" t="n"/>
+      <c r="I73" s="46">
         <f>SUM(C72:H72)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="27">
-      <c r="A73" s="43" t="inlineStr">
+    <row r="74" ht="11.25" customHeight="1" s="27">
+      <c r="A74" s="43" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="11.25" customHeight="1" s="27">
-      <c r="A74" s="44" t="inlineStr">
+    <row r="75" ht="15" customHeight="1" s="27">
+      <c r="A75" s="44" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B74" s="45" t="inlineStr">
+      <c r="B75" s="45" t="inlineStr">
         <is>
           <t>골절진단비</t>
         </is>
       </c>
-      <c r="C74" s="46" t="n"/>
-      <c r="D74" s="46" t="n"/>
-      <c r="E74" s="46" t="n"/>
-      <c r="F74" s="46" t="n"/>
-      <c r="G74" s="46" t="n"/>
-      <c r="H74" s="46" t="n"/>
-      <c r="I74" s="46">
+      <c r="C75" s="46" t="n"/>
+      <c r="D75" s="46" t="n"/>
+      <c r="E75" s="46" t="n"/>
+      <c r="F75" s="46" t="n"/>
+      <c r="G75" s="46" t="n"/>
+      <c r="H75" s="46" t="n"/>
+      <c r="I75" s="46">
         <f>SUM(C74:H74)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="27">
-      <c r="A75" s="43" t="inlineStr">
+    <row r="76" ht="12.75" customHeight="1" s="27">
+      <c r="A76" s="43" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="12.75" customHeight="1" s="27">
-      <c r="A76" s="50" t="inlineStr">
+    <row r="77" ht="15.75" customHeight="1" s="27">
+      <c r="A77" s="50" t="inlineStr">
         <is>
           <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1" s="27">
-      <c r="A77" s="51" t="inlineStr">
+    <row r="78" ht="3" customHeight="1" s="27">
+      <c r="A78" s="51" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C77" s="42">
+      <c r="C78" s="42">
         <f>C7*C6</f>
         <v/>
       </c>
-      <c r="D77" s="42">
+      <c r="D78" s="42">
         <f>D7*D6</f>
         <v/>
       </c>
-      <c r="E77" s="42">
+      <c r="E78" s="42">
         <f>E7*E6</f>
         <v/>
       </c>
-      <c r="F77" s="42">
+      <c r="F78" s="42">
         <f>F7*F6</f>
         <v/>
       </c>
-      <c r="G77" s="42">
+      <c r="G78" s="42">
         <f>G7*G6</f>
         <v/>
       </c>
-      <c r="H77" s="42">
+      <c r="H78" s="42">
         <f>H7*H6</f>
         <v/>
       </c>
-      <c r="I77" s="42">
+      <c r="I78" s="42">
         <f>I7*I6</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="3" customHeight="1" s="27"/>
-    <row r="79" ht="15.75" customHeight="1" s="27">
-      <c r="A79" s="52" t="inlineStr">
+    <row r="79" ht="15.75" customHeight="1" s="27"/>
+    <row r="80" ht="19.5" customHeight="1" s="27">
+      <c r="A80" s="52" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1" s="27">
-      <c r="A80" s="53" t="inlineStr">
-        <is>
-          <t>상품1</t>
-        </is>
-      </c>
-      <c r="B80" s="54" t="n"/>
-      <c r="C80" s="55" t="n"/>
-      <c r="D80" s="56" t="n"/>
-      <c r="E80" s="56" t="n"/>
-      <c r="F80" s="56" t="n"/>
-      <c r="G80" s="56" t="n"/>
-      <c r="H80" s="56" t="n"/>
-      <c r="I80" s="54" t="n"/>
     </row>
     <row r="81" ht="19.5" customHeight="1" s="27">
       <c r="A81" s="53" t="inlineStr">
         <is>
-          <t>상품2</t>
+          <t>상품1</t>
         </is>
       </c>
       <c r="B81" s="54" t="n"/>
@@ -2358,7 +2347,7 @@
     <row r="82" ht="19.5" customHeight="1" s="27">
       <c r="A82" s="53" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B82" s="54" t="n"/>
@@ -2373,7 +2362,7 @@
     <row r="83" ht="19.5" customHeight="1" s="27">
       <c r="A83" s="53" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B83" s="54" t="n"/>
@@ -2388,7 +2377,7 @@
     <row r="84" ht="19.5" customHeight="1" s="27">
       <c r="A84" s="53" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B84" s="54" t="n"/>
@@ -2403,7 +2392,7 @@
     <row r="85" ht="19.5" customHeight="1" s="27">
       <c r="A85" s="53" t="inlineStr">
         <is>
-          <t>상품6</t>
+          <t>상품5</t>
         </is>
       </c>
       <c r="B85" s="54" t="n"/>
@@ -2415,8 +2404,23 @@
       <c r="H85" s="56" t="n"/>
       <c r="I85" s="54" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" s="53" t="inlineStr">
+        <is>
+          <t>상품6</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n"/>
+      <c r="C86" s="55" t="n"/>
+      <c r="D86" s="56" t="n"/>
+      <c r="E86" s="56" t="n"/>
+      <c r="F86" s="56" t="n"/>
+      <c r="G86" s="56" t="n"/>
+      <c r="H86" s="56" t="n"/>
+      <c r="I86" s="54" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:I75"/>
     <mergeCell ref="C82:I82"/>
@@ -2429,14 +2433,15 @@
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="C85:I85"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A73:I73"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
@@ -882,32 +882,50 @@
       <c r="H6" s="40" t="n"/>
       <c r="I6" s="40" t="n"/>
     </row>
-    <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="39" t="inlineStr">
-        <is>
-          <t>보장기간</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
-      <c r="E7" s="40" t="n"/>
-      <c r="F7" s="40" t="n"/>
-      <c r="G7" s="40" t="n"/>
-      <c r="H7" s="40" t="n"/>
-      <c r="I7" s="40" t="n"/>
+    <row r="7" ht="15.75" customHeight="1" s="27">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>▶  월 납입 보험료</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="42">
+        <f>SUM(C7:H7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="41" t="inlineStr">
-        <is>
-          <t>▶  월 납입 보험료</t>
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>▶  사망 보장</t>
         </is>
       </c>
     </row>
     <row r="9" ht="11.25" customHeight="1" s="27">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>▶  사망 보장</t>
-        </is>
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>사망</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>일반사망</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46">
+        <f>SUM(C9:H9)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="11.25" customHeight="1" s="27">
@@ -918,7 +936,7 @@
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
-          <t>일반사망</t>
+          <t>질병사망</t>
         </is>
       </c>
       <c r="C10" s="46" t="n"/>
@@ -928,7 +946,7 @@
       <c r="G10" s="46" t="n"/>
       <c r="H10" s="46" t="n"/>
       <c r="I10" s="46">
-        <f>SUM(C9:H9)</f>
+        <f>SUM(C10:H10)</f>
         <v/>
       </c>
     </row>
@@ -940,7 +958,7 @@
       </c>
       <c r="B11" s="45" t="inlineStr">
         <is>
-          <t>질병사망</t>
+          <t>암사망</t>
         </is>
       </c>
       <c r="C11" s="46" t="n"/>
@@ -950,7 +968,7 @@
       <c r="G11" s="46" t="n"/>
       <c r="H11" s="46" t="n"/>
       <c r="I11" s="46">
-        <f>SUM(C10:H10)</f>
+        <f>SUM(C11:H11)</f>
         <v/>
       </c>
     </row>
@@ -962,7 +980,7 @@
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
-          <t>암사망</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="C12" s="46" t="n"/>
@@ -972,19 +990,19 @@
       <c r="G12" s="46" t="n"/>
       <c r="H12" s="46" t="n"/>
       <c r="I12" s="46">
-        <f>SUM(C11:H11)</f>
+        <f>SUM(C12:H12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="11.25" customHeight="1" s="27">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>사망</t>
+          <t>장해</t>
         </is>
       </c>
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>상해후유장해(100%)</t>
         </is>
       </c>
       <c r="C13" s="46" t="n"/>
@@ -994,7 +1012,7 @@
       <c r="G13" s="46" t="n"/>
       <c r="H13" s="46" t="n"/>
       <c r="I13" s="46">
-        <f>SUM(C12:H12)</f>
+        <f>SUM(C13:H13)</f>
         <v/>
       </c>
     </row>
@@ -1006,7 +1024,7 @@
       </c>
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>상해후유장해(100%)</t>
+          <t>상해후유장해(3%)</t>
         </is>
       </c>
       <c r="C14" s="46" t="n"/>
@@ -1016,7 +1034,7 @@
       <c r="G14" s="46" t="n"/>
       <c r="H14" s="46" t="n"/>
       <c r="I14" s="46">
-        <f>SUM(C13:H13)</f>
+        <f>SUM(C14:H14)</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1046,7 @@
       </c>
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>상해후유장해(3%)</t>
+          <t>질병후유장해(100%)</t>
         </is>
       </c>
       <c r="C15" s="46" t="n"/>
@@ -1038,37 +1056,37 @@
       <c r="G15" s="46" t="n"/>
       <c r="H15" s="46" t="n"/>
       <c r="I15" s="46">
-        <f>SUM(C14:H14)</f>
+        <f>SUM(C15:H15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="27">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>장해</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>질병후유장해(100%)</t>
-        </is>
-      </c>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n"/>
-      <c r="G16" s="46" t="n"/>
-      <c r="H16" s="46" t="n"/>
-      <c r="I16" s="46">
-        <f>SUM(C15:H15)</f>
-        <v/>
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>▶  ⊕ 암 진단</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="11.25" customHeight="1" s="27">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>▶  ⊕ 암 진단</t>
-        </is>
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>암진단</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>일반암 진단비</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="46" t="n"/>
+      <c r="G17" s="46" t="n"/>
+      <c r="H17" s="46" t="n"/>
+      <c r="I17" s="46">
+        <f>SUM(C17:H17)</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="11.25" customHeight="1" s="27">
@@ -1079,7 +1097,7 @@
       </c>
       <c r="B18" s="45" t="inlineStr">
         <is>
-          <t>일반암 진단비</t>
+          <t>고액암 진단비</t>
         </is>
       </c>
       <c r="C18" s="46" t="n"/>
@@ -1089,7 +1107,7 @@
       <c r="G18" s="46" t="n"/>
       <c r="H18" s="46" t="n"/>
       <c r="I18" s="46">
-        <f>SUM(C17:H17)</f>
+        <f>SUM(C18:H18)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1119,7 @@
       </c>
       <c r="B19" s="45" t="inlineStr">
         <is>
-          <t>고액암 진단비</t>
+          <t>소액암 진단비</t>
         </is>
       </c>
       <c r="C19" s="46" t="n"/>
@@ -1111,19 +1129,19 @@
       <c r="G19" s="46" t="n"/>
       <c r="H19" s="46" t="n"/>
       <c r="I19" s="46">
-        <f>SUM(C18:H18)</f>
+        <f>SUM(C19:H19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="11.25" customHeight="1" s="27">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>암진단</t>
+          <t>말기진단</t>
         </is>
       </c>
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>소액암 진단비</t>
+          <t>말기간질환 진단비</t>
         </is>
       </c>
       <c r="C20" s="46" t="n"/>
@@ -1133,7 +1151,7 @@
       <c r="G20" s="46" t="n"/>
       <c r="H20" s="46" t="n"/>
       <c r="I20" s="46">
-        <f>SUM(C19:H19)</f>
+        <f>SUM(C20:H20)</f>
         <v/>
       </c>
     </row>
@@ -1145,7 +1163,7 @@
       </c>
       <c r="B21" s="45" t="inlineStr">
         <is>
-          <t>말기간질환 진단비</t>
+          <t>말기폐질환 진단비</t>
         </is>
       </c>
       <c r="C21" s="46" t="n"/>
@@ -1155,7 +1173,7 @@
       <c r="G21" s="46" t="n"/>
       <c r="H21" s="46" t="n"/>
       <c r="I21" s="46">
-        <f>SUM(C20:H20)</f>
+        <f>SUM(C21:H21)</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1185,7 @@
       </c>
       <c r="B22" s="45" t="inlineStr">
         <is>
-          <t>말기폐질환 진단비</t>
+          <t>말기신부전증 진단비</t>
         </is>
       </c>
       <c r="C22" s="46" t="n"/>
@@ -1177,37 +1195,37 @@
       <c r="G22" s="46" t="n"/>
       <c r="H22" s="46" t="n"/>
       <c r="I22" s="46">
-        <f>SUM(C21:H21)</f>
+        <f>SUM(C22:H22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="27">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>말기진단</t>
-        </is>
-      </c>
-      <c r="B23" s="45" t="inlineStr">
-        <is>
-          <t>말기신부전증 진단비</t>
-        </is>
-      </c>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
-      <c r="H23" s="46" t="n"/>
-      <c r="I23" s="46">
-        <f>SUM(C22:H22)</f>
-        <v/>
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="11.25" customHeight="1" s="27">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
-        </is>
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>암치료</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>상급병원암주요치료비(수술)</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
+      <c r="E24" s="46" t="n"/>
+      <c r="F24" s="46" t="n"/>
+      <c r="G24" s="46" t="n"/>
+      <c r="H24" s="46" t="n"/>
+      <c r="I24" s="46">
+        <f>SUM(C24:H24)</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="11.25" customHeight="1" s="27">
@@ -1218,7 +1236,7 @@
       </c>
       <c r="B25" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(수술)</t>
+          <t>상급병원암주요치료비(방사선)</t>
         </is>
       </c>
       <c r="C25" s="46" t="n"/>
@@ -1228,7 +1246,7 @@
       <c r="G25" s="46" t="n"/>
       <c r="H25" s="46" t="n"/>
       <c r="I25" s="46">
-        <f>SUM(C24:H24)</f>
+        <f>SUM(C25:H25)</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1258,7 @@
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(약물)</t>
         </is>
       </c>
       <c r="C26" s="46" t="n"/>
@@ -1250,7 +1268,7 @@
       <c r="G26" s="46" t="n"/>
       <c r="H26" s="46" t="n"/>
       <c r="I26" s="46">
-        <f>SUM(C25:H25)</f>
+        <f>SUM(C26:H26)</f>
         <v/>
       </c>
     </row>
@@ -1262,7 +1280,7 @@
       </c>
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(복합)</t>
         </is>
       </c>
       <c r="C27" s="46" t="n"/>
@@ -1272,7 +1290,7 @@
       <c r="G27" s="46" t="n"/>
       <c r="H27" s="46" t="n"/>
       <c r="I27" s="46">
-        <f>SUM(C26:H26)</f>
+        <f>SUM(C27:H27)</f>
         <v/>
       </c>
     </row>
@@ -1284,7 +1302,7 @@
       </c>
       <c r="B28" s="45" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>종합병원비급여암주요치료비</t>
         </is>
       </c>
       <c r="C28" s="46" t="n"/>
@@ -1294,7 +1312,7 @@
       <c r="G28" s="46" t="n"/>
       <c r="H28" s="46" t="n"/>
       <c r="I28" s="46">
-        <f>SUM(C27:H27)</f>
+        <f>SUM(C28:H28)</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1324,7 @@
       </c>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>항암방사선치료</t>
         </is>
       </c>
       <c r="C29" s="46" t="n"/>
@@ -1316,7 +1334,7 @@
       <c r="G29" s="46" t="n"/>
       <c r="H29" s="46" t="n"/>
       <c r="I29" s="46">
-        <f>SUM(C28:H28)</f>
+        <f>SUM(C29:H29)</f>
         <v/>
       </c>
     </row>
@@ -1328,7 +1346,7 @@
       </c>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>항암방사선치료</t>
+          <t>항암세기조절방사선치료</t>
         </is>
       </c>
       <c r="C30" s="46" t="n"/>
@@ -1338,7 +1356,7 @@
       <c r="G30" s="46" t="n"/>
       <c r="H30" s="46" t="n"/>
       <c r="I30" s="46">
-        <f>SUM(C29:H29)</f>
+        <f>SUM(C30:H30)</f>
         <v/>
       </c>
     </row>
@@ -1350,7 +1368,7 @@
       </c>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>항암세기조절방사선치료</t>
+          <t>항암양성자방사선치료</t>
         </is>
       </c>
       <c r="C31" s="46" t="n"/>
@@ -1360,7 +1378,7 @@
       <c r="G31" s="46" t="n"/>
       <c r="H31" s="46" t="n"/>
       <c r="I31" s="46">
-        <f>SUM(C30:H30)</f>
+        <f>SUM(C31:H31)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1390,7 @@
       </c>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>항암양성자방사선치료</t>
+          <t>항암약물치료</t>
         </is>
       </c>
       <c r="C32" s="46" t="n"/>
@@ -1382,7 +1400,7 @@
       <c r="G32" s="46" t="n"/>
       <c r="H32" s="46" t="n"/>
       <c r="I32" s="46">
-        <f>SUM(C31:H31)</f>
+        <f>SUM(C32:H32)</f>
         <v/>
       </c>
     </row>
@@ -1394,7 +1412,7 @@
       </c>
       <c r="B33" s="45" t="inlineStr">
         <is>
-          <t>항암약물치료</t>
+          <t>표적항암약물 허가치료</t>
         </is>
       </c>
       <c r="C33" s="46" t="n"/>
@@ -1404,7 +1422,7 @@
       <c r="G33" s="46" t="n"/>
       <c r="H33" s="46" t="n"/>
       <c r="I33" s="46">
-        <f>SUM(C32:H32)</f>
+        <f>SUM(C33:H33)</f>
         <v/>
       </c>
     </row>
@@ -1414,9 +1432,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B34" s="45" t="inlineStr">
-        <is>
-          <t>표적항암약물 허가치료</t>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>CAR-T 항암약물 허가치료</t>
         </is>
       </c>
       <c r="C34" s="46" t="n"/>
@@ -1426,7 +1444,7 @@
       <c r="G34" s="46" t="n"/>
       <c r="H34" s="46" t="n"/>
       <c r="I34" s="46">
-        <f>SUM(C33:H33)</f>
+        <f>SUM(C34:H34)</f>
         <v/>
       </c>
     </row>
@@ -1436,9 +1454,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B35" s="47" t="inlineStr">
-        <is>
-          <t>CAR-T 항암약물 허가치료</t>
+      <c r="B35" s="45" t="inlineStr">
+        <is>
+          <t>항암호르몬약물 허가치료</t>
         </is>
       </c>
       <c r="C35" s="46" t="n"/>
@@ -1448,7 +1466,7 @@
       <c r="G35" s="46" t="n"/>
       <c r="H35" s="46" t="n"/>
       <c r="I35" s="46">
-        <f>SUM(C34:H34)</f>
+        <f>SUM(C35:H35)</f>
         <v/>
       </c>
     </row>
@@ -1460,7 +1478,7 @@
       </c>
       <c r="B36" s="45" t="inlineStr">
         <is>
-          <t>항암호르몬약물 허가치료</t>
+          <t>항암중입자방사선치료</t>
         </is>
       </c>
       <c r="C36" s="46" t="n"/>
@@ -1470,7 +1488,7 @@
       <c r="G36" s="46" t="n"/>
       <c r="H36" s="46" t="n"/>
       <c r="I36" s="46">
-        <f>SUM(C35:H35)</f>
+        <f>SUM(C36:H36)</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1500,7 @@
       </c>
       <c r="B37" s="45" t="inlineStr">
         <is>
-          <t>항암중입자방사선치료</t>
+          <t>암직접치료상급종합병원통원</t>
         </is>
       </c>
       <c r="C37" s="46" t="n"/>
@@ -1492,37 +1510,37 @@
       <c r="G37" s="46" t="n"/>
       <c r="H37" s="46" t="n"/>
       <c r="I37" s="46">
-        <f>SUM(C36:H36)</f>
+        <f>SUM(C37:H37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="27">
-      <c r="A38" s="44" t="inlineStr">
-        <is>
-          <t>암치료</t>
-        </is>
-      </c>
-      <c r="B38" s="45" t="inlineStr">
-        <is>
-          <t>암직접치료상급종합병원통원</t>
-        </is>
-      </c>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
-      <c r="E38" s="46" t="n"/>
-      <c r="F38" s="46" t="n"/>
-      <c r="G38" s="46" t="n"/>
-      <c r="H38" s="46" t="n"/>
-      <c r="I38" s="46">
-        <f>SUM(C37:H37)</f>
-        <v/>
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>▶  ♥ 심뇌혈관 보장</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="11.25" customHeight="1" s="27">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>▶  ♥ 심뇌혈관 보장</t>
-        </is>
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>심뇌</t>
+        </is>
+      </c>
+      <c r="B39" s="45" t="inlineStr">
+        <is>
+          <t>뇌혈관질환 진단</t>
+        </is>
+      </c>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
+      <c r="E39" s="46" t="n"/>
+      <c r="F39" s="46" t="n"/>
+      <c r="G39" s="46" t="n"/>
+      <c r="H39" s="46" t="n"/>
+      <c r="I39" s="46">
+        <f>SUM(C39:H39)</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="11.25" customHeight="1" s="27">
@@ -1533,7 +1551,7 @@
       </c>
       <c r="B40" s="45" t="inlineStr">
         <is>
-          <t>뇌혈관질환 진단</t>
+          <t>뇌경색증진단</t>
         </is>
       </c>
       <c r="C40" s="46" t="n"/>
@@ -1543,7 +1561,7 @@
       <c r="G40" s="46" t="n"/>
       <c r="H40" s="46" t="n"/>
       <c r="I40" s="46">
-        <f>SUM(C39:H39)</f>
+        <f>SUM(C40:H40)</f>
         <v/>
       </c>
     </row>
@@ -1555,7 +1573,7 @@
       </c>
       <c r="B41" s="45" t="inlineStr">
         <is>
-          <t>뇌경색증진단</t>
+          <t>뇌출혈 진단</t>
         </is>
       </c>
       <c r="C41" s="46" t="n"/>
@@ -1565,7 +1583,7 @@
       <c r="G41" s="46" t="n"/>
       <c r="H41" s="46" t="n"/>
       <c r="I41" s="46">
-        <f>SUM(C40:H40)</f>
+        <f>SUM(C41:H41)</f>
         <v/>
       </c>
     </row>
@@ -1577,7 +1595,7 @@
       </c>
       <c r="B42" s="45" t="inlineStr">
         <is>
-          <t>뇌출혈 진단</t>
+          <t>급성심근경색 진단</t>
         </is>
       </c>
       <c r="C42" s="46" t="n"/>
@@ -1587,7 +1605,7 @@
       <c r="G42" s="46" t="n"/>
       <c r="H42" s="46" t="n"/>
       <c r="I42" s="46">
-        <f>SUM(C41:H41)</f>
+        <f>SUM(C42:H42)</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1617,7 @@
       </c>
       <c r="B43" s="45" t="inlineStr">
         <is>
-          <t>급성심근경색 진단</t>
+          <t>허혈심장질환 진단</t>
         </is>
       </c>
       <c r="C43" s="46" t="n"/>
@@ -1609,7 +1627,7 @@
       <c r="G43" s="46" t="n"/>
       <c r="H43" s="46" t="n"/>
       <c r="I43" s="46">
-        <f>SUM(C42:H42)</f>
+        <f>SUM(C43:H43)</f>
         <v/>
       </c>
     </row>
@@ -1621,7 +1639,7 @@
       </c>
       <c r="B44" s="45" t="inlineStr">
         <is>
-          <t>허혈심장질환 진단</t>
+          <t>순환계질환 수술 (연1회)</t>
         </is>
       </c>
       <c r="C44" s="46" t="n"/>
@@ -1631,7 +1649,7 @@
       <c r="G44" s="46" t="n"/>
       <c r="H44" s="46" t="n"/>
       <c r="I44" s="46">
-        <f>SUM(C43:H43)</f>
+        <f>SUM(C44:H44)</f>
         <v/>
       </c>
     </row>
@@ -1643,7 +1661,7 @@
       </c>
       <c r="B45" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 수술 (연1회)</t>
+          <t>순환계질환 혈전 용해 (연1회)</t>
         </is>
       </c>
       <c r="C45" s="46" t="n"/>
@@ -1653,7 +1671,7 @@
       <c r="G45" s="46" t="n"/>
       <c r="H45" s="46" t="n"/>
       <c r="I45" s="46">
-        <f>SUM(C44:H44)</f>
+        <f>SUM(C45:H45)</f>
         <v/>
       </c>
     </row>
@@ -1665,7 +1683,7 @@
       </c>
       <c r="B46" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 혈전 용해 (연1회)</t>
+          <t>순환계질환 혈전제거 (연1회)</t>
         </is>
       </c>
       <c r="C46" s="46" t="n"/>
@@ -1675,7 +1693,7 @@
       <c r="G46" s="46" t="n"/>
       <c r="H46" s="46" t="n"/>
       <c r="I46" s="46">
-        <f>SUM(C45:H45)</f>
+        <f>SUM(C46:H46)</f>
         <v/>
       </c>
     </row>
@@ -1687,7 +1705,7 @@
       </c>
       <c r="B47" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 혈전제거 (연1회)</t>
+          <t>순환계질환 복합치료 (연1회)</t>
         </is>
       </c>
       <c r="C47" s="46" t="n"/>
@@ -1697,7 +1715,7 @@
       <c r="G47" s="46" t="n"/>
       <c r="H47" s="46" t="n"/>
       <c r="I47" s="46">
-        <f>SUM(C46:H46)</f>
+        <f>SUM(C47:H47)</f>
         <v/>
       </c>
     </row>
@@ -1709,7 +1727,7 @@
       </c>
       <c r="B48" s="45" t="inlineStr">
         <is>
-          <t>순환계질환 복합치료 (연1회)</t>
+          <t>순환계질환 중환자실 (연1회)</t>
         </is>
       </c>
       <c r="C48" s="46" t="n"/>
@@ -1719,37 +1737,37 @@
       <c r="G48" s="46" t="n"/>
       <c r="H48" s="46" t="n"/>
       <c r="I48" s="46">
-        <f>SUM(C47:H47)</f>
+        <f>SUM(C48:H48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="27">
-      <c r="A49" s="44" t="inlineStr">
-        <is>
-          <t>심뇌</t>
-        </is>
-      </c>
-      <c r="B49" s="45" t="inlineStr">
-        <is>
-          <t>순환계질환 중환자실 (연1회)</t>
-        </is>
-      </c>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
-      <c r="E49" s="46" t="n"/>
-      <c r="F49" s="46" t="n"/>
-      <c r="G49" s="46" t="n"/>
-      <c r="H49" s="46" t="n"/>
-      <c r="I49" s="46">
-        <f>SUM(C48:H48)</f>
-        <v/>
+      <c r="A49" s="43" t="inlineStr">
+        <is>
+          <t>▶  ✚ 수술 보장</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="11.25" customHeight="1" s="27">
-      <c r="A50" s="43" t="inlineStr">
-        <is>
-          <t>▶  ✚ 수술 보장</t>
-        </is>
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>질병 수술비</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
+      <c r="E50" s="46" t="n"/>
+      <c r="F50" s="46" t="n"/>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="46" t="n"/>
+      <c r="I50" s="46">
+        <f>SUM(C50:H50)</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="11.25" customHeight="1" s="27">
@@ -1760,7 +1778,7 @@
       </c>
       <c r="B51" s="45" t="inlineStr">
         <is>
-          <t>질병 수술비</t>
+          <t>상급종합병원질병수술</t>
         </is>
       </c>
       <c r="C51" s="46" t="n"/>
@@ -1770,7 +1788,7 @@
       <c r="G51" s="46" t="n"/>
       <c r="H51" s="46" t="n"/>
       <c r="I51" s="46">
-        <f>SUM(C50:H50)</f>
+        <f>SUM(C51:H51)</f>
         <v/>
       </c>
     </row>
@@ -1782,7 +1800,7 @@
       </c>
       <c r="B52" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원질병수술</t>
+          <t>재해 수술비</t>
         </is>
       </c>
       <c r="C52" s="46" t="n"/>
@@ -1792,7 +1810,7 @@
       <c r="G52" s="46" t="n"/>
       <c r="H52" s="46" t="n"/>
       <c r="I52" s="46">
-        <f>SUM(C51:H51)</f>
+        <f>SUM(C52:H52)</f>
         <v/>
       </c>
     </row>
@@ -1804,7 +1822,7 @@
       </c>
       <c r="B53" s="45" t="inlineStr">
         <is>
-          <t>재해 수술비</t>
+          <t>암 수술비</t>
         </is>
       </c>
       <c r="C53" s="46" t="n"/>
@@ -1814,7 +1832,7 @@
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="46" t="n"/>
       <c r="I53" s="46">
-        <f>SUM(C52:H52)</f>
+        <f>SUM(C53:H53)</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1844,7 @@
       </c>
       <c r="B54" s="45" t="inlineStr">
         <is>
-          <t>암 수술비</t>
+          <t>뇌출혈 수술</t>
         </is>
       </c>
       <c r="C54" s="46" t="n"/>
@@ -1836,7 +1854,7 @@
       <c r="G54" s="46" t="n"/>
       <c r="H54" s="46" t="n"/>
       <c r="I54" s="46">
-        <f>SUM(C53:H53)</f>
+        <f>SUM(C54:H54)</f>
         <v/>
       </c>
     </row>
@@ -1848,7 +1866,7 @@
       </c>
       <c r="B55" s="45" t="inlineStr">
         <is>
-          <t>뇌출혈 수술</t>
+          <t>급성심근경색 수술</t>
         </is>
       </c>
       <c r="C55" s="46" t="n"/>
@@ -1858,7 +1876,7 @@
       <c r="G55" s="46" t="n"/>
       <c r="H55" s="46" t="n"/>
       <c r="I55" s="46">
-        <f>SUM(C54:H54)</f>
+        <f>SUM(C55:H55)</f>
         <v/>
       </c>
     </row>
@@ -1868,9 +1886,9 @@
           <t>수술</t>
         </is>
       </c>
-      <c r="B56" s="45" t="inlineStr">
-        <is>
-          <t>급성심근경색 수술</t>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>1-5종 수술 1종</t>
         </is>
       </c>
       <c r="C56" s="46" t="n"/>
@@ -1880,7 +1898,7 @@
       <c r="G56" s="46" t="n"/>
       <c r="H56" s="46" t="n"/>
       <c r="I56" s="46">
-        <f>SUM(C55:H55)</f>
+        <f>SUM(C56:H56)</f>
         <v/>
       </c>
     </row>
@@ -1892,7 +1910,7 @@
       </c>
       <c r="B57" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 1종</t>
+          <t>1-5종 수술 2종</t>
         </is>
       </c>
       <c r="C57" s="46" t="n"/>
@@ -1902,7 +1920,7 @@
       <c r="G57" s="46" t="n"/>
       <c r="H57" s="46" t="n"/>
       <c r="I57" s="46">
-        <f>SUM(C56:H56)</f>
+        <f>SUM(C57:H57)</f>
         <v/>
       </c>
     </row>
@@ -1914,7 +1932,7 @@
       </c>
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 2종</t>
+          <t>1-5종 수술 3종</t>
         </is>
       </c>
       <c r="C58" s="46" t="n"/>
@@ -1924,7 +1942,7 @@
       <c r="G58" s="46" t="n"/>
       <c r="H58" s="46" t="n"/>
       <c r="I58" s="46">
-        <f>SUM(C57:H57)</f>
+        <f>SUM(C58:H58)</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1954,7 @@
       </c>
       <c r="B59" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 3종</t>
+          <t>1-5종 수술 4종</t>
         </is>
       </c>
       <c r="C59" s="46" t="n"/>
@@ -1946,7 +1964,7 @@
       <c r="G59" s="46" t="n"/>
       <c r="H59" s="46" t="n"/>
       <c r="I59" s="46">
-        <f>SUM(C58:H58)</f>
+        <f>SUM(C59:H59)</f>
         <v/>
       </c>
     </row>
@@ -1958,7 +1976,7 @@
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>1-5종 수술 4종</t>
+          <t>1-5종 수술 5종</t>
         </is>
       </c>
       <c r="C60" s="46" t="n"/>
@@ -1968,48 +1986,48 @@
       <c r="G60" s="46" t="n"/>
       <c r="H60" s="46" t="n"/>
       <c r="I60" s="46">
-        <f>SUM(C59:H59)</f>
+        <f>SUM(C60:H60)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="27">
-      <c r="A61" s="44" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B61" s="47" t="inlineStr">
-        <is>
-          <t>1-5종 수술 5종</t>
-        </is>
-      </c>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
-      <c r="E61" s="46" t="n"/>
-      <c r="F61" s="46" t="n"/>
-      <c r="G61" s="46" t="n"/>
-      <c r="H61" s="46" t="n"/>
-      <c r="I61" s="46">
-        <f>SUM(C60:H60)</f>
-        <v/>
+      <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="11.25" customHeight="1" s="27">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
-        </is>
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B62" s="49" t="inlineStr">
+        <is>
+          <t>질병/상해 입원 실비</t>
+        </is>
+      </c>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
+      <c r="E62" s="46" t="n"/>
+      <c r="F62" s="46" t="n"/>
+      <c r="G62" s="46" t="n"/>
+      <c r="H62" s="46" t="n"/>
+      <c r="I62" s="46">
+        <f>SUM(C62:H62)</f>
+        <v/>
       </c>
     </row>
     <row r="63" ht="11.25" customHeight="1" s="27">
       <c r="A63" s="48" t="inlineStr">
         <is>
-          <t>입원</t>
+          <t>통원</t>
         </is>
       </c>
       <c r="B63" s="49" t="inlineStr">
         <is>
-          <t>질병/상해 입원 실비</t>
+          <t>질병/상해 통원 실비</t>
         </is>
       </c>
       <c r="C63" s="46" t="n"/>
@@ -2019,19 +2037,19 @@
       <c r="G63" s="46" t="n"/>
       <c r="H63" s="46" t="n"/>
       <c r="I63" s="46">
-        <f>SUM(C62:H62)</f>
+        <f>SUM(C63:H63)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="11.25" customHeight="1" s="27">
-      <c r="A64" s="48" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="B64" s="49" t="inlineStr">
-        <is>
-          <t>질병/상해 통원 실비</t>
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C64" s="46" t="n"/>
@@ -2041,7 +2059,7 @@
       <c r="G64" s="46" t="n"/>
       <c r="H64" s="46" t="n"/>
       <c r="I64" s="46">
-        <f>SUM(C63:H63)</f>
+        <f>SUM(C64:H64)</f>
         <v/>
       </c>
     </row>
@@ -2053,7 +2071,7 @@
       </c>
       <c r="B65" s="45" t="inlineStr">
         <is>
-          <t>질병입원 일당</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C65" s="46" t="n"/>
@@ -2063,7 +2081,7 @@
       <c r="G65" s="46" t="n"/>
       <c r="H65" s="46" t="n"/>
       <c r="I65" s="46">
-        <f>SUM(C64:H64)</f>
+        <f>SUM(C65:H65)</f>
         <v/>
       </c>
     </row>
@@ -2075,7 +2093,7 @@
       </c>
       <c r="B66" s="45" t="inlineStr">
         <is>
-          <t>재해입원 일당</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C66" s="46" t="n"/>
@@ -2085,7 +2103,7 @@
       <c r="G66" s="46" t="n"/>
       <c r="H66" s="46" t="n"/>
       <c r="I66" s="46">
-        <f>SUM(C65:H65)</f>
+        <f>SUM(C66:H66)</f>
         <v/>
       </c>
     </row>
@@ -2097,7 +2115,7 @@
       </c>
       <c r="B67" s="45" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C67" s="46" t="n"/>
@@ -2107,7 +2125,7 @@
       <c r="G67" s="46" t="n"/>
       <c r="H67" s="46" t="n"/>
       <c r="I67" s="46">
-        <f>SUM(C66:H66)</f>
+        <f>SUM(C67:H67)</f>
         <v/>
       </c>
     </row>
@@ -2119,7 +2137,7 @@
       </c>
       <c r="B68" s="45" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C68" s="46" t="n"/>
@@ -2129,7 +2147,7 @@
       <c r="G68" s="46" t="n"/>
       <c r="H68" s="46" t="n"/>
       <c r="I68" s="46">
-        <f>SUM(C67:H67)</f>
+        <f>SUM(C68:H68)</f>
         <v/>
       </c>
     </row>
@@ -2141,7 +2159,7 @@
       </c>
       <c r="B69" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C69" s="46" t="n"/>
@@ -2151,7 +2169,7 @@
       <c r="G69" s="46" t="n"/>
       <c r="H69" s="46" t="n"/>
       <c r="I69" s="46">
-        <f>SUM(C68:H68)</f>
+        <f>SUM(C69:H69)</f>
         <v/>
       </c>
     </row>
@@ -2163,7 +2181,7 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C70" s="46" t="n"/>
@@ -2173,7 +2191,7 @@
       <c r="G70" s="46" t="n"/>
       <c r="H70" s="46" t="n"/>
       <c r="I70" s="46">
-        <f>SUM(C69:H69)</f>
+        <f>SUM(C70:H70)</f>
         <v/>
       </c>
     </row>
@@ -2185,7 +2203,7 @@
       </c>
       <c r="B71" s="45" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>간병인사용일당 (질병)</t>
         </is>
       </c>
       <c r="C71" s="46" t="n"/>
@@ -2195,7 +2213,7 @@
       <c r="G71" s="46" t="n"/>
       <c r="H71" s="46" t="n"/>
       <c r="I71" s="46">
-        <f>SUM(C70:H70)</f>
+        <f>SUM(C71:H71)</f>
         <v/>
       </c>
     </row>
@@ -2207,7 +2225,7 @@
       </c>
       <c r="B72" s="45" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>간병인사용일당 (상해)</t>
         </is>
       </c>
       <c r="C72" s="46" t="n"/>
@@ -2217,122 +2235,115 @@
       <c r="G72" s="46" t="n"/>
       <c r="H72" s="46" t="n"/>
       <c r="I72" s="46">
-        <f>SUM(C71:H71)</f>
+        <f>SUM(C72:H72)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="27">
-      <c r="A73" s="44" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B73" s="45" t="inlineStr">
-        <is>
-          <t>간병인사용일당 (상해)</t>
-        </is>
-      </c>
-      <c r="C73" s="46" t="n"/>
-      <c r="D73" s="46" t="n"/>
-      <c r="E73" s="46" t="n"/>
-      <c r="F73" s="46" t="n"/>
-      <c r="G73" s="46" t="n"/>
-      <c r="H73" s="46" t="n"/>
-      <c r="I73" s="46">
-        <f>SUM(C72:H72)</f>
-        <v/>
+      <c r="A73" s="43" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 치료비,기타</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="11.25" customHeight="1" s="27">
-      <c r="A74" s="43" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 치료비,기타</t>
-        </is>
+      <c r="A74" s="44" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>골절진단비</t>
+        </is>
+      </c>
+      <c r="C74" s="46" t="n"/>
+      <c r="D74" s="46" t="n"/>
+      <c r="E74" s="46" t="n"/>
+      <c r="F74" s="46" t="n"/>
+      <c r="G74" s="46" t="n"/>
+      <c r="H74" s="46" t="n"/>
+      <c r="I74" s="46">
+        <f>SUM(C74:H74)</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="27">
-      <c r="A75" s="44" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B75" s="45" t="inlineStr">
-        <is>
-          <t>골절진단비</t>
-        </is>
-      </c>
-      <c r="C75" s="46" t="n"/>
-      <c r="D75" s="46" t="n"/>
-      <c r="E75" s="46" t="n"/>
-      <c r="F75" s="46" t="n"/>
-      <c r="G75" s="46" t="n"/>
-      <c r="H75" s="46" t="n"/>
-      <c r="I75" s="46">
-        <f>SUM(C74:H74)</f>
-        <v/>
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1" s="27">
-      <c r="A76" s="43" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
+      <c r="A76" s="50" t="inlineStr">
+        <is>
+          <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="27">
-      <c r="A77" s="50" t="inlineStr">
-        <is>
-          <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="3" customHeight="1" s="27">
-      <c r="A78" s="51" t="inlineStr">
+      <c r="A77" s="51" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C78" s="42">
+      <c r="C77" s="42">
         <f>C7*C6</f>
         <v/>
       </c>
-      <c r="D78" s="42">
+      <c r="D77" s="42">
         <f>D7*D6</f>
         <v/>
       </c>
-      <c r="E78" s="42">
+      <c r="E77" s="42">
         <f>E7*E6</f>
         <v/>
       </c>
-      <c r="F78" s="42">
+      <c r="F77" s="42">
         <f>F7*F6</f>
         <v/>
       </c>
-      <c r="G78" s="42">
+      <c r="G77" s="42">
         <f>G7*G6</f>
         <v/>
       </c>
-      <c r="H78" s="42">
+      <c r="H77" s="42">
         <f>H7*H6</f>
         <v/>
       </c>
-      <c r="I78" s="42">
+      <c r="I77" s="42">
         <f>I7*I6</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="27"/>
+    <row r="78" ht="3" customHeight="1" s="27"/>
+    <row r="79" ht="15.75" customHeight="1" s="27">
+      <c r="A79" s="52" t="inlineStr">
+        <is>
+          <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
+        </is>
+      </c>
+    </row>
     <row r="80" ht="19.5" customHeight="1" s="27">
-      <c r="A80" s="52" t="inlineStr">
-        <is>
-          <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
-        </is>
-      </c>
+      <c r="A80" s="53" t="inlineStr">
+        <is>
+          <t>상품1</t>
+        </is>
+      </c>
+      <c r="B80" s="54" t="n"/>
+      <c r="C80" s="55" t="n"/>
+      <c r="D80" s="56" t="n"/>
+      <c r="E80" s="56" t="n"/>
+      <c r="F80" s="56" t="n"/>
+      <c r="G80" s="56" t="n"/>
+      <c r="H80" s="56" t="n"/>
+      <c r="I80" s="54" t="n"/>
     </row>
     <row r="81" ht="19.5" customHeight="1" s="27">
       <c r="A81" s="53" t="inlineStr">
         <is>
-          <t>상품1</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B81" s="54" t="n"/>
@@ -2347,7 +2358,7 @@
     <row r="82" ht="19.5" customHeight="1" s="27">
       <c r="A82" s="53" t="inlineStr">
         <is>
-          <t>상품2</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B82" s="54" t="n"/>
@@ -2362,7 +2373,7 @@
     <row r="83" ht="19.5" customHeight="1" s="27">
       <c r="A83" s="53" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B83" s="54" t="n"/>
@@ -2377,7 +2388,7 @@
     <row r="84" ht="19.5" customHeight="1" s="27">
       <c r="A84" s="53" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품5</t>
         </is>
       </c>
       <c r="B84" s="54" t="n"/>
@@ -2392,7 +2403,7 @@
     <row r="85" ht="19.5" customHeight="1" s="27">
       <c r="A85" s="53" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품6</t>
         </is>
       </c>
       <c r="B85" s="54" t="n"/>
@@ -2404,23 +2415,8 @@
       <c r="H85" s="56" t="n"/>
       <c r="I85" s="54" t="n"/>
     </row>
-    <row r="86">
-      <c r="A86" s="53" t="inlineStr">
-        <is>
-          <t>상품6</t>
-        </is>
-      </c>
-      <c r="B86" s="54" t="n"/>
-      <c r="C86" s="55" t="n"/>
-      <c r="D86" s="56" t="n"/>
-      <c r="E86" s="56" t="n"/>
-      <c r="F86" s="56" t="n"/>
-      <c r="G86" s="56" t="n"/>
-      <c r="H86" s="56" t="n"/>
-      <c r="I86" s="54" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:I75"/>
     <mergeCell ref="C82:I82"/>
@@ -2433,15 +2429,14 @@
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:I9"/>
     <mergeCell ref="C85:I85"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A73:I73"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -208,7 +208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -334,6 +334,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -345,7 +374,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -507,6 +536,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,12 +794,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="26" min="1" max="1"/>
     <col width="28" customWidth="1" style="26" min="2" max="2"/>
-    <col width="13" customWidth="1" style="26" min="3" max="9"/>
+    <col width="15" customWidth="1" style="26" min="3" max="9"/>
+    <col width="15" customWidth="1" style="27" min="4" max="4"/>
+    <col width="15" customWidth="1" style="27" min="5" max="5"/>
+    <col width="15" customWidth="1" style="27" min="6" max="6"/>
+    <col width="15" customWidth="1" style="27" min="7" max="7"/>
+    <col width="15" customWidth="1" style="27" min="8" max="8"/>
+    <col width="15" customWidth="1" style="27" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="27">
@@ -800,7 +840,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="27.75" customHeight="1" s="27">
+    <row r="3" ht="40" customHeight="1" s="27">
       <c r="A3" s="33" t="n"/>
       <c r="C3" s="34" t="inlineStr">
         <is>
@@ -2005,7 +2045,7 @@
       </c>
       <c r="B62" s="49" t="inlineStr">
         <is>
-          <t>질병/상해 입원 실비</t>
+          <t>질병 입원 실비</t>
         </is>
       </c>
       <c r="C62" s="46" t="n"/>
@@ -2022,12 +2062,12 @@
     <row r="63" ht="11.25" customHeight="1" s="27">
       <c r="A63" s="48" t="inlineStr">
         <is>
-          <t>통원</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B63" s="49" t="inlineStr">
         <is>
-          <t>질병/상해 통원 실비</t>
+          <t>상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="46" t="n"/>
@@ -2042,14 +2082,14 @@
       </c>
     </row>
     <row r="64" ht="11.25" customHeight="1" s="27">
-      <c r="A64" s="44" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B64" s="45" t="inlineStr">
-        <is>
-          <t>질병입원 일당</t>
+      <c r="A64" s="48" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B64" s="49" t="inlineStr">
+        <is>
+          <t>질병 통원 실비</t>
         </is>
       </c>
       <c r="C64" s="46" t="n"/>
@@ -2058,20 +2098,17 @@
       <c r="F64" s="46" t="n"/>
       <c r="G64" s="46" t="n"/>
       <c r="H64" s="46" t="n"/>
-      <c r="I64" s="46">
-        <f>SUM(C64:H64)</f>
-        <v/>
-      </c>
+      <c r="I64" s="46" t="n"/>
     </row>
     <row r="65" ht="11.25" customHeight="1" s="27">
-      <c r="A65" s="44" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B65" s="45" t="inlineStr">
-        <is>
-          <t>재해입원 일당</t>
+      <c r="A65" s="48" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B65" s="49" t="inlineStr">
+        <is>
+          <t>상해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="46" t="n"/>
@@ -2080,10 +2117,7 @@
       <c r="F65" s="46" t="n"/>
       <c r="G65" s="46" t="n"/>
       <c r="H65" s="46" t="n"/>
-      <c r="I65" s="46">
-        <f>SUM(C65:H65)</f>
-        <v/>
-      </c>
+      <c r="I65" s="46" t="n"/>
     </row>
     <row r="66" ht="11.25" customHeight="1" s="27">
       <c r="A66" s="44" t="inlineStr">
@@ -2093,7 +2127,7 @@
       </c>
       <c r="B66" s="45" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C66" s="46" t="n"/>
@@ -2103,7 +2137,7 @@
       <c r="G66" s="46" t="n"/>
       <c r="H66" s="46" t="n"/>
       <c r="I66" s="46">
-        <f>SUM(C66:H66)</f>
+        <f>SUM(C64:H64)</f>
         <v/>
       </c>
     </row>
@@ -2115,7 +2149,7 @@
       </c>
       <c r="B67" s="45" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C67" s="46" t="n"/>
@@ -2125,7 +2159,7 @@
       <c r="G67" s="46" t="n"/>
       <c r="H67" s="46" t="n"/>
       <c r="I67" s="46">
-        <f>SUM(C67:H67)</f>
+        <f>SUM(C65:H65)</f>
         <v/>
       </c>
     </row>
@@ -2137,7 +2171,7 @@
       </c>
       <c r="B68" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C68" s="46" t="n"/>
@@ -2147,7 +2181,7 @@
       <c r="G68" s="46" t="n"/>
       <c r="H68" s="46" t="n"/>
       <c r="I68" s="46">
-        <f>SUM(C68:H68)</f>
+        <f>SUM(C66:H66)</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2193,7 @@
       </c>
       <c r="B69" s="45" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C69" s="46" t="n"/>
@@ -2169,7 +2203,7 @@
       <c r="G69" s="46" t="n"/>
       <c r="H69" s="46" t="n"/>
       <c r="I69" s="46">
-        <f>SUM(C69:H69)</f>
+        <f>SUM(C67:H67)</f>
         <v/>
       </c>
     </row>
@@ -2181,7 +2215,7 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C70" s="46" t="n"/>
@@ -2191,7 +2225,7 @@
       <c r="G70" s="46" t="n"/>
       <c r="H70" s="46" t="n"/>
       <c r="I70" s="46">
-        <f>SUM(C70:H70)</f>
+        <f>SUM(C68:H68)</f>
         <v/>
       </c>
     </row>
@@ -2203,7 +2237,7 @@
       </c>
       <c r="B71" s="45" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C71" s="46" t="n"/>
@@ -2213,7 +2247,7 @@
       <c r="G71" s="46" t="n"/>
       <c r="H71" s="46" t="n"/>
       <c r="I71" s="46">
-        <f>SUM(C71:H71)</f>
+        <f>SUM(C69:H69)</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +2259,7 @@
       </c>
       <c r="B72" s="45" t="inlineStr">
         <is>
-          <t>간병인사용일당 (상해)</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C72" s="46" t="n"/>
@@ -2235,26 +2269,38 @@
       <c r="G72" s="46" t="n"/>
       <c r="H72" s="46" t="n"/>
       <c r="I72" s="46">
-        <f>SUM(C72:H72)</f>
+        <f>SUM(C70:H70)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="27">
-      <c r="A73" s="43" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 치료비,기타</t>
-        </is>
-      </c>
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>간병인사용일당 (질병)</t>
+        </is>
+      </c>
+      <c r="C73" s="46" t="n"/>
+      <c r="D73" s="46" t="n"/>
+      <c r="E73" s="46" t="n"/>
+      <c r="F73" s="46" t="n"/>
+      <c r="G73" s="46" t="n"/>
+      <c r="H73" s="46" t="n"/>
+      <c r="I73" s="46" t="n"/>
     </row>
     <row r="74" ht="11.25" customHeight="1" s="27">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B74" s="45" t="inlineStr">
         <is>
-          <t>골절진단비</t>
+          <t>간병인사용일당 (상해)</t>
         </is>
       </c>
       <c r="C74" s="46" t="n"/>
@@ -2264,101 +2310,77 @@
       <c r="G74" s="46" t="n"/>
       <c r="H74" s="46" t="n"/>
       <c r="I74" s="46">
-        <f>SUM(C74:H74)</f>
+        <f>SUM(C72:H72)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="27">
       <c r="A75" s="43" t="inlineStr">
         <is>
+          <t>▶  ⊞ 치료비,기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="12.75" customHeight="1" s="27">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B76" s="45" t="inlineStr">
+        <is>
+          <t>골절진단비</t>
+        </is>
+      </c>
+      <c r="C76" s="46" t="n"/>
+      <c r="D76" s="46" t="n"/>
+      <c r="E76" s="46" t="n"/>
+      <c r="F76" s="46" t="n"/>
+      <c r="G76" s="46" t="n"/>
+      <c r="H76" s="46" t="n"/>
+      <c r="I76" s="46" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="27">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="12.75" customHeight="1" s="27">
-      <c r="A76" s="50" t="inlineStr">
+    <row r="78" ht="3" customHeight="1" s="27">
+      <c r="A78" s="50" t="inlineStr">
         <is>
           <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1" s="27">
-      <c r="A77" s="51" t="inlineStr">
+    <row r="79" ht="15.75" customHeight="1" s="27">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C77" s="42">
-        <f>C7*C6</f>
-        <v/>
-      </c>
-      <c r="D77" s="42">
-        <f>D7*D6</f>
-        <v/>
-      </c>
-      <c r="E77" s="42">
-        <f>E7*E6</f>
-        <v/>
-      </c>
-      <c r="F77" s="42">
-        <f>F7*F6</f>
-        <v/>
-      </c>
-      <c r="G77" s="42">
-        <f>G7*G6</f>
-        <v/>
-      </c>
-      <c r="H77" s="42">
-        <f>H7*H6</f>
-        <v/>
-      </c>
-      <c r="I77" s="42">
-        <f>I7*I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="3" customHeight="1" s="27"/>
-    <row r="79" ht="15.75" customHeight="1" s="27">
-      <c r="A79" s="52" t="inlineStr">
+      <c r="B79" s="58" t="n"/>
+      <c r="C79" s="58" t="n"/>
+      <c r="D79" s="58" t="n"/>
+      <c r="E79" s="58" t="n"/>
+      <c r="F79" s="58" t="n"/>
+      <c r="G79" s="58" t="n"/>
+      <c r="H79" s="58" t="n"/>
+      <c r="I79" s="59" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1" s="27"/>
+    <row r="81" ht="19.5" customHeight="1" s="27">
+      <c r="A81" s="52" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="19.5" customHeight="1" s="27">
-      <c r="A80" s="53" t="inlineStr">
-        <is>
-          <t>상품1</t>
-        </is>
-      </c>
-      <c r="B80" s="54" t="n"/>
-      <c r="C80" s="55" t="n"/>
-      <c r="D80" s="56" t="n"/>
-      <c r="E80" s="56" t="n"/>
-      <c r="F80" s="56" t="n"/>
-      <c r="G80" s="56" t="n"/>
-      <c r="H80" s="56" t="n"/>
-      <c r="I80" s="54" t="n"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1" s="27">
-      <c r="A81" s="53" t="inlineStr">
-        <is>
-          <t>상품2</t>
-        </is>
-      </c>
-      <c r="B81" s="54" t="n"/>
-      <c r="C81" s="55" t="n"/>
-      <c r="D81" s="56" t="n"/>
-      <c r="E81" s="56" t="n"/>
-      <c r="F81" s="56" t="n"/>
-      <c r="G81" s="56" t="n"/>
-      <c r="H81" s="56" t="n"/>
-      <c r="I81" s="54" t="n"/>
     </row>
     <row r="82" ht="19.5" customHeight="1" s="27">
       <c r="A82" s="53" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품1</t>
         </is>
       </c>
       <c r="B82" s="54" t="n"/>
@@ -2373,7 +2395,7 @@
     <row r="83" ht="19.5" customHeight="1" s="27">
       <c r="A83" s="53" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B83" s="54" t="n"/>
@@ -2388,7 +2410,7 @@
     <row r="84" ht="19.5" customHeight="1" s="27">
       <c r="A84" s="53" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B84" s="54" t="n"/>
@@ -2403,7 +2425,7 @@
     <row r="85" ht="19.5" customHeight="1" s="27">
       <c r="A85" s="53" t="inlineStr">
         <is>
-          <t>상품6</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B85" s="54" t="n"/>
@@ -2415,8 +2437,38 @@
       <c r="H85" s="56" t="n"/>
       <c r="I85" s="54" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" s="53" t="inlineStr">
+        <is>
+          <t>상품5</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n"/>
+      <c r="C86" s="55" t="n"/>
+      <c r="D86" s="56" t="n"/>
+      <c r="E86" s="56" t="n"/>
+      <c r="F86" s="56" t="n"/>
+      <c r="G86" s="56" t="n"/>
+      <c r="H86" s="56" t="n"/>
+      <c r="I86" s="54" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="53" t="inlineStr">
+        <is>
+          <t>상품6</t>
+        </is>
+      </c>
+      <c r="B87" s="54" t="n"/>
+      <c r="C87" s="55" t="n"/>
+      <c r="D87" s="56" t="n"/>
+      <c r="E87" s="56" t="n"/>
+      <c r="F87" s="56" t="n"/>
+      <c r="G87" s="56" t="n"/>
+      <c r="H87" s="56" t="n"/>
+      <c r="I87" s="54" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="29">
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:I75"/>
     <mergeCell ref="C82:I82"/>
@@ -2424,7 +2476,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A76:I76"/>
     <mergeCell ref="C83:I83"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A84:B84"/>
@@ -2439,7 +2490,6 @@
     <mergeCell ref="C85:I85"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C84:I84"/>
-    <mergeCell ref="A73:I73"/>
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="C80:I80"/>
     <mergeCell ref="A81:B81"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B63" s="49" t="inlineStr">
         <is>
-          <t>상해 입원 실비</t>
+          <t>재해/상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="46" t="n"/>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B65" s="49" t="inlineStr">
         <is>
-          <t>상해 통원 실비</t>
+          <t>재해/상해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="46" t="n"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -4,53 +4,30 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보장분석표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="DejaVu Sans"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
@@ -63,18 +40,25 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="맑은 고딕"/>
       <charset val="1"/>
       <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <charset val="1"/>
       <family val="0"/>
-      <color rgb="FF000000"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -98,14 +82,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFCC0000"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="DejaVu Sans"/>
       <family val="2"/>
       <b val="1"/>
@@ -115,14 +91,6 @@
     <font>
       <name val="DejaVu Sans"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF1B2A4A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FF1B2A4A"/>
       <sz val="9"/>
@@ -208,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -238,6 +206,50 @@
       <right style="thin">
         <color rgb="FFBBBBBB"/>
       </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFBBBBBB"/>
       </top>
@@ -290,338 +302,176 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBBBBBB"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="60">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFCC0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBBBBBB"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF6BAED6"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF8DC"/>
-      <rgbColor rgb="FFE8E8E8"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2565A0"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1A3C6E"/>
-      <rgbColor rgb="FF4A90C8"/>
-      <rgbColor rgb="FF0F1A2E"/>
-      <rgbColor rgb="FF1B2A4A"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF5B2C6F"/>
-      <rgbColor rgb="FF3A3A3A"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -656,1851 +506,1985 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I87"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="26" min="1" max="1"/>
-    <col width="28" customWidth="1" style="26" min="2" max="2"/>
-    <col width="15" customWidth="1" style="26" min="3" max="9"/>
-    <col width="15" customWidth="1" style="27" min="4" max="4"/>
-    <col width="15" customWidth="1" style="27" min="5" max="5"/>
-    <col width="15" customWidth="1" style="27" min="6" max="6"/>
-    <col width="15" customWidth="1" style="27" min="7" max="7"/>
-    <col width="15" customWidth="1" style="27" min="8" max="8"/>
-    <col width="15" customWidth="1" style="27" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="27">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>○○○님 (남자, 00세) · 보장 분석표</t>
         </is>
       </c>
-      <c r="B1" s="29" t="n"/>
-      <c r="C1" s="29" t="n"/>
-      <c r="D1" s="29" t="n"/>
-      <c r="E1" s="29" t="n"/>
-      <c r="F1" s="29" t="n"/>
-      <c r="G1" s="29" t="n"/>
-      <c r="H1" s="29" t="n"/>
-      <c r="I1" s="30" t="n"/>
-    </row>
-    <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>가입상품</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>◀ 현 재</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>현재 합산</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1" s="27">
-      <c r="A3" s="33" t="n"/>
-      <c r="C3" s="34" t="inlineStr">
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="34" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="37" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="35" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="38" t="n"/>
-    </row>
-    <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="I3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>가입년,월</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n"/>
-      <c r="D4" s="40" t="n"/>
-      <c r="E4" s="40" t="n"/>
-      <c r="F4" s="40" t="n"/>
-      <c r="G4" s="40" t="n"/>
-      <c r="H4" s="40" t="n"/>
-      <c r="I4" s="40" t="n"/>
-    </row>
-    <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>납입기간</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="40" t="n"/>
-      <c r="E5" s="40" t="n"/>
-      <c r="F5" s="40" t="n"/>
-      <c r="G5" s="40" t="n"/>
-      <c r="H5" s="40" t="n"/>
-      <c r="I5" s="40" t="n"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>총납입개월</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="40" t="n"/>
-      <c r="E6" s="40" t="n"/>
-      <c r="F6" s="40" t="n"/>
-      <c r="G6" s="40" t="n"/>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" s="27">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>▶  월 납입 보험료</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n"/>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="42" t="n"/>
-      <c r="F7" s="42" t="n"/>
-      <c r="G7" s="42" t="n"/>
-      <c r="H7" s="42" t="n"/>
-      <c r="I7" s="42">
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15">
         <f>SUM(C7:H7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="27">
-      <c r="A8" s="43" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="11.25" customHeight="1" s="27">
-      <c r="A9" s="44" t="inlineStr">
+    <row r="9" ht="11.25" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>일반사망</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="n"/>
-      <c r="H9" s="46" t="n"/>
-      <c r="I9" s="46">
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19">
         <f>SUM(C9:H9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="11.25" customHeight="1" s="27">
-      <c r="A10" s="44" t="inlineStr">
+    <row r="10" ht="11.25" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>질병사망</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="46" t="n"/>
-      <c r="H10" s="46" t="n"/>
-      <c r="I10" s="46">
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19">
         <f>SUM(C10:H10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="11.25" customHeight="1" s="27">
-      <c r="A11" s="44" t="inlineStr">
+    <row r="11" ht="11.25" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>암사망</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="46" t="n"/>
-      <c r="H11" s="46" t="n"/>
-      <c r="I11" s="46">
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19">
         <f>SUM(C11:H11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="11.25" customHeight="1" s="27">
-      <c r="A12" s="44" t="inlineStr">
+    <row r="12" ht="11.25" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>상해사망</t>
         </is>
       </c>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="46" t="n"/>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
-      <c r="H12" s="46" t="n"/>
-      <c r="I12" s="46">
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19">
         <f>SUM(C12:H12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="11.25" customHeight="1" s="27">
-      <c r="A13" s="44" t="inlineStr">
+    <row r="13" ht="11.25" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>장해</t>
         </is>
       </c>
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>상해후유장해(100%)</t>
         </is>
       </c>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="46" t="n"/>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n"/>
-      <c r="H13" s="46" t="n"/>
-      <c r="I13" s="46">
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19">
         <f>SUM(C13:H13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="11.25" customHeight="1" s="27">
-      <c r="A14" s="44" t="inlineStr">
+    <row r="14" ht="11.25" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>장해</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>상해후유장해(3%)</t>
         </is>
       </c>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
-      <c r="F14" s="46" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46">
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19">
         <f>SUM(C14:H14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="11.25" customHeight="1" s="27">
-      <c r="A15" s="44" t="inlineStr">
+    <row r="15" ht="11.25" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>장해</t>
         </is>
       </c>
-      <c r="B15" s="45" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>질병후유장해(100%)</t>
         </is>
       </c>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-      <c r="H15" s="46" t="n"/>
-      <c r="I15" s="46">
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19">
         <f>SUM(C15:H15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="27">
-      <c r="A16" s="43" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="11.25" customHeight="1" s="27">
-      <c r="A17" s="44" t="inlineStr">
+    <row r="17" ht="11.25" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>암진단</t>
         </is>
       </c>
-      <c r="B17" s="45" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>일반암 진단비</t>
         </is>
       </c>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n"/>
-      <c r="G17" s="46" t="n"/>
-      <c r="H17" s="46" t="n"/>
-      <c r="I17" s="46">
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19">
         <f>SUM(C17:H17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="11.25" customHeight="1" s="27">
-      <c r="A18" s="44" t="inlineStr">
+    <row r="18" ht="11.25" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>암진단</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>고액암 진단비</t>
         </is>
       </c>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
-      <c r="H18" s="46" t="n"/>
-      <c r="I18" s="46">
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19">
         <f>SUM(C18:H18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="11.25" customHeight="1" s="27">
-      <c r="A19" s="44" t="inlineStr">
+    <row r="19" ht="11.25" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>암진단</t>
         </is>
       </c>
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>소액암 진단비</t>
         </is>
       </c>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n"/>
-      <c r="H19" s="46" t="n"/>
-      <c r="I19" s="46">
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19">
         <f>SUM(C19:H19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="11.25" customHeight="1" s="27">
-      <c r="A20" s="44" t="inlineStr">
+    <row r="20" ht="11.25" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>말기진단</t>
         </is>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>말기간질환 진단비</t>
         </is>
       </c>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-      <c r="H20" s="46" t="n"/>
-      <c r="I20" s="46">
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19">
         <f>SUM(C20:H20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="11.25" customHeight="1" s="27">
-      <c r="A21" s="44" t="inlineStr">
+    <row r="21" ht="11.25" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>말기진단</t>
         </is>
       </c>
-      <c r="B21" s="45" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>말기폐질환 진단비</t>
         </is>
       </c>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-      <c r="H21" s="46" t="n"/>
-      <c r="I21" s="46">
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19">
         <f>SUM(C21:H21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="11.25" customHeight="1" s="27">
-      <c r="A22" s="44" t="inlineStr">
+    <row r="22" ht="11.25" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>말기진단</t>
         </is>
       </c>
-      <c r="B22" s="45" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>말기신부전증 진단비</t>
         </is>
       </c>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
-      <c r="H22" s="46" t="n"/>
-      <c r="I22" s="46">
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19">
         <f>SUM(C22:H22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="27">
-      <c r="A23" s="43" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="11.25" customHeight="1" s="27">
-      <c r="A24" s="44" t="inlineStr">
+    <row r="24" ht="11.25" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>상급병원암주요치료비(수술)</t>
         </is>
       </c>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
-      <c r="H24" s="46" t="n"/>
-      <c r="I24" s="46">
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="19">
         <f>SUM(C24:H24)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="11.25" customHeight="1" s="27">
-      <c r="A25" s="44" t="inlineStr">
+    <row r="25" ht="11.25" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>상급병원암주요치료비(방사선)</t>
         </is>
       </c>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-      <c r="H25" s="46" t="n"/>
-      <c r="I25" s="46">
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19">
         <f>SUM(C25:H25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="11.25" customHeight="1" s="27">
-      <c r="A26" s="44" t="inlineStr">
+    <row r="26" ht="11.25" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>상급병원암주요치료비(약물)</t>
         </is>
       </c>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n"/>
-      <c r="H26" s="46" t="n"/>
-      <c r="I26" s="46">
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="I26" s="19">
         <f>SUM(C26:H26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="11.25" customHeight="1" s="27">
-      <c r="A27" s="44" t="inlineStr">
+    <row r="27" ht="11.25" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>상급병원암주요치료비(복합)</t>
         </is>
       </c>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
-      <c r="H27" s="46" t="n"/>
-      <c r="I27" s="46">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19">
         <f>SUM(C27:H27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="11.25" customHeight="1" s="27">
-      <c r="A28" s="44" t="inlineStr">
+    <row r="28" ht="11.25" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>종합병원비급여암주요치료비</t>
         </is>
       </c>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
-      <c r="H28" s="46" t="n"/>
-      <c r="I28" s="46">
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="19" t="n"/>
+      <c r="I28" s="19">
         <f>SUM(C28:H28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="11.25" customHeight="1" s="27">
-      <c r="A29" s="44" t="inlineStr">
+    <row r="29" ht="11.25" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>항암방사선치료</t>
         </is>
       </c>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="n"/>
-      <c r="H29" s="46" t="n"/>
-      <c r="I29" s="46">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19">
         <f>SUM(C29:H29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="11.25" customHeight="1" s="27">
-      <c r="A30" s="44" t="inlineStr">
+    <row r="30" ht="11.25" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>항암세기조절방사선치료</t>
         </is>
       </c>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n"/>
-      <c r="H30" s="46" t="n"/>
-      <c r="I30" s="46">
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19">
         <f>SUM(C30:H30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="11.25" customHeight="1" s="27">
-      <c r="A31" s="44" t="inlineStr">
+    <row r="31" ht="11.25" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>항암양성자방사선치료</t>
         </is>
       </c>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="46" t="n"/>
-      <c r="H31" s="46" t="n"/>
-      <c r="I31" s="46">
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19">
         <f>SUM(C31:H31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="11.25" customHeight="1" s="27">
-      <c r="A32" s="44" t="inlineStr">
+    <row r="32" ht="11.25" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B32" s="45" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>항암약물치료</t>
         </is>
       </c>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="46" t="n"/>
-      <c r="H32" s="46" t="n"/>
-      <c r="I32" s="46">
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19">
         <f>SUM(C32:H32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="11.25" customHeight="1" s="27">
-      <c r="A33" s="44" t="inlineStr">
+    <row r="33" ht="11.25" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>표적항암약물 허가치료</t>
         </is>
       </c>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n"/>
-      <c r="H33" s="46" t="n"/>
-      <c r="I33" s="46">
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19">
         <f>SUM(C33:H33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="11.25" customHeight="1" s="27">
-      <c r="A34" s="44" t="inlineStr">
+    <row r="34" ht="11.25" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B34" s="47" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>CAR-T 항암약물 허가치료</t>
         </is>
       </c>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="46" t="n"/>
-      <c r="H34" s="46" t="n"/>
-      <c r="I34" s="46">
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="19" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="19">
         <f>SUM(C34:H34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="11.25" customHeight="1" s="27">
-      <c r="A35" s="44" t="inlineStr">
+    <row r="35" ht="11.25" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>항암호르몬약물 허가치료</t>
         </is>
       </c>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
-      <c r="H35" s="46" t="n"/>
-      <c r="I35" s="46">
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19">
         <f>SUM(C35:H35)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="11.25" customHeight="1" s="27">
-      <c r="A36" s="44" t="inlineStr">
+    <row r="36" ht="11.25" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B36" s="45" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>항암중입자방사선치료</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
-      <c r="I36" s="46">
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19">
         <f>SUM(C36:H36)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="11.25" customHeight="1" s="27">
-      <c r="A37" s="44" t="inlineStr">
+    <row r="37" ht="11.25" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>암치료</t>
         </is>
       </c>
-      <c r="B37" s="45" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>암직접치료상급종합병원통원</t>
         </is>
       </c>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
-      <c r="E37" s="46" t="n"/>
-      <c r="F37" s="46" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="H37" s="46" t="n"/>
-      <c r="I37" s="46">
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="19">
         <f>SUM(C37:H37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="27">
-      <c r="A38" s="43" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="11.25" customHeight="1" s="27">
-      <c r="A39" s="44" t="inlineStr">
+    <row r="39" ht="11.25" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B39" s="45" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>뇌혈관질환 진단</t>
         </is>
       </c>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="46" t="n"/>
-      <c r="G39" s="46" t="n"/>
-      <c r="H39" s="46" t="n"/>
-      <c r="I39" s="46">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19">
         <f>SUM(C39:H39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="11.25" customHeight="1" s="27">
-      <c r="A40" s="44" t="inlineStr">
+    <row r="40" ht="11.25" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B40" s="45" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>뇌경색증진단</t>
         </is>
       </c>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="46" t="n"/>
-      <c r="G40" s="46" t="n"/>
-      <c r="H40" s="46" t="n"/>
-      <c r="I40" s="46">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="19" t="n"/>
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="19">
         <f>SUM(C40:H40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="11.25" customHeight="1" s="27">
-      <c r="A41" s="44" t="inlineStr">
+    <row r="41" ht="11.25" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B41" s="45" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>뇌출혈 진단</t>
         </is>
       </c>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
-      <c r="E41" s="46" t="n"/>
-      <c r="F41" s="46" t="n"/>
-      <c r="G41" s="46" t="n"/>
-      <c r="H41" s="46" t="n"/>
-      <c r="I41" s="46">
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="19" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="19" t="n"/>
+      <c r="H41" s="19" t="n"/>
+      <c r="I41" s="19">
         <f>SUM(C41:H41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="11.25" customHeight="1" s="27">
-      <c r="A42" s="44" t="inlineStr">
+    <row r="42" ht="11.25" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B42" s="45" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>급성심근경색 진단</t>
         </is>
       </c>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n"/>
-      <c r="H42" s="46" t="n"/>
-      <c r="I42" s="46">
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19">
         <f>SUM(C42:H42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="11.25" customHeight="1" s="27">
-      <c r="A43" s="44" t="inlineStr">
+    <row r="43" ht="11.25" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B43" s="45" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>허혈심장질환 진단</t>
         </is>
       </c>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
-      <c r="E43" s="46" t="n"/>
-      <c r="F43" s="46" t="n"/>
-      <c r="G43" s="46" t="n"/>
-      <c r="H43" s="46" t="n"/>
-      <c r="I43" s="46">
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19">
         <f>SUM(C43:H43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="11.25" customHeight="1" s="27">
-      <c r="A44" s="44" t="inlineStr">
+    <row r="44" ht="11.25" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B44" s="45" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>순환계질환 수술 (연1회)</t>
         </is>
       </c>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
-      <c r="E44" s="46" t="n"/>
-      <c r="F44" s="46" t="n"/>
-      <c r="G44" s="46" t="n"/>
-      <c r="H44" s="46" t="n"/>
-      <c r="I44" s="46">
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="19">
         <f>SUM(C44:H44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="11.25" customHeight="1" s="27">
-      <c r="A45" s="44" t="inlineStr">
+    <row r="45" ht="11.25" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B45" s="45" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>순환계질환 혈전 용해 (연1회)</t>
         </is>
       </c>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n"/>
-      <c r="H45" s="46" t="n"/>
-      <c r="I45" s="46">
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19">
         <f>SUM(C45:H45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="11.25" customHeight="1" s="27">
-      <c r="A46" s="44" t="inlineStr">
+    <row r="46" ht="11.25" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B46" s="45" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>순환계질환 혈전제거 (연1회)</t>
         </is>
       </c>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
-      <c r="E46" s="46" t="n"/>
-      <c r="F46" s="46" t="n"/>
-      <c r="G46" s="46" t="n"/>
-      <c r="H46" s="46" t="n"/>
-      <c r="I46" s="46">
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19">
         <f>SUM(C46:H46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="11.25" customHeight="1" s="27">
-      <c r="A47" s="44" t="inlineStr">
+    <row r="47" ht="11.25" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>순환계질환 복합치료 (연1회)</t>
         </is>
       </c>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
-      <c r="E47" s="46" t="n"/>
-      <c r="F47" s="46" t="n"/>
-      <c r="G47" s="46" t="n"/>
-      <c r="H47" s="46" t="n"/>
-      <c r="I47" s="46">
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="19" t="n"/>
+      <c r="G47" s="19" t="n"/>
+      <c r="H47" s="19" t="n"/>
+      <c r="I47" s="19">
         <f>SUM(C47:H47)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="11.25" customHeight="1" s="27">
-      <c r="A48" s="44" t="inlineStr">
+    <row r="48" ht="11.25" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>심뇌</t>
         </is>
       </c>
-      <c r="B48" s="45" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>순환계질환 중환자실 (연1회)</t>
         </is>
       </c>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
-      <c r="E48" s="46" t="n"/>
-      <c r="F48" s="46" t="n"/>
-      <c r="G48" s="46" t="n"/>
-      <c r="H48" s="46" t="n"/>
-      <c r="I48" s="46">
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="19">
         <f>SUM(C48:H48)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="27">
-      <c r="A49" s="43" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="11.25" customHeight="1" s="27">
-      <c r="A50" s="44" t="inlineStr">
+    <row r="50" ht="11.25" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B50" s="45" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>질병 수술비</t>
         </is>
       </c>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="46" t="n"/>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="46" t="n"/>
-      <c r="I50" s="46">
+      <c r="C50" s="19" t="n"/>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="19" t="n"/>
+      <c r="G50" s="19" t="n"/>
+      <c r="H50" s="19" t="n"/>
+      <c r="I50" s="19">
         <f>SUM(C50:H50)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="11.25" customHeight="1" s="27">
-      <c r="A51" s="44" t="inlineStr">
+    <row r="51" ht="11.25" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B51" s="45" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>상급종합병원질병수술</t>
         </is>
       </c>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
-      <c r="E51" s="46" t="n"/>
-      <c r="F51" s="46" t="n"/>
-      <c r="G51" s="46" t="n"/>
-      <c r="H51" s="46" t="n"/>
-      <c r="I51" s="46">
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
+      <c r="I51" s="19">
         <f>SUM(C51:H51)</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="11.25" customHeight="1" s="27">
-      <c r="A52" s="44" t="inlineStr">
+    <row r="52" ht="11.25" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B52" s="45" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>재해 수술비</t>
         </is>
       </c>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
-      <c r="E52" s="46" t="n"/>
-      <c r="F52" s="46" t="n"/>
-      <c r="G52" s="46" t="n"/>
-      <c r="H52" s="46" t="n"/>
-      <c r="I52" s="46">
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+      <c r="H52" s="19" t="n"/>
+      <c r="I52" s="19">
         <f>SUM(C52:H52)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="11.25" customHeight="1" s="27">
-      <c r="A53" s="44" t="inlineStr">
+    <row r="53" ht="11.25" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B53" s="45" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>암 수술비</t>
         </is>
       </c>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
-      <c r="E53" s="46" t="n"/>
-      <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n"/>
-      <c r="H53" s="46" t="n"/>
-      <c r="I53" s="46">
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+      <c r="H53" s="19" t="n"/>
+      <c r="I53" s="19">
         <f>SUM(C53:H53)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="11.25" customHeight="1" s="27">
-      <c r="A54" s="44" t="inlineStr">
+    <row r="54" ht="11.25" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B54" s="45" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>뇌출혈 수술</t>
         </is>
       </c>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
-      <c r="E54" s="46" t="n"/>
-      <c r="F54" s="46" t="n"/>
-      <c r="G54" s="46" t="n"/>
-      <c r="H54" s="46" t="n"/>
-      <c r="I54" s="46">
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19">
         <f>SUM(C54:H54)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="11.25" customHeight="1" s="27">
-      <c r="A55" s="44" t="inlineStr">
+    <row r="55" ht="11.25" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B55" s="45" t="inlineStr">
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>급성심근경색 수술</t>
         </is>
       </c>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
-      <c r="E55" s="46" t="n"/>
-      <c r="F55" s="46" t="n"/>
-      <c r="G55" s="46" t="n"/>
-      <c r="H55" s="46" t="n"/>
-      <c r="I55" s="46">
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+      <c r="H55" s="19" t="n"/>
+      <c r="I55" s="19">
         <f>SUM(C55:H55)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="11.25" customHeight="1" s="27">
-      <c r="A56" s="44" t="inlineStr">
+    <row r="56" ht="11.25" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B56" s="47" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>1-5종 수술 1종</t>
         </is>
       </c>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
-      <c r="E56" s="46" t="n"/>
-      <c r="F56" s="46" t="n"/>
-      <c r="G56" s="46" t="n"/>
-      <c r="H56" s="46" t="n"/>
-      <c r="I56" s="46">
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
+      <c r="H56" s="19" t="n"/>
+      <c r="I56" s="19">
         <f>SUM(C56:H56)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="11.25" customHeight="1" s="27">
-      <c r="A57" s="44" t="inlineStr">
+    <row r="57" ht="11.25" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B57" s="47" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>1-5종 수술 2종</t>
         </is>
       </c>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
-      <c r="E57" s="46" t="n"/>
-      <c r="F57" s="46" t="n"/>
-      <c r="G57" s="46" t="n"/>
-      <c r="H57" s="46" t="n"/>
-      <c r="I57" s="46">
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
+      <c r="G57" s="19" t="n"/>
+      <c r="H57" s="19" t="n"/>
+      <c r="I57" s="19">
         <f>SUM(C57:H57)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="11.25" customHeight="1" s="27">
-      <c r="A58" s="44" t="inlineStr">
+    <row r="58" ht="11.25" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B58" s="47" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>1-5종 수술 3종</t>
         </is>
       </c>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
-      <c r="E58" s="46" t="n"/>
-      <c r="F58" s="46" t="n"/>
-      <c r="G58" s="46" t="n"/>
-      <c r="H58" s="46" t="n"/>
-      <c r="I58" s="46">
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n"/>
+      <c r="G58" s="19" t="n"/>
+      <c r="H58" s="19" t="n"/>
+      <c r="I58" s="19">
         <f>SUM(C58:H58)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="11.25" customHeight="1" s="27">
-      <c r="A59" s="44" t="inlineStr">
+    <row r="59" ht="11.25" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B59" s="47" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>1-5종 수술 4종</t>
         </is>
       </c>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
-      <c r="E59" s="46" t="n"/>
-      <c r="F59" s="46" t="n"/>
-      <c r="G59" s="46" t="n"/>
-      <c r="H59" s="46" t="n"/>
-      <c r="I59" s="46">
+      <c r="C59" s="19" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="19" t="n"/>
+      <c r="G59" s="19" t="n"/>
+      <c r="H59" s="19" t="n"/>
+      <c r="I59" s="19">
         <f>SUM(C59:H59)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="11.25" customHeight="1" s="27">
-      <c r="A60" s="44" t="inlineStr">
+    <row r="60" ht="11.25" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B60" s="47" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>1-5종 수술 5종</t>
         </is>
       </c>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="46" t="n"/>
-      <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="46">
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="19" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="19">
         <f>SUM(C60:H60)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="27">
-      <c r="A61" s="43" t="inlineStr">
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="11.25" customHeight="1" s="27">
-      <c r="A62" s="48" t="inlineStr">
+    <row r="62" ht="11.25" customHeight="1">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B62" s="49" t="inlineStr">
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>질병 입원 실비</t>
         </is>
       </c>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
-      <c r="E62" s="46" t="n"/>
-      <c r="F62" s="46" t="n"/>
-      <c r="G62" s="46" t="n"/>
-      <c r="H62" s="46" t="n"/>
-      <c r="I62" s="46">
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19">
         <f>SUM(C62:H62)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="11.25" customHeight="1" s="27">
-      <c r="A63" s="48" t="inlineStr">
+    <row r="63" ht="11.25" customHeight="1">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B63" s="49" t="inlineStr">
+      <c r="B63" s="22" t="inlineStr">
         <is>
           <t>재해/상해 입원 실비</t>
         </is>
       </c>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
-      <c r="E63" s="46" t="n"/>
-      <c r="F63" s="46" t="n"/>
-      <c r="G63" s="46" t="n"/>
-      <c r="H63" s="46" t="n"/>
-      <c r="I63" s="46">
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="19" t="n"/>
+      <c r="I63" s="19">
         <f>SUM(C63:H63)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="11.25" customHeight="1" s="27">
-      <c r="A64" s="48" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="B64" s="49" t="inlineStr">
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>질병 통원 실비</t>
         </is>
       </c>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
-      <c r="E64" s="46" t="n"/>
-      <c r="F64" s="46" t="n"/>
-      <c r="G64" s="46" t="n"/>
-      <c r="H64" s="46" t="n"/>
-      <c r="I64" s="46" t="n"/>
-    </row>
-    <row r="65" ht="11.25" customHeight="1" s="27">
-      <c r="A65" s="48" t="inlineStr">
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="B65" s="49" t="inlineStr">
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>재해/상해 통원 실비</t>
         </is>
       </c>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
-      <c r="E65" s="46" t="n"/>
-      <c r="F65" s="46" t="n"/>
-      <c r="G65" s="46" t="n"/>
-      <c r="H65" s="46" t="n"/>
-      <c r="I65" s="46" t="n"/>
-    </row>
-    <row r="66" ht="11.25" customHeight="1" s="27">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="C65" s="19" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="19" t="n"/>
+      <c r="G65" s="19" t="n"/>
+      <c r="H65" s="19" t="n"/>
+      <c r="I65" s="19" t="n"/>
+    </row>
+    <row r="66" ht="11.25" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B66" s="45" t="inlineStr">
+      <c r="B66" s="18" t="inlineStr">
         <is>
           <t>질병입원 일당</t>
         </is>
       </c>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="46" t="n"/>
-      <c r="G66" s="46" t="n"/>
-      <c r="H66" s="46" t="n"/>
-      <c r="I66" s="46">
+      <c r="C66" s="19" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="19" t="n"/>
+      <c r="I66" s="19">
         <f>SUM(C64:H64)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="11.25" customHeight="1" s="27">
-      <c r="A67" s="44" t="inlineStr">
+    <row r="67" ht="11.25" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B67" s="45" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>재해입원 일당</t>
         </is>
       </c>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="46" t="n"/>
-      <c r="F67" s="46" t="n"/>
-      <c r="G67" s="46" t="n"/>
-      <c r="H67" s="46" t="n"/>
-      <c r="I67" s="46">
+      <c r="C67" s="19" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="19" t="n"/>
+      <c r="G67" s="19" t="n"/>
+      <c r="H67" s="19" t="n"/>
+      <c r="I67" s="19">
         <f>SUM(C65:H65)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="11.25" customHeight="1" s="27">
-      <c r="A68" s="44" t="inlineStr">
+    <row r="68" ht="11.25" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B68" s="45" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>암입원 일당</t>
         </is>
       </c>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
-      <c r="E68" s="46" t="n"/>
-      <c r="F68" s="46" t="n"/>
-      <c r="G68" s="46" t="n"/>
-      <c r="H68" s="46" t="n"/>
-      <c r="I68" s="46">
+      <c r="C68" s="19" t="n"/>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="19" t="n"/>
+      <c r="G68" s="19" t="n"/>
+      <c r="H68" s="19" t="n"/>
+      <c r="I68" s="19">
         <f>SUM(C66:H66)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="11.25" customHeight="1" s="27">
-      <c r="A69" s="44" t="inlineStr">
+    <row r="69" ht="11.25" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B69" s="45" t="inlineStr">
+      <c r="B69" s="18" t="inlineStr">
         <is>
           <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
-      <c r="C69" s="46" t="n"/>
-      <c r="D69" s="46" t="n"/>
-      <c r="E69" s="46" t="n"/>
-      <c r="F69" s="46" t="n"/>
-      <c r="G69" s="46" t="n"/>
-      <c r="H69" s="46" t="n"/>
-      <c r="I69" s="46">
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+      <c r="H69" s="19" t="n"/>
+      <c r="I69" s="19">
         <f>SUM(C67:H67)</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="11.25" customHeight="1" s="27">
-      <c r="A70" s="44" t="inlineStr">
+    <row r="70" ht="11.25" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B70" s="45" t="inlineStr">
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
-      <c r="E70" s="46" t="n"/>
-      <c r="F70" s="46" t="n"/>
-      <c r="G70" s="46" t="n"/>
-      <c r="H70" s="46" t="n"/>
-      <c r="I70" s="46">
+      <c r="C70" s="19" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="19" t="n"/>
+      <c r="G70" s="19" t="n"/>
+      <c r="H70" s="19" t="n"/>
+      <c r="I70" s="19">
         <f>SUM(C68:H68)</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="11.25" customHeight="1" s="27">
-      <c r="A71" s="44" t="inlineStr">
+    <row r="71" ht="11.25" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B71" s="45" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
-      <c r="C71" s="46" t="n"/>
-      <c r="D71" s="46" t="n"/>
-      <c r="E71" s="46" t="n"/>
-      <c r="F71" s="46" t="n"/>
-      <c r="G71" s="46" t="n"/>
-      <c r="H71" s="46" t="n"/>
-      <c r="I71" s="46">
+      <c r="C71" s="19" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="19" t="n"/>
+      <c r="G71" s="19" t="n"/>
+      <c r="H71" s="19" t="n"/>
+      <c r="I71" s="19">
         <f>SUM(C69:H69)</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="11.25" customHeight="1" s="27">
-      <c r="A72" s="44" t="inlineStr">
+    <row r="72" ht="11.25" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B72" s="45" t="inlineStr">
+      <c r="B72" s="18" t="inlineStr">
         <is>
           <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
-      <c r="F72" s="46" t="n"/>
-      <c r="G72" s="46" t="n"/>
-      <c r="H72" s="46" t="n"/>
-      <c r="I72" s="46">
+      <c r="C72" s="19" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="19" t="n"/>
+      <c r="G72" s="19" t="n"/>
+      <c r="H72" s="19" t="n"/>
+      <c r="I72" s="19">
         <f>SUM(C70:H70)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="27">
-      <c r="A73" s="44" t="inlineStr">
+    <row r="73" ht="11.25" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B73" s="45" t="inlineStr">
+      <c r="B73" s="18" t="inlineStr">
         <is>
           <t>간병인사용일당 (질병)</t>
         </is>
       </c>
-      <c r="C73" s="46" t="n"/>
-      <c r="D73" s="46" t="n"/>
-      <c r="E73" s="46" t="n"/>
-      <c r="F73" s="46" t="n"/>
-      <c r="G73" s="46" t="n"/>
-      <c r="H73" s="46" t="n"/>
-      <c r="I73" s="46" t="n"/>
-    </row>
-    <row r="74" ht="11.25" customHeight="1" s="27">
-      <c r="A74" s="44" t="inlineStr">
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="19" t="n"/>
+      <c r="H73" s="19" t="n"/>
+      <c r="I73" s="19">
+        <f>SUM(C71:H71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="11.25" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="B74" s="45" t="inlineStr">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>간병인사용일당 (상해)</t>
         </is>
       </c>
-      <c r="C74" s="46" t="n"/>
-      <c r="D74" s="46" t="n"/>
-      <c r="E74" s="46" t="n"/>
-      <c r="F74" s="46" t="n"/>
-      <c r="G74" s="46" t="n"/>
-      <c r="H74" s="46" t="n"/>
-      <c r="I74" s="46">
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="19" t="n"/>
+      <c r="H74" s="19" t="n"/>
+      <c r="I74" s="19">
         <f>SUM(C72:H72)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="27">
-      <c r="A75" s="43" t="inlineStr">
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="12.75" customHeight="1" s="27">
-      <c r="A76" s="44" t="inlineStr">
+    <row r="76" ht="11.25" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B76" s="45" t="inlineStr">
+      <c r="B76" s="18" t="inlineStr">
         <is>
           <t>골절진단비</t>
         </is>
       </c>
-      <c r="C76" s="46" t="n"/>
-      <c r="D76" s="46" t="n"/>
-      <c r="E76" s="46" t="n"/>
-      <c r="F76" s="46" t="n"/>
-      <c r="G76" s="46" t="n"/>
-      <c r="H76" s="46" t="n"/>
-      <c r="I76" s="46" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="27">
-      <c r="A77" s="43" t="inlineStr">
+      <c r="C76" s="19" t="n"/>
+      <c r="D76" s="19" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="19" t="n"/>
+      <c r="G76" s="19" t="n"/>
+      <c r="H76" s="19" t="n"/>
+      <c r="I76" s="19">
+        <f>SUM(C74:H74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="3" customHeight="1" s="27">
-      <c r="A78" s="50" t="inlineStr">
+    <row r="78" ht="12.75" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="27">
-      <c r="A79" s="57" t="inlineStr">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="B79" s="58" t="n"/>
-      <c r="C79" s="58" t="n"/>
-      <c r="D79" s="58" t="n"/>
-      <c r="E79" s="58" t="n"/>
-      <c r="F79" s="58" t="n"/>
-      <c r="G79" s="58" t="n"/>
-      <c r="H79" s="58" t="n"/>
-      <c r="I79" s="59" t="n"/>
-    </row>
-    <row r="80" ht="19.5" customHeight="1" s="27"/>
-    <row r="81" ht="19.5" customHeight="1" s="27">
-      <c r="A81" s="52" t="inlineStr">
+      <c r="C79" s="15">
+        <f>C7*C6</f>
+        <v/>
+      </c>
+      <c r="D79" s="15">
+        <f>D7*D6</f>
+        <v/>
+      </c>
+      <c r="E79" s="15">
+        <f>E7*E6</f>
+        <v/>
+      </c>
+      <c r="F79" s="15">
+        <f>F7*F6</f>
+        <v/>
+      </c>
+      <c r="G79" s="15">
+        <f>G7*G6</f>
+        <v/>
+      </c>
+      <c r="H79" s="15">
+        <f>H7*H6</f>
+        <v/>
+      </c>
+      <c r="I79" s="15">
+        <f>I7*I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="3" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="25" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="19.5" customHeight="1" s="27">
-      <c r="A82" s="53" t="inlineStr">
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>상품1</t>
         </is>
       </c>
-      <c r="B82" s="54" t="n"/>
-      <c r="C82" s="55" t="n"/>
-      <c r="D82" s="56" t="n"/>
-      <c r="E82" s="56" t="n"/>
-      <c r="F82" s="56" t="n"/>
-      <c r="G82" s="56" t="n"/>
-      <c r="H82" s="56" t="n"/>
-      <c r="I82" s="54" t="n"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1" s="27">
-      <c r="A83" s="53" t="inlineStr">
+      <c r="B82" s="27" t="n"/>
+      <c r="C82" s="28" t="n"/>
+      <c r="D82" s="29" t="n"/>
+      <c r="E82" s="29" t="n"/>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="29" t="n"/>
+      <c r="H82" s="29" t="n"/>
+      <c r="I82" s="27" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>상품2</t>
         </is>
       </c>
-      <c r="B83" s="54" t="n"/>
-      <c r="C83" s="55" t="n"/>
-      <c r="D83" s="56" t="n"/>
-      <c r="E83" s="56" t="n"/>
-      <c r="F83" s="56" t="n"/>
-      <c r="G83" s="56" t="n"/>
-      <c r="H83" s="56" t="n"/>
-      <c r="I83" s="54" t="n"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1" s="27">
-      <c r="A84" s="53" t="inlineStr">
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="28" t="n"/>
+      <c r="D83" s="29" t="n"/>
+      <c r="E83" s="29" t="n"/>
+      <c r="F83" s="29" t="n"/>
+      <c r="G83" s="29" t="n"/>
+      <c r="H83" s="29" t="n"/>
+      <c r="I83" s="27" t="n"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>상품3</t>
         </is>
       </c>
-      <c r="B84" s="54" t="n"/>
-      <c r="C84" s="55" t="n"/>
-      <c r="D84" s="56" t="n"/>
-      <c r="E84" s="56" t="n"/>
-      <c r="F84" s="56" t="n"/>
-      <c r="G84" s="56" t="n"/>
-      <c r="H84" s="56" t="n"/>
-      <c r="I84" s="54" t="n"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1" s="27">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="B84" s="27" t="n"/>
+      <c r="C84" s="28" t="n"/>
+      <c r="D84" s="29" t="n"/>
+      <c r="E84" s="29" t="n"/>
+      <c r="F84" s="29" t="n"/>
+      <c r="G84" s="29" t="n"/>
+      <c r="H84" s="29" t="n"/>
+      <c r="I84" s="27" t="n"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>상품4</t>
         </is>
       </c>
-      <c r="B85" s="54" t="n"/>
-      <c r="C85" s="55" t="n"/>
-      <c r="D85" s="56" t="n"/>
-      <c r="E85" s="56" t="n"/>
-      <c r="F85" s="56" t="n"/>
-      <c r="G85" s="56" t="n"/>
-      <c r="H85" s="56" t="n"/>
-      <c r="I85" s="54" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="B85" s="27" t="n"/>
+      <c r="C85" s="28" t="n"/>
+      <c r="D85" s="29" t="n"/>
+      <c r="E85" s="29" t="n"/>
+      <c r="F85" s="29" t="n"/>
+      <c r="G85" s="29" t="n"/>
+      <c r="H85" s="29" t="n"/>
+      <c r="I85" s="27" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>상품5</t>
         </is>
       </c>
-      <c r="B86" s="54" t="n"/>
-      <c r="C86" s="55" t="n"/>
-      <c r="D86" s="56" t="n"/>
-      <c r="E86" s="56" t="n"/>
-      <c r="F86" s="56" t="n"/>
-      <c r="G86" s="56" t="n"/>
-      <c r="H86" s="56" t="n"/>
-      <c r="I86" s="54" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="53" t="inlineStr">
+      <c r="B86" s="27" t="n"/>
+      <c r="C86" s="28" t="n"/>
+      <c r="D86" s="29" t="n"/>
+      <c r="E86" s="29" t="n"/>
+      <c r="F86" s="29" t="n"/>
+      <c r="G86" s="29" t="n"/>
+      <c r="H86" s="29" t="n"/>
+      <c r="I86" s="27" t="n"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>상품6</t>
         </is>
       </c>
-      <c r="B87" s="54" t="n"/>
-      <c r="C87" s="55" t="n"/>
-      <c r="D87" s="56" t="n"/>
-      <c r="E87" s="56" t="n"/>
-      <c r="F87" s="56" t="n"/>
-      <c r="G87" s="56" t="n"/>
-      <c r="H87" s="56" t="n"/>
-      <c r="I87" s="54" t="n"/>
+      <c r="B87" s="27" t="n"/>
+      <c r="C87" s="28" t="n"/>
+      <c r="D87" s="29" t="n"/>
+      <c r="E87" s="29" t="n"/>
+      <c r="F87" s="29" t="n"/>
+      <c r="G87" s="29" t="n"/>
+      <c r="H87" s="29" t="n"/>
+      <c r="I87" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:I75"/>
     <mergeCell ref="C82:I82"/>
-    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="A79:B79"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A87:B87"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C87:I87"/>
     <mergeCell ref="C83:I83"/>
+    <mergeCell ref="A84:B84"/>
     <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="C86:I86"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A86:B86"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C85:I85"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C84:I84"/>
     <mergeCell ref="A49:I49"/>
-    <mergeCell ref="C80:I80"/>
-    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A61:I61"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="8" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>재해/상해 입원 실비</t>
+          <t>재해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="19" t="n"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>재해/상해 통원 실비</t>
+          <t>재해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="19" t="n"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +95,14 @@
       <color rgb="FF1B2A4A"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -173,6 +179,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDE7"/>
         <bgColor rgb="FFFFF8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B2A4A"/>
+        <bgColor rgb="001B2A4A"/>
       </patternFill>
     </fill>
   </fills>
@@ -306,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -387,6 +399,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -898,7 +913,7 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1059,7 +1074,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1198,9 +1213,9 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>▶  암 치료비</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1528,7 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -1740,7 +1755,7 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -1989,7 +2004,7 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2276,7 +2291,7 @@
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2305,7 +2320,7 @@
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -102,7 +102,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +185,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B2A4A"/>
         <bgColor rgb="001B2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -318,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,6 +406,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,7 +922,7 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1074,7 +1083,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1213,7 +1222,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>▶  암 치료비</t>
         </is>
@@ -1227,7 +1236,7 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(수술)</t>
+          <t>상급병원암주요치료비(수술) (연 1회)</t>
         </is>
       </c>
       <c r="C24" s="19" t="n"/>
@@ -1249,7 +1258,7 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(방사선) (연 1회)</t>
         </is>
       </c>
       <c r="C25" s="19" t="n"/>
@@ -1271,7 +1280,7 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(약물) (연 1회)</t>
         </is>
       </c>
       <c r="C26" s="19" t="n"/>
@@ -1293,7 +1302,7 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>상급병원암주요치료비(복합) (연 1회)</t>
         </is>
       </c>
       <c r="C27" s="19" t="n"/>
@@ -1315,7 +1324,7 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>종합병원비급여암주요치료비 (연 1회)</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
@@ -1528,7 +1537,7 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -1755,7 +1764,7 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -2004,7 +2013,7 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2291,7 +2300,7 @@
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="30" t="inlineStr">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2320,7 +2329,7 @@
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="30" t="inlineStr">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
@@ -2370,7 +2379,7 @@
     </row>
     <row r="80" ht="3" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="25" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -102,7 +102,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -191,6 +191,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF4B80"/>
+        <bgColor rgb="00BF4B80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E8B57"/>
+        <bgColor rgb="002E8B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D27519"/>
+        <bgColor rgb="00D27519"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B7E91"/>
+        <bgColor rgb="005B7E91"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,6 +451,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -922,7 +985,7 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1083,7 +1146,7 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1222,7 +1285,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>▶  암 치료비</t>
         </is>
@@ -1537,7 +1600,7 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -1764,7 +1827,7 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -2013,7 +2076,7 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2300,7 +2363,7 @@
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="31" t="inlineStr">
+      <c r="A75" s="38" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2379,7 +2442,7 @@
     </row>
     <row r="80" ht="3" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="31" t="inlineStr">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +101,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +244,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="005B7E91"/>
         <bgColor rgb="005B7E91"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B4C7E"/>
+        <bgColor rgb="002B4C7E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B6FA0"/>
+        <bgColor rgb="003B6FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A7D9A"/>
+        <bgColor rgb="005A7D9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B3FA0"/>
+        <bgColor rgb="006B3FA0"/>
       </patternFill>
     </fill>
   </fills>
@@ -366,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -473,6 +508,36 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -854,7 +919,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>○○○님 (남자, 00세) · 보장 분석표</t>
         </is>
@@ -869,117 +934,117 @@
       <c r="I1" s="3" t="n"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>가입상품</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="40" t="inlineStr">
         <is>
           <t>◀ 현 재</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="41" t="inlineStr">
         <is>
           <t>현재 합산</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="6" t="n"/>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="A3" s="42" t="n"/>
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="43" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="43" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="43" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="43" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="43" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="11" t="n"/>
+      <c r="I3" s="44" t="n"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>가입년,월</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>납입기간</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>총납입개월</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
+      <c r="E6" s="46" t="n"/>
+      <c r="F6" s="46" t="n"/>
+      <c r="G6" s="46" t="n"/>
+      <c r="H6" s="46" t="n"/>
+      <c r="I6" s="46" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>▶  월 납입 보험료</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15">
+      <c r="C7" s="48" t="n"/>
+      <c r="D7" s="48" t="n"/>
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="48" t="n"/>
+      <c r="G7" s="48" t="n"/>
+      <c r="H7" s="48" t="n"/>
+      <c r="I7" s="48">
         <f>SUM(C7:H7)</f>
         <v/>
       </c>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +112,25 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001B2A4A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="001B2A4A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -268,6 +285,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="006B3FA0"/>
         <bgColor rgb="006B3FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E74C3C"/>
+        <bgColor rgb="00E74C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67E22"/>
+        <bgColor rgb="00E67E22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1C40F"/>
+        <bgColor rgb="00F1C40F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0027AE60"/>
+        <bgColor rgb="0027AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980B9"/>
+        <bgColor rgb="002980B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008E44AD"/>
+        <bgColor rgb="008E44AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FA"/>
+        <bgColor rgb="00F0F4FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -538,6 +597,27 @@
     </xf>
     <xf numFmtId="3" fontId="11" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,37 +1032,37 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="42" t="n"/>
-      <c r="C3" s="43" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="43" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="43" t="inlineStr">
+      <c r="E3" s="51" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="43" t="inlineStr">
+      <c r="F3" s="52" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="43" t="inlineStr">
+      <c r="G3" s="53" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="43" t="inlineStr">
+      <c r="H3" s="54" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
@@ -996,13 +1076,13 @@
           <t>가입년,월</t>
         </is>
       </c>
-      <c r="C4" s="46" t="n"/>
-      <c r="D4" s="46" t="n"/>
-      <c r="E4" s="46" t="n"/>
-      <c r="F4" s="46" t="n"/>
-      <c r="G4" s="46" t="n"/>
-      <c r="H4" s="46" t="n"/>
-      <c r="I4" s="46" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="45" t="inlineStr">
@@ -1010,13 +1090,13 @@
           <t>납입기간</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="46" t="n"/>
-      <c r="F5" s="46" t="n"/>
-      <c r="G5" s="46" t="n"/>
-      <c r="H5" s="46" t="n"/>
-      <c r="I5" s="46" t="n"/>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="45" t="inlineStr">
@@ -1024,13 +1104,13 @@
           <t>총납입개월</t>
         </is>
       </c>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="46" t="n"/>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="46" t="n"/>
-      <c r="I6" s="46" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="55" t="n"/>
+      <c r="E6" s="55" t="n"/>
+      <c r="F6" s="55" t="n"/>
+      <c r="G6" s="55" t="n"/>
+      <c r="H6" s="55" t="n"/>
+      <c r="I6" s="55" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="47" t="inlineStr">

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -327,6 +327,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F0F4FA"/>
         <bgColor rgb="00F0F4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1948A"/>
+        <bgColor rgb="00F1948A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0B27A"/>
+        <bgColor rgb="00F0B27A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9E79F"/>
+        <bgColor rgb="00F9E79F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082E0AA"/>
+        <bgColor rgb="0082E0AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085C1E9"/>
+        <bgColor rgb="0085C1E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C39BD3"/>
+        <bgColor rgb="00C39BD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -460,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -617,6 +653,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1032,37 +1086,37 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="42" t="n"/>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="56" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="50" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="51" t="inlineStr">
+      <c r="E3" s="58" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="52" t="inlineStr">
+      <c r="F3" s="59" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="53" t="inlineStr">
+      <c r="G3" s="60" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="54" t="inlineStr">
+      <c r="H3" s="61" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="46">
     <fill>
       <patternFill/>
     </fill>
@@ -363,6 +363,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C39BD3"/>
         <bgColor rgb="00C39BD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8D0"/>
+        <bgColor rgb="00FDE8D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FACDA6"/>
+        <bgColor rgb="00FACDA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7B27A"/>
+        <bgColor rgb="00F7B27A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4974E"/>
+        <bgColor rgb="00F4974E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F07D24"/>
+        <bgColor rgb="00F07D24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D96A10"/>
+        <bgColor rgb="00D96A10"/>
       </patternFill>
     </fill>
   </fills>
@@ -496,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -671,6 +707,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="43" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="44" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1086,37 +1140,37 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="42" t="n"/>
-      <c r="C3" s="56" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D3" s="63" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="58" t="inlineStr">
+      <c r="E3" s="64" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="59" t="inlineStr">
+      <c r="F3" s="65" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="60" t="inlineStr">
+      <c r="G3" s="66" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="61" t="inlineStr">
+      <c r="H3" s="67" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -399,6 +399,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D96A10"/>
         <bgColor rgb="00D96A10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8D5F2"/>
+        <bgColor rgb="00A8D5F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005BA3D9"/>
+        <bgColor rgb="005BA3D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8F7"/>
+        <bgColor rgb="00D0E8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A7BBF"/>
+        <bgColor rgb="003A7BBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007EC4EA"/>
+        <bgColor rgb="007EC4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B6DAE"/>
+        <bgColor rgb="002B6DAE"/>
       </patternFill>
     </fill>
   </fills>
@@ -532,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,6 +761,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="46" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="49" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="51" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1140,37 +1194,37 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="42" t="n"/>
-      <c r="C3" s="62" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="63" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="65" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="66" t="inlineStr">
+      <c r="G3" s="72" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="67" t="inlineStr">
+      <c r="H3" s="73" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="55">
     <fill>
       <patternFill/>
     </fill>
@@ -435,6 +435,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="002B6DAE"/>
         <bgColor rgb="002B6DAE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A94CC"/>
+        <bgColor rgb="004A94CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006BB0E0"/>
+        <bgColor rgb="006BB0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00336FA5"/>
+        <bgColor rgb="00336FA5"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -779,6 +797,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="52" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="53" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="54" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1194,37 +1221,37 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="42" t="n"/>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" s="74" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="D3" s="73" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="71" t="inlineStr">
+      <c r="F3" s="76" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="72" t="inlineStr">
+      <c r="G3" s="69" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="73" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="165" formatCode="m/d"/>
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0;&quot;&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -232,6 +232,16 @@
       <name val="KoPubWorld돋움체 Bold"/>
       <color rgb="007F6000"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="57">
@@ -572,7 +582,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1011,11 +1021,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1571,6 +1587,21 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="53" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="34" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="35" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1999,7 +2030,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z282"/>
+  <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="3" customWidth="1" style="5" min="1" max="1"/>
@@ -3705,209 +3736,108 @@
       <c r="Z48" s="4" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="141" t="n"/>
-      <c r="B49" s="141" t="inlineStr">
+      <c r="A49" s="222" t="n"/>
+      <c r="B49" s="222" t="inlineStr">
+        <is>
+          <t>특정순환계질환
+주요치료비</t>
+        </is>
+      </c>
+      <c r="C49" s="223" t="inlineStr">
+        <is>
+          <t>특정순환계 주요치료 수술 (연 1회)</t>
+        </is>
+      </c>
+      <c r="D49" s="224" t="n"/>
+      <c r="E49" s="224" t="n"/>
+      <c r="F49" s="224" t="n"/>
+      <c r="G49" s="224" t="n"/>
+      <c r="H49" s="224" t="n"/>
+      <c r="I49" s="224" t="n"/>
+      <c r="J49" s="224" t="n"/>
+      <c r="K49" s="224" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="C50" s="225" t="inlineStr">
+        <is>
+          <t>특정순환계질환 주요치료 혈전용해 (연 1회)</t>
+        </is>
+      </c>
+      <c r="D50" s="226" t="n"/>
+      <c r="E50" s="226" t="n"/>
+      <c r="F50" s="226" t="n"/>
+      <c r="G50" s="226" t="n"/>
+      <c r="H50" s="226" t="n"/>
+      <c r="I50" s="226" t="n"/>
+      <c r="J50" s="226" t="n"/>
+      <c r="K50" s="226" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="C51" s="223" t="inlineStr">
+        <is>
+          <t>특정순환계질환 주요치료 혈전제거 (연 1회)</t>
+        </is>
+      </c>
+      <c r="D51" s="224" t="n"/>
+      <c r="E51" s="224" t="n"/>
+      <c r="F51" s="224" t="n"/>
+      <c r="G51" s="224" t="n"/>
+      <c r="H51" s="224" t="n"/>
+      <c r="I51" s="224" t="n"/>
+      <c r="J51" s="224" t="n"/>
+      <c r="K51" s="224" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="C52" s="225" t="inlineStr">
+        <is>
+          <t>특정순환계질환 주요치료 혈전복합 (연 1회)</t>
+        </is>
+      </c>
+      <c r="D52" s="226" t="n"/>
+      <c r="E52" s="226" t="n"/>
+      <c r="F52" s="226" t="n"/>
+      <c r="G52" s="226" t="n"/>
+      <c r="H52" s="226" t="n"/>
+      <c r="I52" s="226" t="n"/>
+      <c r="J52" s="226" t="n"/>
+      <c r="K52" s="226" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="C53" s="223" t="inlineStr">
+        <is>
+          <t>특정순환계질환 주요치료 중환자실 (연 1회)</t>
+        </is>
+      </c>
+      <c r="D53" s="224" t="n"/>
+      <c r="E53" s="224" t="n"/>
+      <c r="F53" s="224" t="n"/>
+      <c r="G53" s="224" t="n"/>
+      <c r="H53" s="224" t="n"/>
+      <c r="I53" s="224" t="n"/>
+      <c r="J53" s="224" t="n"/>
+      <c r="K53" s="224" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="141" t="n"/>
+      <c r="B54" s="141" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="C49" s="134" t="inlineStr">
+      <c r="C54" s="134" t="inlineStr">
         <is>
           <t>질병 수술</t>
         </is>
       </c>
-      <c r="D49" s="135" t="n"/>
-      <c r="E49" s="135" t="n"/>
-      <c r="F49" s="135" t="n"/>
-      <c r="G49" s="135" t="n"/>
-      <c r="H49" s="135" t="n"/>
-      <c r="I49" s="135" t="n"/>
-      <c r="J49" s="135" t="n"/>
-      <c r="K49" s="135">
+      <c r="D54" s="135" t="n"/>
+      <c r="E54" s="135" t="n"/>
+      <c r="F54" s="135" t="n"/>
+      <c r="G54" s="135" t="n"/>
+      <c r="H54" s="135" t="n"/>
+      <c r="I54" s="135" t="n"/>
+      <c r="J54" s="135" t="n"/>
+      <c r="K54" s="135">
         <f>SUM(D49:J49)</f>
-        <v/>
-      </c>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n"/>
-      <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
-      <c r="R49" s="4" t="n"/>
-      <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
-      <c r="U49" s="4" t="n"/>
-      <c r="V49" s="4" t="n"/>
-      <c r="W49" s="4" t="n"/>
-      <c r="X49" s="4" t="n"/>
-      <c r="Y49" s="4" t="n"/>
-      <c r="Z49" s="4" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="181" t="n"/>
-      <c r="B50" s="181" t="n"/>
-      <c r="C50" s="137" t="inlineStr">
-        <is>
-          <t>질병수술비 1-5종</t>
-        </is>
-      </c>
-      <c r="D50" s="138" t="n"/>
-      <c r="E50" s="138" t="n"/>
-      <c r="F50" s="138" t="n"/>
-      <c r="G50" s="138" t="n"/>
-      <c r="H50" s="138" t="n"/>
-      <c r="I50" s="138" t="n"/>
-      <c r="J50" s="138" t="n"/>
-      <c r="K50" s="138">
-        <f>SUM(D50:J50)</f>
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n"/>
-      <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
-      <c r="R50" s="4" t="n"/>
-      <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
-      <c r="U50" s="4" t="n"/>
-      <c r="V50" s="4" t="n"/>
-      <c r="W50" s="4" t="n"/>
-      <c r="X50" s="4" t="n"/>
-      <c r="Y50" s="4" t="n"/>
-      <c r="Z50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="181" t="n"/>
-      <c r="B51" s="181" t="n"/>
-      <c r="C51" s="134" t="inlineStr">
-        <is>
-          <t>재해수술비 1-5종</t>
-        </is>
-      </c>
-      <c r="D51" s="135" t="n"/>
-      <c r="E51" s="135" t="n"/>
-      <c r="F51" s="135" t="n"/>
-      <c r="G51" s="135" t="n"/>
-      <c r="H51" s="135" t="n"/>
-      <c r="I51" s="135" t="n"/>
-      <c r="J51" s="135" t="n"/>
-      <c r="K51" s="135">
-        <f>SUM(D51:J51)</f>
-        <v/>
-      </c>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="n"/>
-      <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
-      <c r="R51" s="4" t="n"/>
-      <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
-      <c r="U51" s="4" t="n"/>
-      <c r="V51" s="4" t="n"/>
-      <c r="W51" s="4" t="n"/>
-      <c r="X51" s="4" t="n"/>
-      <c r="Y51" s="4" t="n"/>
-      <c r="Z51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="111" t="n"/>
-      <c r="B52" s="111" t="inlineStr">
-        <is>
-          <t>골절 / 깁스</t>
-        </is>
-      </c>
-      <c r="C52" s="111" t="inlineStr">
-        <is>
-          <t>골절</t>
-        </is>
-      </c>
-      <c r="D52" s="112" t="n"/>
-      <c r="E52" s="112" t="n"/>
-      <c r="F52" s="112" t="n"/>
-      <c r="G52" s="112" t="n"/>
-      <c r="H52" s="112" t="n"/>
-      <c r="I52" s="112" t="n"/>
-      <c r="J52" s="112" t="n"/>
-      <c r="K52" s="112">
-        <f>SUM(D52:J52)</f>
-        <v/>
-      </c>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="4" t="n"/>
-      <c r="S52" s="4" t="n"/>
-      <c r="T52" s="4" t="n"/>
-      <c r="U52" s="4" t="n"/>
-      <c r="V52" s="4" t="n"/>
-      <c r="W52" s="4" t="n"/>
-      <c r="X52" s="4" t="n"/>
-      <c r="Y52" s="4" t="n"/>
-      <c r="Z52" s="4" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="182" t="n"/>
-      <c r="B53" s="182" t="n"/>
-      <c r="C53" s="114" t="inlineStr">
-        <is>
-          <t>깁스</t>
-        </is>
-      </c>
-      <c r="D53" s="115" t="n"/>
-      <c r="E53" s="115" t="n"/>
-      <c r="F53" s="115" t="n"/>
-      <c r="G53" s="115" t="n"/>
-      <c r="H53" s="115" t="n"/>
-      <c r="I53" s="115" t="n"/>
-      <c r="J53" s="115" t="n"/>
-      <c r="K53" s="115">
-        <f>SUM(D53:J53)</f>
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
-      <c r="N53" s="4" t="n"/>
-      <c r="O53" s="4" t="n"/>
-      <c r="P53" s="4" t="n"/>
-      <c r="Q53" s="4" t="n"/>
-      <c r="R53" s="4" t="n"/>
-      <c r="S53" s="4" t="n"/>
-      <c r="T53" s="4" t="n"/>
-      <c r="U53" s="4" t="n"/>
-      <c r="V53" s="4" t="n"/>
-      <c r="W53" s="4" t="n"/>
-      <c r="X53" s="4" t="n"/>
-      <c r="Y53" s="4" t="n"/>
-      <c r="Z53" s="4" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="111" t="n"/>
-      <c r="B54" s="111" t="inlineStr">
-        <is>
-          <t>입원비 / 통원비</t>
-        </is>
-      </c>
-      <c r="C54" s="111" t="inlineStr">
-        <is>
-          <t>질병 (1일이상)</t>
-        </is>
-      </c>
-      <c r="D54" s="112" t="n"/>
-      <c r="E54" s="112" t="n"/>
-      <c r="F54" s="112" t="n"/>
-      <c r="G54" s="112" t="n"/>
-      <c r="H54" s="112" t="n"/>
-      <c r="I54" s="112" t="n"/>
-      <c r="J54" s="112" t="n"/>
-      <c r="K54" s="112">
-        <f>SUM(D54:J54)</f>
         <v/>
       </c>
       <c r="L54" s="4" t="n"/>
@@ -3929,20 +3859,20 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="181" t="n"/>
       <c r="B55" s="181" t="n"/>
-      <c r="C55" s="114" t="inlineStr">
+      <c r="C55" s="137" t="inlineStr">
         <is>
-          <t>재해 (1일이상)</t>
+          <t>질병수술비 1-5종</t>
         </is>
       </c>
-      <c r="D55" s="115" t="n"/>
-      <c r="E55" s="115" t="n"/>
-      <c r="F55" s="115" t="n"/>
-      <c r="G55" s="115" t="n"/>
-      <c r="H55" s="115" t="n"/>
-      <c r="I55" s="115" t="n"/>
-      <c r="J55" s="115" t="n"/>
-      <c r="K55" s="115">
-        <f>SUM(D55:J55)</f>
+      <c r="D55" s="138" t="n"/>
+      <c r="E55" s="138" t="n"/>
+      <c r="F55" s="138" t="n"/>
+      <c r="G55" s="138" t="n"/>
+      <c r="H55" s="138" t="n"/>
+      <c r="I55" s="138" t="n"/>
+      <c r="J55" s="138" t="n"/>
+      <c r="K55" s="138">
+        <f>SUM(D50:J50)</f>
         <v/>
       </c>
       <c r="L55" s="4" t="n"/>
@@ -3964,20 +3894,20 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="181" t="n"/>
       <c r="B56" s="181" t="n"/>
-      <c r="C56" s="111" t="inlineStr">
+      <c r="C56" s="134" t="inlineStr">
         <is>
-          <t>암입원비</t>
+          <t>재해수술비 1-5종</t>
         </is>
       </c>
-      <c r="D56" s="112" t="n"/>
-      <c r="E56" s="112" t="n"/>
-      <c r="F56" s="112" t="n"/>
-      <c r="G56" s="112" t="n"/>
-      <c r="H56" s="112" t="n"/>
-      <c r="I56" s="112" t="n"/>
-      <c r="J56" s="112" t="n"/>
-      <c r="K56" s="112">
-        <f>SUM(D56:J56)</f>
+      <c r="D56" s="135" t="n"/>
+      <c r="E56" s="135" t="n"/>
+      <c r="F56" s="135" t="n"/>
+      <c r="G56" s="135" t="n"/>
+      <c r="H56" s="135" t="n"/>
+      <c r="I56" s="135" t="n"/>
+      <c r="J56" s="135" t="n"/>
+      <c r="K56" s="135">
+        <f>SUM(D51:J51)</f>
         <v/>
       </c>
       <c r="L56" s="4" t="n"/>
@@ -3997,22 +3927,26 @@
       <c r="Z56" s="4" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="181" t="n"/>
-      <c r="B57" s="181" t="n"/>
-      <c r="C57" s="114" t="inlineStr">
+      <c r="A57" s="111" t="n"/>
+      <c r="B57" s="111" t="inlineStr">
         <is>
-          <t>종합병원입원비1인실</t>
+          <t>골절 / 깁스</t>
         </is>
       </c>
-      <c r="D57" s="115" t="n"/>
-      <c r="E57" s="115" t="n"/>
-      <c r="F57" s="115" t="n"/>
-      <c r="G57" s="115" t="n"/>
-      <c r="H57" s="115" t="n"/>
-      <c r="I57" s="115" t="n"/>
-      <c r="J57" s="115" t="n"/>
-      <c r="K57" s="115">
-        <f>SUM(D57:J57)</f>
+      <c r="C57" s="111" t="inlineStr">
+        <is>
+          <t>골절</t>
+        </is>
+      </c>
+      <c r="D57" s="112" t="n"/>
+      <c r="E57" s="112" t="n"/>
+      <c r="F57" s="112" t="n"/>
+      <c r="G57" s="112" t="n"/>
+      <c r="H57" s="112" t="n"/>
+      <c r="I57" s="112" t="n"/>
+      <c r="J57" s="112" t="n"/>
+      <c r="K57" s="112">
+        <f>SUM(D52:J52)</f>
         <v/>
       </c>
       <c r="L57" s="4" t="n"/>
@@ -4032,22 +3966,22 @@
       <c r="Z57" s="4" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="181" t="n"/>
-      <c r="B58" s="181" t="n"/>
-      <c r="C58" s="111" t="inlineStr">
+      <c r="A58" s="182" t="n"/>
+      <c r="B58" s="182" t="n"/>
+      <c r="C58" s="114" t="inlineStr">
         <is>
-          <t>종합병원입원비2~3인실</t>
+          <t>깁스</t>
         </is>
       </c>
-      <c r="D58" s="112" t="n"/>
-      <c r="E58" s="112" t="n"/>
-      <c r="F58" s="112" t="n"/>
-      <c r="G58" s="112" t="n"/>
-      <c r="H58" s="112" t="n"/>
-      <c r="I58" s="112" t="n"/>
-      <c r="J58" s="112" t="n"/>
-      <c r="K58" s="112">
-        <f>SUM(D58:J58)</f>
+      <c r="D58" s="115" t="n"/>
+      <c r="E58" s="115" t="n"/>
+      <c r="F58" s="115" t="n"/>
+      <c r="G58" s="115" t="n"/>
+      <c r="H58" s="115" t="n"/>
+      <c r="I58" s="115" t="n"/>
+      <c r="J58" s="115" t="n"/>
+      <c r="K58" s="115">
+        <f>SUM(D53:J53)</f>
         <v/>
       </c>
       <c r="L58" s="4" t="n"/>
@@ -4067,22 +4001,26 @@
       <c r="Z58" s="4" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="181" t="n"/>
-      <c r="B59" s="181" t="n"/>
-      <c r="C59" s="114" t="inlineStr">
+      <c r="A59" s="111" t="n"/>
+      <c r="B59" s="111" t="inlineStr">
         <is>
-          <t>상급병원입원비1인실</t>
+          <t>입원비 / 통원비</t>
         </is>
       </c>
-      <c r="D59" s="115" t="n"/>
-      <c r="E59" s="115" t="n"/>
-      <c r="F59" s="115" t="n"/>
-      <c r="G59" s="115" t="n"/>
-      <c r="H59" s="115" t="n"/>
-      <c r="I59" s="115" t="n"/>
-      <c r="J59" s="115" t="n"/>
-      <c r="K59" s="115">
-        <f>SUM(D59:J59)</f>
+      <c r="C59" s="111" t="inlineStr">
+        <is>
+          <t>질병 (1일이상)</t>
+        </is>
+      </c>
+      <c r="D59" s="112" t="n"/>
+      <c r="E59" s="112" t="n"/>
+      <c r="F59" s="112" t="n"/>
+      <c r="G59" s="112" t="n"/>
+      <c r="H59" s="112" t="n"/>
+      <c r="I59" s="112" t="n"/>
+      <c r="J59" s="112" t="n"/>
+      <c r="K59" s="112">
+        <f>SUM(D54:J54)</f>
         <v/>
       </c>
       <c r="L59" s="4" t="n"/>
@@ -4104,20 +4042,20 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="181" t="n"/>
       <c r="B60" s="181" t="n"/>
-      <c r="C60" s="111" t="inlineStr">
+      <c r="C60" s="114" t="inlineStr">
         <is>
-          <t>상급병원입원비2~3인실</t>
+          <t>재해 (1일이상)</t>
         </is>
       </c>
-      <c r="D60" s="112" t="n"/>
-      <c r="E60" s="112" t="n"/>
-      <c r="F60" s="112" t="n"/>
-      <c r="G60" s="112" t="n"/>
-      <c r="H60" s="112" t="n"/>
-      <c r="I60" s="112" t="n"/>
-      <c r="J60" s="112" t="n"/>
-      <c r="K60" s="112">
-        <f>SUM(D60:J60)</f>
+      <c r="D60" s="115" t="n"/>
+      <c r="E60" s="115" t="n"/>
+      <c r="F60" s="115" t="n"/>
+      <c r="G60" s="115" t="n"/>
+      <c r="H60" s="115" t="n"/>
+      <c r="I60" s="115" t="n"/>
+      <c r="J60" s="115" t="n"/>
+      <c r="K60" s="115">
+        <f>SUM(D55:J55)</f>
         <v/>
       </c>
       <c r="L60" s="4" t="n"/>
@@ -4139,20 +4077,20 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="181" t="n"/>
       <c r="B61" s="181" t="n"/>
-      <c r="C61" s="114" t="inlineStr">
+      <c r="C61" s="111" t="inlineStr">
         <is>
-          <t>중환자실입원비</t>
+          <t>암입원비</t>
         </is>
       </c>
-      <c r="D61" s="115" t="n"/>
-      <c r="E61" s="115" t="n"/>
-      <c r="F61" s="115" t="n"/>
-      <c r="G61" s="115" t="n"/>
-      <c r="H61" s="115" t="n"/>
-      <c r="I61" s="115" t="n"/>
-      <c r="J61" s="115" t="n"/>
-      <c r="K61" s="115">
-        <f>SUM(D61:J61)</f>
+      <c r="D61" s="112" t="n"/>
+      <c r="E61" s="112" t="n"/>
+      <c r="F61" s="112" t="n"/>
+      <c r="G61" s="112" t="n"/>
+      <c r="H61" s="112" t="n"/>
+      <c r="I61" s="112" t="n"/>
+      <c r="J61" s="112" t="n"/>
+      <c r="K61" s="112">
+        <f>SUM(D56:J56)</f>
         <v/>
       </c>
       <c r="L61" s="4" t="n"/>
@@ -4174,20 +4112,20 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="181" t="n"/>
       <c r="B62" s="181" t="n"/>
-      <c r="C62" s="111" t="inlineStr">
+      <c r="C62" s="114" t="inlineStr">
         <is>
-          <t>종합병원통원비</t>
+          <t>종합병원입원비1인실</t>
         </is>
       </c>
-      <c r="D62" s="112" t="n"/>
-      <c r="E62" s="112" t="n"/>
-      <c r="F62" s="112" t="n"/>
-      <c r="G62" s="112" t="n"/>
-      <c r="H62" s="112" t="n"/>
-      <c r="I62" s="112" t="n"/>
-      <c r="J62" s="112" t="n"/>
-      <c r="K62" s="112">
-        <f>SUM(D62:J62)</f>
+      <c r="D62" s="115" t="n"/>
+      <c r="E62" s="115" t="n"/>
+      <c r="F62" s="115" t="n"/>
+      <c r="G62" s="115" t="n"/>
+      <c r="H62" s="115" t="n"/>
+      <c r="I62" s="115" t="n"/>
+      <c r="J62" s="115" t="n"/>
+      <c r="K62" s="115">
+        <f>SUM(D57:J57)</f>
         <v/>
       </c>
       <c r="L62" s="4" t="n"/>
@@ -4209,20 +4147,20 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="181" t="n"/>
       <c r="B63" s="181" t="n"/>
-      <c r="C63" s="114" t="inlineStr">
+      <c r="C63" s="111" t="inlineStr">
         <is>
-          <t>상급종합병원통원비</t>
+          <t>종합병원입원비2~3인실</t>
         </is>
       </c>
-      <c r="D63" s="115" t="n"/>
-      <c r="E63" s="115" t="n"/>
-      <c r="F63" s="115" t="n"/>
-      <c r="G63" s="115" t="n"/>
-      <c r="H63" s="115" t="n"/>
-      <c r="I63" s="115" t="n"/>
-      <c r="J63" s="115" t="n"/>
-      <c r="K63" s="115">
-        <f>SUM(D63:J63)</f>
+      <c r="D63" s="112" t="n"/>
+      <c r="E63" s="112" t="n"/>
+      <c r="F63" s="112" t="n"/>
+      <c r="G63" s="112" t="n"/>
+      <c r="H63" s="112" t="n"/>
+      <c r="I63" s="112" t="n"/>
+      <c r="J63" s="112" t="n"/>
+      <c r="K63" s="112">
+        <f>SUM(D58:J58)</f>
         <v/>
       </c>
       <c r="L63" s="4" t="n"/>
@@ -4242,22 +4180,22 @@
       <c r="Z63" s="4" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="182" t="n"/>
-      <c r="B64" s="182" t="n"/>
-      <c r="C64" s="111" t="inlineStr">
+      <c r="A64" s="181" t="n"/>
+      <c r="B64" s="181" t="n"/>
+      <c r="C64" s="114" t="inlineStr">
         <is>
-          <t>상급종합병원암통원비</t>
+          <t>상급병원입원비1인실</t>
         </is>
       </c>
-      <c r="D64" s="112" t="n"/>
-      <c r="E64" s="112" t="n"/>
-      <c r="F64" s="112" t="n"/>
-      <c r="G64" s="112" t="n"/>
-      <c r="H64" s="112" t="n"/>
-      <c r="I64" s="112" t="n"/>
-      <c r="J64" s="112" t="n"/>
-      <c r="K64" s="112">
-        <f>SUM(D64:J64)</f>
+      <c r="D64" s="115" t="n"/>
+      <c r="E64" s="115" t="n"/>
+      <c r="F64" s="115" t="n"/>
+      <c r="G64" s="115" t="n"/>
+      <c r="H64" s="115" t="n"/>
+      <c r="I64" s="115" t="n"/>
+      <c r="J64" s="115" t="n"/>
+      <c r="K64" s="115">
+        <f>SUM(D59:J59)</f>
         <v/>
       </c>
       <c r="L64" s="4" t="n"/>
@@ -4277,26 +4215,22 @@
       <c r="Z64" s="4" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="184" t="n"/>
-      <c r="B65" s="184" t="inlineStr">
+      <c r="A65" s="181" t="n"/>
+      <c r="B65" s="181" t="n"/>
+      <c r="C65" s="111" t="inlineStr">
         <is>
-          <t>치매보장</t>
+          <t>상급병원입원비2~3인실</t>
         </is>
       </c>
-      <c r="C65" s="184" t="inlineStr">
-        <is>
-          <t>경증치매</t>
-        </is>
-      </c>
-      <c r="D65" s="185" t="n"/>
-      <c r="E65" s="185" t="n"/>
-      <c r="F65" s="185" t="n"/>
-      <c r="G65" s="185" t="n"/>
-      <c r="H65" s="185" t="n"/>
-      <c r="I65" s="185" t="n"/>
-      <c r="J65" s="185" t="n"/>
-      <c r="K65" s="185">
-        <f>SUM(D65:J65)</f>
+      <c r="D65" s="112" t="n"/>
+      <c r="E65" s="112" t="n"/>
+      <c r="F65" s="112" t="n"/>
+      <c r="G65" s="112" t="n"/>
+      <c r="H65" s="112" t="n"/>
+      <c r="I65" s="112" t="n"/>
+      <c r="J65" s="112" t="n"/>
+      <c r="K65" s="112">
+        <f>SUM(D60:J60)</f>
         <v/>
       </c>
       <c r="L65" s="4" t="n"/>
@@ -4316,22 +4250,22 @@
       <c r="Z65" s="4" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="182" t="n"/>
-      <c r="B66" s="182" t="n"/>
-      <c r="C66" s="187" t="inlineStr">
+      <c r="A66" s="181" t="n"/>
+      <c r="B66" s="181" t="n"/>
+      <c r="C66" s="114" t="inlineStr">
         <is>
-          <t>중증치매</t>
+          <t>중환자실입원비</t>
         </is>
       </c>
-      <c r="D66" s="188" t="n"/>
-      <c r="E66" s="188" t="n"/>
-      <c r="F66" s="188" t="n"/>
-      <c r="G66" s="188" t="n"/>
-      <c r="H66" s="188" t="n"/>
-      <c r="I66" s="188" t="n"/>
-      <c r="J66" s="188" t="n"/>
-      <c r="K66" s="188">
-        <f>SUM(D66:J66)</f>
+      <c r="D66" s="115" t="n"/>
+      <c r="E66" s="115" t="n"/>
+      <c r="F66" s="115" t="n"/>
+      <c r="G66" s="115" t="n"/>
+      <c r="H66" s="115" t="n"/>
+      <c r="I66" s="115" t="n"/>
+      <c r="J66" s="115" t="n"/>
+      <c r="K66" s="115">
+        <f>SUM(D61:J61)</f>
         <v/>
       </c>
       <c r="L66" s="4" t="n"/>
@@ -4351,26 +4285,22 @@
       <c r="Z66" s="4" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="148" t="n"/>
-      <c r="B67" s="148" t="inlineStr">
+      <c r="A67" s="181" t="n"/>
+      <c r="B67" s="181" t="n"/>
+      <c r="C67" s="111" t="inlineStr">
         <is>
-          <t>간병비</t>
+          <t>종합병원통원비</t>
         </is>
       </c>
-      <c r="C67" s="148" t="inlineStr">
-        <is>
-          <t>간병비(질병)</t>
-        </is>
-      </c>
-      <c r="D67" s="149" t="n"/>
-      <c r="E67" s="149" t="n"/>
-      <c r="F67" s="149" t="n"/>
-      <c r="G67" s="149" t="n"/>
-      <c r="H67" s="149" t="n"/>
-      <c r="I67" s="149" t="n"/>
-      <c r="J67" s="149" t="n"/>
-      <c r="K67" s="149">
-        <f>SUM(D67:J67)</f>
+      <c r="D67" s="112" t="n"/>
+      <c r="E67" s="112" t="n"/>
+      <c r="F67" s="112" t="n"/>
+      <c r="G67" s="112" t="n"/>
+      <c r="H67" s="112" t="n"/>
+      <c r="I67" s="112" t="n"/>
+      <c r="J67" s="112" t="n"/>
+      <c r="K67" s="112">
+        <f>SUM(D62:J62)</f>
         <v/>
       </c>
       <c r="L67" s="4" t="n"/>
@@ -4390,22 +4320,22 @@
       <c r="Z67" s="4" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="182" t="n"/>
-      <c r="B68" s="182" t="n"/>
-      <c r="C68" s="151" t="inlineStr">
+      <c r="A68" s="181" t="n"/>
+      <c r="B68" s="181" t="n"/>
+      <c r="C68" s="114" t="inlineStr">
         <is>
-          <t>간병비(상해)</t>
+          <t>상급종합병원통원비</t>
         </is>
       </c>
-      <c r="D68" s="152" t="n"/>
-      <c r="E68" s="152" t="n"/>
-      <c r="F68" s="152" t="n"/>
-      <c r="G68" s="152" t="n"/>
-      <c r="H68" s="152" t="n"/>
-      <c r="I68" s="152" t="n"/>
-      <c r="J68" s="152" t="n"/>
-      <c r="K68" s="152">
-        <f>SUM(D68:J68)</f>
+      <c r="D68" s="115" t="n"/>
+      <c r="E68" s="115" t="n"/>
+      <c r="F68" s="115" t="n"/>
+      <c r="G68" s="115" t="n"/>
+      <c r="H68" s="115" t="n"/>
+      <c r="I68" s="115" t="n"/>
+      <c r="J68" s="115" t="n"/>
+      <c r="K68" s="115">
+        <f>SUM(D63:J63)</f>
         <v/>
       </c>
       <c r="L68" s="4" t="n"/>
@@ -4425,26 +4355,22 @@
       <c r="Z68" s="4" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="153" t="n"/>
-      <c r="B69" s="153" t="inlineStr">
+      <c r="A69" s="182" t="n"/>
+      <c r="B69" s="182" t="n"/>
+      <c r="C69" s="111" t="inlineStr">
         <is>
-          <t>치아</t>
+          <t>상급종합병원암통원비</t>
         </is>
       </c>
-      <c r="C69" s="153" t="inlineStr">
-        <is>
-          <t>치아보철치료비</t>
-        </is>
-      </c>
-      <c r="D69" s="154" t="n"/>
-      <c r="E69" s="154" t="n"/>
-      <c r="F69" s="154" t="n"/>
-      <c r="G69" s="154" t="n"/>
-      <c r="H69" s="154" t="n"/>
-      <c r="I69" s="154" t="n"/>
-      <c r="J69" s="154" t="n"/>
-      <c r="K69" s="154">
-        <f>SUM(D69:J69)</f>
+      <c r="D69" s="112" t="n"/>
+      <c r="E69" s="112" t="n"/>
+      <c r="F69" s="112" t="n"/>
+      <c r="G69" s="112" t="n"/>
+      <c r="H69" s="112" t="n"/>
+      <c r="I69" s="112" t="n"/>
+      <c r="J69" s="112" t="n"/>
+      <c r="K69" s="112">
+        <f>SUM(D64:J64)</f>
         <v/>
       </c>
       <c r="L69" s="4" t="n"/>
@@ -4464,22 +4390,26 @@
       <c r="Z69" s="4" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="182" t="n"/>
-      <c r="B70" s="182" t="n"/>
-      <c r="C70" s="156" t="inlineStr">
+      <c r="A70" s="184" t="n"/>
+      <c r="B70" s="184" t="inlineStr">
         <is>
-          <t>치아보존치료비</t>
+          <t>치매보장</t>
         </is>
       </c>
-      <c r="D70" s="157" t="n"/>
-      <c r="E70" s="157" t="n"/>
-      <c r="F70" s="157" t="n"/>
-      <c r="G70" s="157" t="n"/>
-      <c r="H70" s="157" t="n"/>
-      <c r="I70" s="157" t="n"/>
-      <c r="J70" s="157" t="n"/>
-      <c r="K70" s="157">
-        <f>SUM(D70:J70)</f>
+      <c r="C70" s="184" t="inlineStr">
+        <is>
+          <t>경증치매</t>
+        </is>
+      </c>
+      <c r="D70" s="185" t="n"/>
+      <c r="E70" s="185" t="n"/>
+      <c r="F70" s="185" t="n"/>
+      <c r="G70" s="185" t="n"/>
+      <c r="H70" s="185" t="n"/>
+      <c r="I70" s="185" t="n"/>
+      <c r="J70" s="185" t="n"/>
+      <c r="K70" s="185">
+        <f>SUM(D65:J65)</f>
         <v/>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -4499,26 +4429,22 @@
       <c r="Z70" s="4" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="118" t="n"/>
-      <c r="B71" s="118" t="inlineStr">
+      <c r="A71" s="182" t="n"/>
+      <c r="B71" s="182" t="n"/>
+      <c r="C71" s="187" t="inlineStr">
         <is>
-          <t>실손의료비</t>
+          <t>중증치매</t>
         </is>
       </c>
-      <c r="C71" s="118" t="inlineStr">
-        <is>
-          <t>질병입원</t>
-        </is>
-      </c>
-      <c r="D71" s="119" t="n"/>
-      <c r="E71" s="119" t="n"/>
-      <c r="F71" s="119" t="n"/>
-      <c r="G71" s="119" t="n"/>
-      <c r="H71" s="119" t="n"/>
-      <c r="I71" s="119" t="n"/>
-      <c r="J71" s="119" t="n"/>
-      <c r="K71" s="119">
-        <f>SUM(D71:J71)</f>
+      <c r="D71" s="188" t="n"/>
+      <c r="E71" s="188" t="n"/>
+      <c r="F71" s="188" t="n"/>
+      <c r="G71" s="188" t="n"/>
+      <c r="H71" s="188" t="n"/>
+      <c r="I71" s="188" t="n"/>
+      <c r="J71" s="188" t="n"/>
+      <c r="K71" s="188">
+        <f>SUM(D66:J66)</f>
         <v/>
       </c>
       <c r="L71" s="4" t="n"/>
@@ -4538,22 +4464,26 @@
       <c r="Z71" s="4" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="181" t="n"/>
-      <c r="B72" s="181" t="n"/>
-      <c r="C72" s="121" t="inlineStr">
+      <c r="A72" s="148" t="n"/>
+      <c r="B72" s="148" t="inlineStr">
         <is>
-          <t>질병통원</t>
+          <t>간병비</t>
         </is>
       </c>
-      <c r="D72" s="122" t="n"/>
-      <c r="E72" s="122" t="n"/>
-      <c r="F72" s="122" t="n"/>
-      <c r="G72" s="122" t="n"/>
-      <c r="H72" s="122" t="n"/>
-      <c r="I72" s="122" t="n"/>
-      <c r="J72" s="122" t="n"/>
-      <c r="K72" s="122">
-        <f>SUM(D72:J72)</f>
+      <c r="C72" s="148" t="inlineStr">
+        <is>
+          <t>간병비(질병)</t>
+        </is>
+      </c>
+      <c r="D72" s="149" t="n"/>
+      <c r="E72" s="149" t="n"/>
+      <c r="F72" s="149" t="n"/>
+      <c r="G72" s="149" t="n"/>
+      <c r="H72" s="149" t="n"/>
+      <c r="I72" s="149" t="n"/>
+      <c r="J72" s="149" t="n"/>
+      <c r="K72" s="149">
+        <f>SUM(D67:J67)</f>
         <v/>
       </c>
       <c r="L72" s="4" t="n"/>
@@ -4573,22 +4503,22 @@
       <c r="Z72" s="4" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="181" t="n"/>
-      <c r="B73" s="181" t="n"/>
-      <c r="C73" s="118" t="inlineStr">
+      <c r="A73" s="182" t="n"/>
+      <c r="B73" s="182" t="n"/>
+      <c r="C73" s="151" t="inlineStr">
         <is>
-          <t>상해입원</t>
+          <t>간병비(상해)</t>
         </is>
       </c>
-      <c r="D73" s="119" t="n"/>
-      <c r="E73" s="119" t="n"/>
-      <c r="F73" s="119" t="n"/>
-      <c r="G73" s="119" t="n"/>
-      <c r="H73" s="119" t="n"/>
-      <c r="I73" s="119" t="n"/>
-      <c r="J73" s="119" t="n"/>
-      <c r="K73" s="119">
-        <f>SUM(D73:J73)</f>
+      <c r="D73" s="152" t="n"/>
+      <c r="E73" s="152" t="n"/>
+      <c r="F73" s="152" t="n"/>
+      <c r="G73" s="152" t="n"/>
+      <c r="H73" s="152" t="n"/>
+      <c r="I73" s="152" t="n"/>
+      <c r="J73" s="152" t="n"/>
+      <c r="K73" s="152">
+        <f>SUM(D68:J68)</f>
         <v/>
       </c>
       <c r="L73" s="4" t="n"/>
@@ -4608,22 +4538,26 @@
       <c r="Z73" s="4" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="182" t="n"/>
-      <c r="B74" s="182" t="n"/>
-      <c r="C74" s="121" t="inlineStr">
+      <c r="A74" s="153" t="n"/>
+      <c r="B74" s="153" t="inlineStr">
         <is>
-          <t>상해통원</t>
+          <t>치아</t>
         </is>
       </c>
-      <c r="D74" s="122" t="n"/>
-      <c r="E74" s="122" t="n"/>
-      <c r="F74" s="122" t="n"/>
-      <c r="G74" s="122" t="n"/>
-      <c r="H74" s="122" t="n"/>
-      <c r="I74" s="122" t="n"/>
-      <c r="J74" s="122" t="n"/>
-      <c r="K74" s="122">
-        <f>SUM(D74:J74)</f>
+      <c r="C74" s="153" t="inlineStr">
+        <is>
+          <t>치아보철치료비</t>
+        </is>
+      </c>
+      <c r="D74" s="154" t="n"/>
+      <c r="E74" s="154" t="n"/>
+      <c r="F74" s="154" t="n"/>
+      <c r="G74" s="154" t="n"/>
+      <c r="H74" s="154" t="n"/>
+      <c r="I74" s="154" t="n"/>
+      <c r="J74" s="154" t="n"/>
+      <c r="K74" s="154">
+        <f>SUM(D69:J69)</f>
         <v/>
       </c>
       <c r="L74" s="4" t="n"/>
@@ -4643,24 +4577,22 @@
       <c r="Z74" s="4" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="158" t="n"/>
-      <c r="B75" s="159" t="inlineStr">
+      <c r="A75" s="182" t="n"/>
+      <c r="B75" s="182" t="n"/>
+      <c r="C75" s="156" t="inlineStr">
         <is>
-          <t>기납입보험료</t>
+          <t>치아보존치료비</t>
         </is>
       </c>
-      <c r="C75" s="159" t="n"/>
-      <c r="D75" s="160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="160" t="n"/>
-      <c r="F75" s="160" t="n"/>
-      <c r="G75" s="160" t="n"/>
-      <c r="H75" s="160" t="n"/>
-      <c r="I75" s="160" t="n"/>
-      <c r="J75" s="160" t="n"/>
-      <c r="K75" s="160">
-        <f>SUM(D75:J75)</f>
+      <c r="D75" s="157" t="n"/>
+      <c r="E75" s="157" t="n"/>
+      <c r="F75" s="157" t="n"/>
+      <c r="G75" s="157" t="n"/>
+      <c r="H75" s="157" t="n"/>
+      <c r="I75" s="157" t="n"/>
+      <c r="J75" s="157" t="n"/>
+      <c r="K75" s="157">
+        <f>SUM(D70:J70)</f>
         <v/>
       </c>
       <c r="L75" s="4" t="n"/>
@@ -4680,24 +4612,26 @@
       <c r="Z75" s="4" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="181" t="n"/>
-      <c r="B76" s="162" t="inlineStr">
+      <c r="A76" s="118" t="n"/>
+      <c r="B76" s="118" t="inlineStr">
         <is>
-          <t>납입할보험료</t>
+          <t>실손의료비</t>
         </is>
       </c>
-      <c r="C76" s="162" t="n"/>
-      <c r="D76" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="163" t="n"/>
-      <c r="F76" s="163" t="n"/>
-      <c r="G76" s="163" t="n"/>
-      <c r="H76" s="163" t="n"/>
-      <c r="I76" s="163" t="n"/>
-      <c r="J76" s="163" t="n"/>
-      <c r="K76" s="163">
-        <f>SUM(D76:J76)</f>
+      <c r="C76" s="118" t="inlineStr">
+        <is>
+          <t>질병입원</t>
+        </is>
+      </c>
+      <c r="D76" s="119" t="n"/>
+      <c r="E76" s="119" t="n"/>
+      <c r="F76" s="119" t="n"/>
+      <c r="G76" s="119" t="n"/>
+      <c r="H76" s="119" t="n"/>
+      <c r="I76" s="119" t="n"/>
+      <c r="J76" s="119" t="n"/>
+      <c r="K76" s="119">
+        <f>SUM(D71:J71)</f>
         <v/>
       </c>
       <c r="L76" s="4" t="n"/>
@@ -4717,43 +4651,22 @@
       <c r="Z76" s="4" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="182" t="n"/>
-      <c r="B77" s="159" t="inlineStr">
+      <c r="A77" s="181" t="n"/>
+      <c r="B77" s="181" t="n"/>
+      <c r="C77" s="121" t="inlineStr">
         <is>
-          <t>총납입보험료</t>
+          <t>질병통원</t>
         </is>
       </c>
-      <c r="C77" s="159" t="n"/>
-      <c r="D77" s="160">
-        <f>D75+D76</f>
-        <v/>
-      </c>
-      <c r="E77" s="160">
-        <f>E75+E76</f>
-        <v/>
-      </c>
-      <c r="F77" s="160">
-        <f>F75+F76</f>
-        <v/>
-      </c>
-      <c r="G77" s="160">
-        <f>G75+G76</f>
-        <v/>
-      </c>
-      <c r="H77" s="160">
-        <f>H75+H76</f>
-        <v/>
-      </c>
-      <c r="I77" s="160">
-        <f>I75+I76</f>
-        <v/>
-      </c>
-      <c r="J77" s="160">
-        <f>J75+J76</f>
-        <v/>
-      </c>
-      <c r="K77" s="160">
-        <f>SUM(D77:J77)</f>
+      <c r="D77" s="122" t="n"/>
+      <c r="E77" s="122" t="n"/>
+      <c r="F77" s="122" t="n"/>
+      <c r="G77" s="122" t="n"/>
+      <c r="H77" s="122" t="n"/>
+      <c r="I77" s="122" t="n"/>
+      <c r="J77" s="122" t="n"/>
+      <c r="K77" s="122">
+        <f>SUM(D72:J72)</f>
         <v/>
       </c>
       <c r="L77" s="4" t="n"/>
@@ -4773,17 +4686,24 @@
       <c r="Z77" s="4" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="48" t="n"/>
-      <c r="B78" s="49" t="n"/>
-      <c r="C78" s="49" t="n"/>
-      <c r="D78" s="165" t="n"/>
-      <c r="E78" s="165" t="n"/>
-      <c r="F78" s="165" t="n"/>
-      <c r="G78" s="165" t="n"/>
-      <c r="H78" s="165" t="n"/>
-      <c r="I78" s="165" t="n"/>
-      <c r="J78" s="165" t="n"/>
-      <c r="K78" s="165" t="n"/>
+      <c r="A78" s="181" t="n"/>
+      <c r="B78" s="181" t="n"/>
+      <c r="C78" s="118" t="inlineStr">
+        <is>
+          <t>상해입원</t>
+        </is>
+      </c>
+      <c r="D78" s="119" t="n"/>
+      <c r="E78" s="119" t="n"/>
+      <c r="F78" s="119" t="n"/>
+      <c r="G78" s="119" t="n"/>
+      <c r="H78" s="119" t="n"/>
+      <c r="I78" s="119" t="n"/>
+      <c r="J78" s="119" t="n"/>
+      <c r="K78" s="119">
+        <f>SUM(D73:J73)</f>
+        <v/>
+      </c>
       <c r="L78" s="4" t="n"/>
       <c r="M78" s="4" t="n"/>
       <c r="N78" s="4" t="n"/>
@@ -4801,21 +4721,27 @@
       <c r="Z78" s="4" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="208" t="inlineStr">
+      <c r="A79" s="182" t="n"/>
+      <c r="B79" s="182" t="n"/>
+      <c r="C79" s="121" t="inlineStr">
         <is>
-          <t>🔄  갱신형 / 비갱신형 구분</t>
+          <t>상해통원</t>
         </is>
       </c>
-      <c r="B79" s="208" t="n"/>
-      <c r="C79" s="208" t="n"/>
-      <c r="D79" s="208" t="n"/>
-      <c r="E79" s="208" t="n"/>
-      <c r="F79" s="208" t="n"/>
-      <c r="G79" s="208" t="n"/>
-      <c r="H79" s="208" t="n"/>
-      <c r="I79" s="208" t="n"/>
-      <c r="J79" s="208" t="n"/>
-      <c r="K79" s="208" t="n"/>
+      <c r="D79" s="122" t="n"/>
+      <c r="E79" s="122" t="n"/>
+      <c r="F79" s="122" t="n"/>
+      <c r="G79" s="122" t="n"/>
+      <c r="H79" s="122" t="n"/>
+      <c r="I79" s="122" t="n"/>
+      <c r="J79" s="122" t="n"/>
+      <c r="K79" s="122">
+        <f>SUM(D74:J74)</f>
+        <v/>
+      </c>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
@@ -4830,21 +4756,29 @@
       <c r="Z79" s="4" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="209" t="inlineStr">
+      <c r="A80" s="158" t="n"/>
+      <c r="B80" s="159" t="inlineStr">
         <is>
-          <t>갱신 구분</t>
+          <t>기납입보험료</t>
         </is>
       </c>
-      <c r="B80" s="209" t="n"/>
-      <c r="C80" s="209" t="n"/>
-      <c r="D80" s="210" t="n"/>
-      <c r="E80" s="210" t="n"/>
-      <c r="F80" s="210" t="n"/>
-      <c r="G80" s="210" t="n"/>
-      <c r="H80" s="210" t="n"/>
-      <c r="I80" s="210" t="n"/>
-      <c r="J80" s="210" t="n"/>
-      <c r="K80" s="211" t="n"/>
+      <c r="C80" s="159" t="n"/>
+      <c r="D80" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="160" t="n"/>
+      <c r="F80" s="160" t="n"/>
+      <c r="G80" s="160" t="n"/>
+      <c r="H80" s="160" t="n"/>
+      <c r="I80" s="160" t="n"/>
+      <c r="J80" s="160" t="n"/>
+      <c r="K80" s="160">
+        <f>SUM(D75:J75)</f>
+        <v/>
+      </c>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
@@ -4859,22 +4793,29 @@
       <c r="Z80" s="4" t="n"/>
     </row>
     <row r="81" ht="26" customHeight="1">
-      <c r="A81" s="209" t="inlineStr">
+      <c r="A81" s="181" t="n"/>
+      <c r="B81" s="162" t="inlineStr">
         <is>
-          <t>보험료
-변화 예고</t>
+          <t>납입할보험료</t>
         </is>
       </c>
-      <c r="B81" s="209" t="n"/>
-      <c r="C81" s="209" t="n"/>
-      <c r="D81" s="210" t="n"/>
-      <c r="E81" s="210" t="n"/>
-      <c r="F81" s="210" t="n"/>
-      <c r="G81" s="210" t="n"/>
-      <c r="H81" s="210" t="n"/>
-      <c r="I81" s="210" t="n"/>
-      <c r="J81" s="210" t="n"/>
-      <c r="K81" s="211" t="n"/>
+      <c r="C81" s="162" t="n"/>
+      <c r="D81" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="163" t="n"/>
+      <c r="F81" s="163" t="n"/>
+      <c r="G81" s="163" t="n"/>
+      <c r="H81" s="163" t="n"/>
+      <c r="I81" s="163" t="n"/>
+      <c r="J81" s="163" t="n"/>
+      <c r="K81" s="163">
+        <f>SUM(D76:J76)</f>
+        <v/>
+      </c>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
@@ -4889,6 +4830,48 @@
       <c r="Z81" s="4" t="n"/>
     </row>
     <row r="82" ht="7.5" customHeight="1">
+      <c r="A82" s="182" t="n"/>
+      <c r="B82" s="159" t="inlineStr">
+        <is>
+          <t>총납입보험료</t>
+        </is>
+      </c>
+      <c r="C82" s="159" t="n"/>
+      <c r="D82" s="160">
+        <f>D75+D76</f>
+        <v/>
+      </c>
+      <c r="E82" s="160">
+        <f>E75+E76</f>
+        <v/>
+      </c>
+      <c r="F82" s="160">
+        <f>F75+F76</f>
+        <v/>
+      </c>
+      <c r="G82" s="160">
+        <f>G75+G76</f>
+        <v/>
+      </c>
+      <c r="H82" s="160">
+        <f>H75+H76</f>
+        <v/>
+      </c>
+      <c r="I82" s="160">
+        <f>I75+I76</f>
+        <v/>
+      </c>
+      <c r="J82" s="160">
+        <f>J75+J76</f>
+        <v/>
+      </c>
+      <c r="K82" s="160">
+        <f>SUM(D77:J77)</f>
+        <v/>
+      </c>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
@@ -4903,21 +4886,20 @@
       <c r="Z82" s="4" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="212" t="inlineStr">
-        <is>
-          <t>📋  현재 유지중인 보험 리뷰</t>
-        </is>
-      </c>
-      <c r="B83" s="212" t="n"/>
-      <c r="C83" s="212" t="n"/>
-      <c r="D83" s="212" t="n"/>
-      <c r="E83" s="212" t="n"/>
-      <c r="F83" s="212" t="n"/>
-      <c r="G83" s="212" t="n"/>
-      <c r="H83" s="212" t="n"/>
-      <c r="I83" s="212" t="n"/>
-      <c r="J83" s="212" t="n"/>
-      <c r="K83" s="212" t="n"/>
+      <c r="A83" s="48" t="n"/>
+      <c r="B83" s="49" t="n"/>
+      <c r="C83" s="49" t="n"/>
+      <c r="D83" s="165" t="n"/>
+      <c r="E83" s="165" t="n"/>
+      <c r="F83" s="165" t="n"/>
+      <c r="G83" s="165" t="n"/>
+      <c r="H83" s="165" t="n"/>
+      <c r="I83" s="165" t="n"/>
+      <c r="J83" s="165" t="n"/>
+      <c r="K83" s="165" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
@@ -4932,37 +4914,21 @@
       <c r="Z83" s="4" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="209" t="inlineStr">
+      <c r="A84" s="208" t="inlineStr">
         <is>
-          <t>보험사 / 상품명</t>
+          <t>🔄  갱신형 / 비갱신형 구분</t>
         </is>
       </c>
-      <c r="B84" s="209" t="n"/>
-      <c r="C84" s="209" t="inlineStr">
-        <is>
-          <t>가입일 / 만기</t>
-        </is>
-      </c>
-      <c r="D84" s="209" t="inlineStr">
-        <is>
-          <t>월 보험료</t>
-        </is>
-      </c>
-      <c r="E84" s="209" t="inlineStr">
-        <is>
-          <t>주요 체크사항</t>
-        </is>
-      </c>
-      <c r="F84" s="209" t="n"/>
-      <c r="G84" s="209" t="n"/>
-      <c r="H84" s="209" t="n"/>
-      <c r="I84" s="209" t="inlineStr">
-        <is>
-          <t>특이사항 (면책기간, 보장범위 등)</t>
-        </is>
-      </c>
-      <c r="J84" s="209" t="n"/>
-      <c r="K84" s="209" t="n"/>
+      <c r="B84" s="215" t="n"/>
+      <c r="C84" s="215" t="n"/>
+      <c r="D84" s="215" t="n"/>
+      <c r="E84" s="215" t="n"/>
+      <c r="F84" s="215" t="n"/>
+      <c r="G84" s="215" t="n"/>
+      <c r="H84" s="215" t="n"/>
+      <c r="I84" s="215" t="n"/>
+      <c r="J84" s="215" t="n"/>
+      <c r="K84" s="214" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
@@ -4977,17 +4943,21 @@
       <c r="Z84" s="4" t="n"/>
     </row>
     <row r="85" ht="70" customHeight="1">
-      <c r="A85" s="213" t="n"/>
-      <c r="B85" s="214" t="n"/>
-      <c r="C85" s="213" t="n"/>
-      <c r="D85" s="213" t="n"/>
-      <c r="E85" s="213" t="n"/>
-      <c r="F85" s="215" t="n"/>
-      <c r="G85" s="215" t="n"/>
-      <c r="H85" s="214" t="n"/>
-      <c r="I85" s="213" t="n"/>
-      <c r="J85" s="215" t="n"/>
-      <c r="K85" s="214" t="n"/>
+      <c r="A85" s="209" t="inlineStr">
+        <is>
+          <t>갱신 구분</t>
+        </is>
+      </c>
+      <c r="B85" s="215" t="n"/>
+      <c r="C85" s="214" t="n"/>
+      <c r="D85" s="210" t="n"/>
+      <c r="E85" s="210" t="n"/>
+      <c r="F85" s="210" t="n"/>
+      <c r="G85" s="210" t="n"/>
+      <c r="H85" s="210" t="n"/>
+      <c r="I85" s="210" t="n"/>
+      <c r="J85" s="210" t="n"/>
+      <c r="K85" s="211" t="n"/>
       <c r="O85" s="4" t="n"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
@@ -5002,17 +4972,22 @@
       <c r="Z85" s="4" t="n"/>
     </row>
     <row r="86" ht="70" customHeight="1">
-      <c r="A86" s="216" t="n"/>
-      <c r="B86" s="214" t="n"/>
-      <c r="C86" s="216" t="n"/>
-      <c r="D86" s="216" t="n"/>
-      <c r="E86" s="216" t="n"/>
-      <c r="F86" s="215" t="n"/>
-      <c r="G86" s="215" t="n"/>
-      <c r="H86" s="214" t="n"/>
-      <c r="I86" s="216" t="n"/>
-      <c r="J86" s="215" t="n"/>
-      <c r="K86" s="214" t="n"/>
+      <c r="A86" s="209" t="inlineStr">
+        <is>
+          <t>보험료
+변화 예고</t>
+        </is>
+      </c>
+      <c r="B86" s="215" t="n"/>
+      <c r="C86" s="214" t="n"/>
+      <c r="D86" s="210" t="n"/>
+      <c r="E86" s="210" t="n"/>
+      <c r="F86" s="210" t="n"/>
+      <c r="G86" s="210" t="n"/>
+      <c r="H86" s="210" t="n"/>
+      <c r="I86" s="210" t="n"/>
+      <c r="J86" s="210" t="n"/>
+      <c r="K86" s="211" t="n"/>
       <c r="O86" s="4" t="n"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
@@ -5027,17 +5002,6 @@
       <c r="Z86" s="4" t="n"/>
     </row>
     <row r="87" ht="70" customHeight="1">
-      <c r="A87" s="217" t="n"/>
-      <c r="B87" s="214" t="n"/>
-      <c r="C87" s="217" t="n"/>
-      <c r="D87" s="217" t="n"/>
-      <c r="E87" s="217" t="n"/>
-      <c r="F87" s="215" t="n"/>
-      <c r="G87" s="215" t="n"/>
-      <c r="H87" s="214" t="n"/>
-      <c r="I87" s="217" t="n"/>
-      <c r="J87" s="215" t="n"/>
-      <c r="K87" s="214" t="n"/>
       <c r="O87" s="4" t="n"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
@@ -5052,15 +5016,19 @@
       <c r="Z87" s="4" t="n"/>
     </row>
     <row r="88" ht="70" customHeight="1">
-      <c r="A88" s="218" t="n"/>
-      <c r="B88" s="214" t="n"/>
-      <c r="C88" s="218" t="n"/>
-      <c r="D88" s="218" t="n"/>
-      <c r="E88" s="218" t="n"/>
+      <c r="A88" s="212" t="inlineStr">
+        <is>
+          <t>📋  현재 유지중인 보험 리뷰</t>
+        </is>
+      </c>
+      <c r="B88" s="215" t="n"/>
+      <c r="C88" s="215" t="n"/>
+      <c r="D88" s="215" t="n"/>
+      <c r="E88" s="215" t="n"/>
       <c r="F88" s="215" t="n"/>
       <c r="G88" s="215" t="n"/>
-      <c r="H88" s="214" t="n"/>
-      <c r="I88" s="218" t="n"/>
+      <c r="H88" s="215" t="n"/>
+      <c r="I88" s="215" t="n"/>
       <c r="J88" s="215" t="n"/>
       <c r="K88" s="214" t="n"/>
       <c r="O88" s="4" t="n"/>
@@ -5077,15 +5045,35 @@
       <c r="Z88" s="4" t="n"/>
     </row>
     <row r="89" ht="70" customHeight="1">
-      <c r="A89" s="219" t="n"/>
+      <c r="A89" s="209" t="inlineStr">
+        <is>
+          <t>보험사 / 상품명</t>
+        </is>
+      </c>
       <c r="B89" s="214" t="n"/>
-      <c r="C89" s="219" t="n"/>
-      <c r="D89" s="219" t="n"/>
-      <c r="E89" s="219" t="n"/>
+      <c r="C89" s="209" t="inlineStr">
+        <is>
+          <t>가입일 / 만기</t>
+        </is>
+      </c>
+      <c r="D89" s="209" t="inlineStr">
+        <is>
+          <t>월 보험료</t>
+        </is>
+      </c>
+      <c r="E89" s="209" t="inlineStr">
+        <is>
+          <t>주요 체크사항</t>
+        </is>
+      </c>
       <c r="F89" s="215" t="n"/>
       <c r="G89" s="215" t="n"/>
       <c r="H89" s="214" t="n"/>
-      <c r="I89" s="219" t="n"/>
+      <c r="I89" s="209" t="inlineStr">
+        <is>
+          <t>특이사항 (면책기간, 보장범위 등)</t>
+        </is>
+      </c>
       <c r="J89" s="215" t="n"/>
       <c r="K89" s="214" t="n"/>
       <c r="O89" s="4" t="n"/>
@@ -5102,15 +5090,15 @@
       <c r="Z89" s="4" t="n"/>
     </row>
     <row r="90" ht="70" customHeight="1">
-      <c r="A90" s="220" t="n"/>
+      <c r="A90" s="213" t="n"/>
       <c r="B90" s="214" t="n"/>
-      <c r="C90" s="220" t="n"/>
-      <c r="D90" s="220" t="n"/>
-      <c r="E90" s="220" t="n"/>
+      <c r="C90" s="213" t="n"/>
+      <c r="D90" s="213" t="n"/>
+      <c r="E90" s="213" t="n"/>
       <c r="F90" s="215" t="n"/>
       <c r="G90" s="215" t="n"/>
       <c r="H90" s="214" t="n"/>
-      <c r="I90" s="220" t="n"/>
+      <c r="I90" s="213" t="n"/>
       <c r="J90" s="215" t="n"/>
       <c r="K90" s="214" t="n"/>
       <c r="O90" s="4" t="n"/>
@@ -5127,15 +5115,15 @@
       <c r="Z90" s="4" t="n"/>
     </row>
     <row r="91" ht="70" customHeight="1">
-      <c r="A91" s="221" t="n"/>
+      <c r="A91" s="216" t="n"/>
       <c r="B91" s="214" t="n"/>
-      <c r="C91" s="221" t="n"/>
-      <c r="D91" s="221" t="n"/>
-      <c r="E91" s="221" t="n"/>
+      <c r="C91" s="216" t="n"/>
+      <c r="D91" s="216" t="n"/>
+      <c r="E91" s="216" t="n"/>
       <c r="F91" s="215" t="n"/>
       <c r="G91" s="215" t="n"/>
       <c r="H91" s="214" t="n"/>
-      <c r="I91" s="221" t="n"/>
+      <c r="I91" s="216" t="n"/>
       <c r="J91" s="215" t="n"/>
       <c r="K91" s="214" t="n"/>
       <c r="O91" s="4" t="n"/>
@@ -5152,6 +5140,17 @@
       <c r="Z91" s="4" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="217" t="n"/>
+      <c r="B92" s="214" t="n"/>
+      <c r="C92" s="217" t="n"/>
+      <c r="D92" s="217" t="n"/>
+      <c r="E92" s="217" t="n"/>
+      <c r="F92" s="215" t="n"/>
+      <c r="G92" s="215" t="n"/>
+      <c r="H92" s="214" t="n"/>
+      <c r="I92" s="217" t="n"/>
+      <c r="J92" s="215" t="n"/>
+      <c r="K92" s="214" t="n"/>
       <c r="O92" s="4" t="n"/>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
@@ -5166,6 +5165,17 @@
       <c r="Z92" s="4" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="218" t="n"/>
+      <c r="B93" s="214" t="n"/>
+      <c r="C93" s="218" t="n"/>
+      <c r="D93" s="218" t="n"/>
+      <c r="E93" s="218" t="n"/>
+      <c r="F93" s="215" t="n"/>
+      <c r="G93" s="215" t="n"/>
+      <c r="H93" s="214" t="n"/>
+      <c r="I93" s="218" t="n"/>
+      <c r="J93" s="215" t="n"/>
+      <c r="K93" s="214" t="n"/>
       <c r="O93" s="4" t="n"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
@@ -5180,6 +5190,17 @@
       <c r="Z93" s="4" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="219" t="n"/>
+      <c r="B94" s="214" t="n"/>
+      <c r="C94" s="219" t="n"/>
+      <c r="D94" s="219" t="n"/>
+      <c r="E94" s="219" t="n"/>
+      <c r="F94" s="215" t="n"/>
+      <c r="G94" s="215" t="n"/>
+      <c r="H94" s="214" t="n"/>
+      <c r="I94" s="219" t="n"/>
+      <c r="J94" s="215" t="n"/>
+      <c r="K94" s="214" t="n"/>
       <c r="O94" s="4" t="n"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
@@ -5194,6 +5215,17 @@
       <c r="Z94" s="4" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="220" t="n"/>
+      <c r="B95" s="214" t="n"/>
+      <c r="C95" s="220" t="n"/>
+      <c r="D95" s="220" t="n"/>
+      <c r="E95" s="220" t="n"/>
+      <c r="F95" s="215" t="n"/>
+      <c r="G95" s="215" t="n"/>
+      <c r="H95" s="214" t="n"/>
+      <c r="I95" s="220" t="n"/>
+      <c r="J95" s="215" t="n"/>
+      <c r="K95" s="214" t="n"/>
       <c r="O95" s="4" t="n"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
@@ -5208,6 +5240,17 @@
       <c r="Z95" s="4" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="221" t="n"/>
+      <c r="B96" s="214" t="n"/>
+      <c r="C96" s="221" t="n"/>
+      <c r="D96" s="221" t="n"/>
+      <c r="E96" s="221" t="n"/>
+      <c r="F96" s="215" t="n"/>
+      <c r="G96" s="215" t="n"/>
+      <c r="H96" s="214" t="n"/>
+      <c r="I96" s="221" t="n"/>
+      <c r="J96" s="215" t="n"/>
+      <c r="K96" s="214" t="n"/>
       <c r="O96" s="4" t="n"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
@@ -5488,20 +5531,6 @@
       <c r="Z115" s="4" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="4" t="n"/>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n"/>
-      <c r="I116" s="4" t="n"/>
-      <c r="J116" s="4" t="n"/>
-      <c r="K116" s="4" t="n"/>
-      <c r="L116" s="4" t="n"/>
-      <c r="M116" s="4" t="n"/>
-      <c r="N116" s="4" t="n"/>
       <c r="O116" s="4" t="n"/>
       <c r="P116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
@@ -5516,20 +5545,6 @@
       <c r="Z116" s="4" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="4" t="n"/>
-      <c r="B117" s="4" t="n"/>
-      <c r="C117" s="4" t="n"/>
-      <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="4" t="n"/>
-      <c r="H117" s="4" t="n"/>
-      <c r="I117" s="4" t="n"/>
-      <c r="J117" s="4" t="n"/>
-      <c r="K117" s="4" t="n"/>
-      <c r="L117" s="4" t="n"/>
-      <c r="M117" s="4" t="n"/>
-      <c r="N117" s="4" t="n"/>
       <c r="O117" s="4" t="n"/>
       <c r="P117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
@@ -5544,20 +5559,6 @@
       <c r="Z117" s="4" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="4" t="n"/>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
-      <c r="J118" s="4" t="n"/>
-      <c r="K118" s="4" t="n"/>
-      <c r="L118" s="4" t="n"/>
-      <c r="M118" s="4" t="n"/>
-      <c r="N118" s="4" t="n"/>
       <c r="O118" s="4" t="n"/>
       <c r="P118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
@@ -5572,20 +5573,6 @@
       <c r="Z118" s="4" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="4" t="n"/>
-      <c r="B119" s="4" t="n"/>
-      <c r="C119" s="4" t="n"/>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="4" t="n"/>
-      <c r="G119" s="4" t="n"/>
-      <c r="H119" s="4" t="n"/>
-      <c r="I119" s="4" t="n"/>
-      <c r="J119" s="4" t="n"/>
-      <c r="K119" s="4" t="n"/>
-      <c r="L119" s="4" t="n"/>
-      <c r="M119" s="4" t="n"/>
-      <c r="N119" s="4" t="n"/>
       <c r="O119" s="4" t="n"/>
       <c r="P119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
@@ -5600,20 +5587,6 @@
       <c r="Z119" s="4" t="n"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="4" t="n"/>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="n"/>
-      <c r="J120" s="4" t="n"/>
-      <c r="K120" s="4" t="n"/>
-      <c r="L120" s="4" t="n"/>
-      <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="n"/>
       <c r="O120" s="4" t="n"/>
       <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
@@ -10163,11 +10136,146 @@
       <c r="Y282" s="4" t="n"/>
       <c r="Z282" s="4" t="n"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="A283" s="4" t="n"/>
+      <c r="B283" s="4" t="n"/>
+      <c r="C283" s="4" t="n"/>
+      <c r="D283" s="4" t="n"/>
+      <c r="E283" s="4" t="n"/>
+      <c r="F283" s="4" t="n"/>
+      <c r="G283" s="4" t="n"/>
+      <c r="H283" s="4" t="n"/>
+      <c r="I283" s="4" t="n"/>
+      <c r="J283" s="4" t="n"/>
+      <c r="K283" s="4" t="n"/>
+      <c r="L283" s="4" t="n"/>
+      <c r="M283" s="4" t="n"/>
+      <c r="N283" s="4" t="n"/>
+      <c r="O283" s="4" t="n"/>
+      <c r="P283" s="4" t="n"/>
+      <c r="Q283" s="4" t="n"/>
+      <c r="R283" s="4" t="n"/>
+      <c r="S283" s="4" t="n"/>
+      <c r="T283" s="4" t="n"/>
+      <c r="U283" s="4" t="n"/>
+      <c r="V283" s="4" t="n"/>
+      <c r="W283" s="4" t="n"/>
+      <c r="X283" s="4" t="n"/>
+      <c r="Y283" s="4" t="n"/>
+      <c r="Z283" s="4" t="n"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="A284" s="4" t="n"/>
+      <c r="B284" s="4" t="n"/>
+      <c r="C284" s="4" t="n"/>
+      <c r="D284" s="4" t="n"/>
+      <c r="E284" s="4" t="n"/>
+      <c r="F284" s="4" t="n"/>
+      <c r="G284" s="4" t="n"/>
+      <c r="H284" s="4" t="n"/>
+      <c r="I284" s="4" t="n"/>
+      <c r="J284" s="4" t="n"/>
+      <c r="K284" s="4" t="n"/>
+      <c r="L284" s="4" t="n"/>
+      <c r="M284" s="4" t="n"/>
+      <c r="N284" s="4" t="n"/>
+      <c r="O284" s="4" t="n"/>
+      <c r="P284" s="4" t="n"/>
+      <c r="Q284" s="4" t="n"/>
+      <c r="R284" s="4" t="n"/>
+      <c r="S284" s="4" t="n"/>
+      <c r="T284" s="4" t="n"/>
+      <c r="U284" s="4" t="n"/>
+      <c r="V284" s="4" t="n"/>
+      <c r="W284" s="4" t="n"/>
+      <c r="X284" s="4" t="n"/>
+      <c r="Y284" s="4" t="n"/>
+      <c r="Z284" s="4" t="n"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="A285" s="4" t="n"/>
+      <c r="B285" s="4" t="n"/>
+      <c r="C285" s="4" t="n"/>
+      <c r="D285" s="4" t="n"/>
+      <c r="E285" s="4" t="n"/>
+      <c r="F285" s="4" t="n"/>
+      <c r="G285" s="4" t="n"/>
+      <c r="H285" s="4" t="n"/>
+      <c r="I285" s="4" t="n"/>
+      <c r="J285" s="4" t="n"/>
+      <c r="K285" s="4" t="n"/>
+      <c r="L285" s="4" t="n"/>
+      <c r="M285" s="4" t="n"/>
+      <c r="N285" s="4" t="n"/>
+      <c r="O285" s="4" t="n"/>
+      <c r="P285" s="4" t="n"/>
+      <c r="Q285" s="4" t="n"/>
+      <c r="R285" s="4" t="n"/>
+      <c r="S285" s="4" t="n"/>
+      <c r="T285" s="4" t="n"/>
+      <c r="U285" s="4" t="n"/>
+      <c r="V285" s="4" t="n"/>
+      <c r="W285" s="4" t="n"/>
+      <c r="X285" s="4" t="n"/>
+      <c r="Y285" s="4" t="n"/>
+      <c r="Z285" s="4" t="n"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="A286" s="4" t="n"/>
+      <c r="B286" s="4" t="n"/>
+      <c r="C286" s="4" t="n"/>
+      <c r="D286" s="4" t="n"/>
+      <c r="E286" s="4" t="n"/>
+      <c r="F286" s="4" t="n"/>
+      <c r="G286" s="4" t="n"/>
+      <c r="H286" s="4" t="n"/>
+      <c r="I286" s="4" t="n"/>
+      <c r="J286" s="4" t="n"/>
+      <c r="K286" s="4" t="n"/>
+      <c r="L286" s="4" t="n"/>
+      <c r="M286" s="4" t="n"/>
+      <c r="N286" s="4" t="n"/>
+      <c r="O286" s="4" t="n"/>
+      <c r="P286" s="4" t="n"/>
+      <c r="Q286" s="4" t="n"/>
+      <c r="R286" s="4" t="n"/>
+      <c r="S286" s="4" t="n"/>
+      <c r="T286" s="4" t="n"/>
+      <c r="U286" s="4" t="n"/>
+      <c r="V286" s="4" t="n"/>
+      <c r="W286" s="4" t="n"/>
+      <c r="X286" s="4" t="n"/>
+      <c r="Y286" s="4" t="n"/>
+      <c r="Z286" s="4" t="n"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="A287" s="4" t="n"/>
+      <c r="B287" s="4" t="n"/>
+      <c r="C287" s="4" t="n"/>
+      <c r="D287" s="4" t="n"/>
+      <c r="E287" s="4" t="n"/>
+      <c r="F287" s="4" t="n"/>
+      <c r="G287" s="4" t="n"/>
+      <c r="H287" s="4" t="n"/>
+      <c r="I287" s="4" t="n"/>
+      <c r="J287" s="4" t="n"/>
+      <c r="K287" s="4" t="n"/>
+      <c r="L287" s="4" t="n"/>
+      <c r="M287" s="4" t="n"/>
+      <c r="N287" s="4" t="n"/>
+      <c r="O287" s="4" t="n"/>
+      <c r="P287" s="4" t="n"/>
+      <c r="Q287" s="4" t="n"/>
+      <c r="R287" s="4" t="n"/>
+      <c r="S287" s="4" t="n"/>
+      <c r="T287" s="4" t="n"/>
+      <c r="U287" s="4" t="n"/>
+      <c r="V287" s="4" t="n"/>
+      <c r="W287" s="4" t="n"/>
+      <c r="X287" s="4" t="n"/>
+      <c r="Y287" s="4" t="n"/>
+      <c r="Z287" s="4" t="n"/>
+    </row>
     <row r="288" ht="15.75" customHeight="1"/>
     <row r="289" ht="15.75" customHeight="1"/>
     <row r="290" ht="15.75" customHeight="1"/>
@@ -10877,63 +10985,65 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="A83:K83"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="B52:B53"/>
+  <mergeCells count="60">
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
     <mergeCell ref="E91:H91"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="I93:K93"/>
     <mergeCell ref="A2:A8"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A79:K79"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B30:B34"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="A17:A34"/>
-    <mergeCell ref="B30:B34"/>
     <mergeCell ref="A39:A48"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A85:C85"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="E96:H96"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A76:A79"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="E92:H92"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B39:B48"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="B54:B64"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="A59:A69"/>
+    <mergeCell ref="I90:K90"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I86:K86"/>
     <mergeCell ref="A91:B91"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="I89:K89"/>
-    <mergeCell ref="A52:A53"/>
     <mergeCell ref="I91:K91"/>
     <mergeCell ref="B21:B29"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="A54:A64"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="B59:B69"/>
     <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B35:B38"/>
     <mergeCell ref="E89:H89"/>
     <mergeCell ref="K2:K6"/>
   </mergeCells>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -582,7 +582,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1027,11 +1027,32 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1603,6 +1624,8 @@
     <xf numFmtId="166" fontId="31" fillId="35" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3735,7 +3758,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3757,7 +3780,9 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="227" t="n"/>
+      <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
         <is>
           <t>특정순환계질환 주요치료 혈전용해 (연 1회)</t>
@@ -3772,7 +3797,9 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="227" t="n"/>
+      <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
         <is>
           <t>특정순환계질환 주요치료 혈전제거 (연 1회)</t>
@@ -3787,7 +3814,9 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="227" t="n"/>
+      <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
         <is>
           <t>특정순환계질환 주요치료 혈전복합 (연 1회)</t>
@@ -3802,7 +3831,9 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="228" t="n"/>
+      <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
         <is>
           <t>특정순환계질환 주요치료 중환자실 (연 1회)</t>
@@ -4685,7 +4716,7 @@
       <c r="Y77" s="4" t="n"/>
       <c r="Z77" s="4" t="n"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15" customHeight="1">
       <c r="A78" s="181" t="n"/>
       <c r="B78" s="181" t="n"/>
       <c r="C78" s="118" t="inlineStr">
@@ -4720,7 +4751,7 @@
       <c r="Y78" s="4" t="n"/>
       <c r="Z78" s="4" t="n"/>
     </row>
-    <row r="79" ht="22" customHeight="1">
+    <row r="79" ht="15" customHeight="1">
       <c r="A79" s="182" t="n"/>
       <c r="B79" s="182" t="n"/>
       <c r="C79" s="121" t="inlineStr">
@@ -4792,7 +4823,7 @@
       <c r="Y80" s="4" t="n"/>
       <c r="Z80" s="4" t="n"/>
     </row>
-    <row r="81" ht="26" customHeight="1">
+    <row r="81" ht="22" customHeight="1">
       <c r="A81" s="181" t="n"/>
       <c r="B81" s="162" t="inlineStr">
         <is>
@@ -4829,7 +4860,7 @@
       <c r="Y81" s="4" t="n"/>
       <c r="Z81" s="4" t="n"/>
     </row>
-    <row r="82" ht="7.5" customHeight="1">
+    <row r="82" ht="22" customHeight="1">
       <c r="A82" s="182" t="n"/>
       <c r="B82" s="159" t="inlineStr">
         <is>
@@ -4885,7 +4916,7 @@
       <c r="Y82" s="4" t="n"/>
       <c r="Z82" s="4" t="n"/>
     </row>
-    <row r="83" ht="28" customHeight="1">
+    <row r="83" ht="7.5" customHeight="1">
       <c r="A83" s="48" t="n"/>
       <c r="B83" s="49" t="n"/>
       <c r="C83" s="49" t="n"/>
@@ -4913,7 +4944,7 @@
       <c r="Y83" s="4" t="n"/>
       <c r="Z83" s="4" t="n"/>
     </row>
-    <row r="84" ht="20" customHeight="1">
+    <row r="84" ht="28" customHeight="1">
       <c r="A84" s="208" t="inlineStr">
         <is>
           <t>🔄  갱신형 / 비갱신형 구분</t>
@@ -4942,7 +4973,7 @@
       <c r="Y84" s="4" t="n"/>
       <c r="Z84" s="4" t="n"/>
     </row>
-    <row r="85" ht="70" customHeight="1">
+    <row r="85" ht="20" customHeight="1">
       <c r="A85" s="209" t="inlineStr">
         <is>
           <t>갱신 구분</t>
@@ -4971,7 +5002,7 @@
       <c r="Y85" s="4" t="n"/>
       <c r="Z85" s="4" t="n"/>
     </row>
-    <row r="86" ht="70" customHeight="1">
+    <row r="86" ht="26" customHeight="1">
       <c r="A86" s="209" t="inlineStr">
         <is>
           <t>보험료
@@ -5001,7 +5032,7 @@
       <c r="Y86" s="4" t="n"/>
       <c r="Z86" s="4" t="n"/>
     </row>
-    <row r="87" ht="70" customHeight="1">
+    <row r="87" ht="7.5" customHeight="1">
       <c r="O87" s="4" t="n"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
@@ -5015,7 +5046,7 @@
       <c r="Y87" s="4" t="n"/>
       <c r="Z87" s="4" t="n"/>
     </row>
-    <row r="88" ht="70" customHeight="1">
+    <row r="88" ht="28" customHeight="1">
       <c r="A88" s="212" t="inlineStr">
         <is>
           <t>📋  현재 유지중인 보험 리뷰</t>
@@ -5044,7 +5075,7 @@
       <c r="Y88" s="4" t="n"/>
       <c r="Z88" s="4" t="n"/>
     </row>
-    <row r="89" ht="70" customHeight="1">
+    <row r="89" ht="20" customHeight="1">
       <c r="A89" s="209" t="inlineStr">
         <is>
           <t>보험사 / 상품명</t>
@@ -5139,7 +5170,7 @@
       <c r="Y91" s="4" t="n"/>
       <c r="Z91" s="4" t="n"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="70" customHeight="1">
       <c r="A92" s="217" t="n"/>
       <c r="B92" s="214" t="n"/>
       <c r="C92" s="217" t="n"/>
@@ -5164,7 +5195,7 @@
       <c r="Y92" s="4" t="n"/>
       <c r="Z92" s="4" t="n"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="70" customHeight="1">
       <c r="A93" s="218" t="n"/>
       <c r="B93" s="214" t="n"/>
       <c r="C93" s="218" t="n"/>
@@ -5189,7 +5220,7 @@
       <c r="Y93" s="4" t="n"/>
       <c r="Z93" s="4" t="n"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="70" customHeight="1">
       <c r="A94" s="219" t="n"/>
       <c r="B94" s="214" t="n"/>
       <c r="C94" s="219" t="n"/>
@@ -5214,7 +5245,7 @@
       <c r="Y94" s="4" t="n"/>
       <c r="Z94" s="4" t="n"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="70" customHeight="1">
       <c r="A95" s="220" t="n"/>
       <c r="B95" s="214" t="n"/>
       <c r="C95" s="220" t="n"/>
@@ -5239,7 +5270,7 @@
       <c r="Y95" s="4" t="n"/>
       <c r="Z95" s="4" t="n"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="70" customHeight="1">
       <c r="A96" s="221" t="n"/>
       <c r="B96" s="214" t="n"/>
       <c r="C96" s="221" t="n"/>
@@ -10997,8 +11028,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -11027,8 +11027,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11082,7 +11082,7 @@
   <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="78" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -11027,9 +11027,9 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11082,7 +11082,7 @@
   <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="84" min="0" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2051,7 +2051,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
@@ -11028,8 +11028,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11080,7 +11080,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="8" scale="65" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>
   </rowBreaks>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2051,7 +2051,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
@@ -11027,8 +11027,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11080,7 +11080,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="8" scale="65" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="8" scale="65" fitToHeight="0" fitToWidth="0"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>
   </rowBreaks>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2051,7 +2051,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr autoPageBreaks="0" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
@@ -11027,9 +11027,9 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11080,7 +11080,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="8" scale="65" fitToHeight="0" fitToWidth="0"/>
+  <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>
   </rowBreaks>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -3074,7 +3074,7 @@
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="181" t="n"/>
       <c r="B31" s="181" t="n"/>
       <c r="C31" s="118" t="inlineStr">
@@ -3150,7 +3150,7 @@
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="181" t="n"/>
       <c r="B32" s="181" t="n"/>
       <c r="C32" s="121" t="inlineStr">
@@ -3186,7 +3186,7 @@
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="20" customHeight="1">
       <c r="A33" s="181" t="n"/>
       <c r="B33" s="181" t="n"/>
       <c r="C33" s="118" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="182" t="n"/>
       <c r="B34" s="182" t="n"/>
       <c r="C34" s="121" t="inlineStr">
@@ -3758,7 +3758,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
@@ -3797,7 +3797,7 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="20" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
@@ -3814,7 +3814,7 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
@@ -3831,7 +3831,7 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="Y79" s="4" t="n"/>
       <c r="Z79" s="4" t="n"/>
     </row>
-    <row r="80" ht="22" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="158" t="n"/>
       <c r="B80" s="159" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       <c r="Y80" s="4" t="n"/>
       <c r="Z80" s="4" t="n"/>
     </row>
-    <row r="81" ht="22" customHeight="1">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="181" t="n"/>
       <c r="B81" s="162" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       <c r="Y81" s="4" t="n"/>
       <c r="Z81" s="4" t="n"/>
     </row>
-    <row r="82" ht="22" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="182" t="n"/>
       <c r="B82" s="159" t="inlineStr">
         <is>
@@ -11028,8 +11028,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -11027,8 +11027,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11079,7 +11079,7 @@
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.15" bottom="0.15" header="0" footer="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -3074,7 +3074,7 @@
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="25" customHeight="1">
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="25" customHeight="1">
       <c r="A31" s="181" t="n"/>
       <c r="B31" s="181" t="n"/>
       <c r="C31" s="118" t="inlineStr">
@@ -3150,7 +3150,7 @@
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="25" customHeight="1">
       <c r="A32" s="181" t="n"/>
       <c r="B32" s="181" t="n"/>
       <c r="C32" s="121" t="inlineStr">
@@ -3186,7 +3186,7 @@
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" ht="25" customHeight="1">
       <c r="A33" s="181" t="n"/>
       <c r="B33" s="181" t="n"/>
       <c r="C33" s="118" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="25" customHeight="1">
       <c r="A34" s="182" t="n"/>
       <c r="B34" s="182" t="n"/>
       <c r="C34" s="121" t="inlineStr">
@@ -3758,7 +3758,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="25" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3768,7 +3768,8 @@
       </c>
       <c r="C49" s="223" t="inlineStr">
         <is>
-          <t>특정순환계 주요치료 수술 (연 1회)</t>
+          <t>특정순환계 주요치료
+수술 (연 1회)</t>
         </is>
       </c>
       <c r="D49" s="224" t="n"/>
@@ -3780,12 +3781,13 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="25" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료 혈전용해 (연 1회)</t>
+          <t>특정순환계질환 주요치료
+혈전용해 (연 1회)</t>
         </is>
       </c>
       <c r="D50" s="226" t="n"/>
@@ -3797,12 +3799,13 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51" ht="25" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료 혈전제거 (연 1회)</t>
+          <t>특정순환계질환 주요치료
+혈전제거 (연 1회)</t>
         </is>
       </c>
       <c r="D51" s="224" t="n"/>
@@ -3814,12 +3817,13 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="25" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료 혈전복합 (연 1회)</t>
+          <t>특정순환계질환 주요치료
+혈전복합 (연 1회)</t>
         </is>
       </c>
       <c r="D52" s="226" t="n"/>
@@ -3831,12 +3835,13 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="25" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료 중환자실 (연 1회)</t>
+          <t>특정순환계질환 주요치료
+중환자실 (연 1회)</t>
         </is>
       </c>
       <c r="D53" s="224" t="n"/>
@@ -11027,8 +11032,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="B49:B53"/>
     <mergeCell ref="A86:C86"/>
-    <mergeCell ref="B49:B53"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11079,7 +11084,7 @@
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.15" header="0" footer="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2064,7 +2064,7 @@
     <col width="12.6640625" customWidth="1" style="5" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1" ht="17" customHeight="1">
       <c r="A1" s="95" t="inlineStr">
         <is>
           <t>님(남/여 - 세)을 위한 보장분석</t>
@@ -2091,7 +2091,7 @@
       <c r="Y1" s="4" t="n"/>
       <c r="Z1" s="4" t="n"/>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="13" customHeight="1">
       <c r="A2" s="97" t="n"/>
       <c r="B2" s="98" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="13" customHeight="1">
       <c r="A3" s="180" t="n"/>
       <c r="B3" s="181" t="n"/>
       <c r="C3" s="102" t="inlineStr">
@@ -2163,7 +2163,7 @@
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="13" customHeight="1">
       <c r="A4" s="180" t="n"/>
       <c r="B4" s="181" t="n"/>
       <c r="C4" s="98" t="inlineStr">
@@ -2195,7 +2195,7 @@
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="13" customHeight="1">
       <c r="A5" s="180" t="n"/>
       <c r="B5" s="181" t="n"/>
       <c r="C5" s="102" t="inlineStr">
@@ -2227,7 +2227,7 @@
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="13" customHeight="1">
       <c r="A6" s="180" t="n"/>
       <c r="B6" s="182" t="n"/>
       <c r="C6" s="98" t="inlineStr">
@@ -2259,7 +2259,7 @@
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="13" customHeight="1">
       <c r="A7" s="180" t="n"/>
       <c r="B7" s="102" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
     </row>
-    <row r="8" hidden="1" ht="15.75" customHeight="1">
+    <row r="8" hidden="1" ht="10" customHeight="1">
       <c r="A8" s="183" t="n"/>
       <c r="B8" s="109" t="n"/>
       <c r="C8" s="109" t="n"/>
@@ -3074,7 +3074,7 @@
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
     </row>
-    <row r="30" ht="25" customHeight="1">
+    <row r="30" ht="27" customHeight="1">
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
@@ -3083,8 +3083,8 @@
       </c>
       <c r="C30" s="121" t="inlineStr">
         <is>
-          <t>상급종합병원암주치 
-수술 (연간 1회)</t>
+          <t>상급병원 암주치
+수술 (연 1회)</t>
         </is>
       </c>
       <c r="D30" s="122" t="n"/>
@@ -3114,13 +3114,13 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
     </row>
-    <row r="31" ht="25" customHeight="1">
+    <row r="31" ht="27" customHeight="1">
       <c r="A31" s="181" t="n"/>
       <c r="B31" s="181" t="n"/>
       <c r="C31" s="118" t="inlineStr">
         <is>
-          <t>상급종합병원암주치 
-항암약물 (연간 1회)</t>
+          <t>상급병원 암주치
+항암약물 (연 1회)</t>
         </is>
       </c>
       <c r="D31" s="119" t="n"/>
@@ -3150,13 +3150,13 @@
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
     </row>
-    <row r="32" ht="25" customHeight="1">
+    <row r="32" ht="27" customHeight="1">
       <c r="A32" s="181" t="n"/>
       <c r="B32" s="181" t="n"/>
       <c r="C32" s="121" t="inlineStr">
         <is>
-          <t>상급종합병원암주치 
-항암방사선 (연간 1회)</t>
+          <t>상급병원 암주치
+항암방사선 (연 1회)</t>
         </is>
       </c>
       <c r="D32" s="122" t="n"/>
@@ -3186,13 +3186,13 @@
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
     </row>
-    <row r="33" ht="25" customHeight="1">
+    <row r="33" ht="27" customHeight="1">
       <c r="A33" s="181" t="n"/>
       <c r="B33" s="181" t="n"/>
       <c r="C33" s="118" t="inlineStr">
         <is>
-          <t>상급종합병원암주치 
-항암복합 (연간 1회)</t>
+          <t>상급병원 암주치
+항암복합 (연 1회)</t>
         </is>
       </c>
       <c r="D33" s="119" t="n"/>
@@ -3222,13 +3222,13 @@
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
     </row>
-    <row r="34" ht="25" customHeight="1">
+    <row r="34" ht="27" customHeight="1">
       <c r="A34" s="182" t="n"/>
       <c r="B34" s="182" t="n"/>
       <c r="C34" s="121" t="inlineStr">
         <is>
-          <t>비급여 종합병원 
-암주요치료비 (연간 1회)</t>
+          <t>비급여 종합병원
+암주요치료 (연 1회)</t>
         </is>
       </c>
       <c r="D34" s="122" t="n"/>
@@ -3758,7 +3758,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="25" customHeight="1">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="25" customHeight="1">
+    <row r="50" ht="27" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
@@ -3799,7 +3799,7 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="25" customHeight="1">
+    <row r="51" ht="27" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
@@ -3817,7 +3817,7 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="25" customHeight="1">
+    <row r="52" ht="27" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
@@ -3835,7 +3835,7 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="25" customHeight="1">
+    <row r="53" ht="27" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
@@ -4921,7 +4921,7 @@
       <c r="Y82" s="4" t="n"/>
       <c r="Z82" s="4" t="n"/>
     </row>
-    <row r="83" ht="7.5" customHeight="1">
+    <row r="83" ht="5" customHeight="1">
       <c r="A83" s="48" t="n"/>
       <c r="B83" s="49" t="n"/>
       <c r="C83" s="49" t="n"/>
@@ -11033,8 +11033,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="B54:B56"/>
     <mergeCell ref="A86:C86"/>
-    <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11084,7 +11084,7 @@
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.15" header="0" footer="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2064,7 +2064,7 @@
     <col width="12.6640625" customWidth="1" style="5" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="95" t="inlineStr">
         <is>
           <t>님(남/여 - 세)을 위한 보장분석</t>
@@ -2091,7 +2091,7 @@
       <c r="Y1" s="4" t="n"/>
       <c r="Z1" s="4" t="n"/>
     </row>
-    <row r="2" ht="13" customHeight="1">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="97" t="n"/>
       <c r="B2" s="98" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       <c r="Y2" s="4" t="n"/>
       <c r="Z2" s="4" t="n"/>
     </row>
-    <row r="3" ht="13" customHeight="1">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="180" t="n"/>
       <c r="B3" s="181" t="n"/>
       <c r="C3" s="102" t="inlineStr">
@@ -2163,7 +2163,7 @@
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
     </row>
-    <row r="4" ht="13" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="180" t="n"/>
       <c r="B4" s="181" t="n"/>
       <c r="C4" s="98" t="inlineStr">
@@ -2195,7 +2195,7 @@
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
     </row>
-    <row r="5" ht="13" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="180" t="n"/>
       <c r="B5" s="181" t="n"/>
       <c r="C5" s="102" t="inlineStr">
@@ -2227,7 +2227,7 @@
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
     </row>
-    <row r="6" ht="13" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="180" t="n"/>
       <c r="B6" s="182" t="n"/>
       <c r="C6" s="98" t="inlineStr">
@@ -2259,7 +2259,7 @@
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
     </row>
-    <row r="7" ht="13" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="180" t="n"/>
       <c r="B7" s="102" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
     </row>
-    <row r="30" ht="27" customHeight="1">
+    <row r="30" ht="25" customHeight="1">
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
     </row>
-    <row r="31" ht="27" customHeight="1">
+    <row r="31" ht="25" customHeight="1">
       <c r="A31" s="181" t="n"/>
       <c r="B31" s="181" t="n"/>
       <c r="C31" s="118" t="inlineStr">
@@ -3150,7 +3150,7 @@
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
     </row>
-    <row r="32" ht="27" customHeight="1">
+    <row r="32" ht="25" customHeight="1">
       <c r="A32" s="181" t="n"/>
       <c r="B32" s="181" t="n"/>
       <c r="C32" s="121" t="inlineStr">
@@ -3186,7 +3186,7 @@
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
     </row>
-    <row r="33" ht="27" customHeight="1">
+    <row r="33" ht="25" customHeight="1">
       <c r="A33" s="181" t="n"/>
       <c r="B33" s="181" t="n"/>
       <c r="C33" s="118" t="inlineStr">
@@ -3222,7 +3222,7 @@
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
     </row>
-    <row r="34" ht="27" customHeight="1">
+    <row r="34" ht="25" customHeight="1">
       <c r="A34" s="182" t="n"/>
       <c r="B34" s="182" t="n"/>
       <c r="C34" s="121" t="inlineStr">
@@ -3758,7 +3758,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="27" customHeight="1">
+    <row r="49" ht="25" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50" ht="25" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
@@ -3799,7 +3799,7 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="27" customHeight="1">
+    <row r="51" ht="25" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
@@ -3817,7 +3817,7 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="27" customHeight="1">
+    <row r="52" ht="25" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
@@ -3835,7 +3835,7 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="27" customHeight="1">
+    <row r="53" ht="25" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
@@ -4791,7 +4791,7 @@
       <c r="Y79" s="4" t="n"/>
       <c r="Z79" s="4" t="n"/>
     </row>
-    <row r="80" ht="18" customHeight="1">
+    <row r="80" ht="15" customHeight="1">
       <c r="A80" s="158" t="n"/>
       <c r="B80" s="159" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
       <c r="Y80" s="4" t="n"/>
       <c r="Z80" s="4" t="n"/>
     </row>
-    <row r="81" ht="18" customHeight="1">
+    <row r="81" ht="15" customHeight="1">
       <c r="A81" s="181" t="n"/>
       <c r="B81" s="162" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
       <c r="Y81" s="4" t="n"/>
       <c r="Z81" s="4" t="n"/>
     </row>
-    <row r="82" ht="18" customHeight="1">
+    <row r="82" ht="15" customHeight="1">
       <c r="A82" s="182" t="n"/>
       <c r="B82" s="159" t="inlineStr">
         <is>
@@ -11033,8 +11033,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11084,7 +11084,7 @@
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.15" header="0" footer="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.2" bottom="0.15" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="84" min="0" max="16383" man="1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2058,7 +2058,7 @@
   <cols>
     <col hidden="1" width="3" customWidth="1" style="5" min="1" max="1"/>
     <col width="15.88671875" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20.21875" customWidth="1" style="5" min="3" max="3"/>
+    <col width="23" customWidth="1" style="5" min="3" max="3"/>
     <col width="15.109375" customWidth="1" style="5" min="4" max="10"/>
     <col width="17.88671875" customWidth="1" style="5" min="11" max="11"/>
     <col width="12.6640625" customWidth="1" style="5" min="12" max="16384"/>
@@ -3074,7 +3074,7 @@
       <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
     </row>
-    <row r="30" ht="25" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
@@ -3083,8 +3083,7 @@
       </c>
       <c r="C30" s="121" t="inlineStr">
         <is>
-          <t>상급병원 암주치
-수술 (연 1회)</t>
+          <t>상급병원 암주치 수술</t>
         </is>
       </c>
       <c r="D30" s="122" t="n"/>
@@ -3114,13 +3113,12 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
     </row>
-    <row r="31" ht="25" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="181" t="n"/>
       <c r="B31" s="181" t="n"/>
       <c r="C31" s="118" t="inlineStr">
         <is>
-          <t>상급병원 암주치
-항암약물 (연 1회)</t>
+          <t>상급병원 암주치 항암약물</t>
         </is>
       </c>
       <c r="D31" s="119" t="n"/>
@@ -3150,13 +3148,12 @@
       <c r="Y31" s="4" t="n"/>
       <c r="Z31" s="4" t="n"/>
     </row>
-    <row r="32" ht="25" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="181" t="n"/>
       <c r="B32" s="181" t="n"/>
       <c r="C32" s="121" t="inlineStr">
         <is>
-          <t>상급병원 암주치
-항암방사선 (연 1회)</t>
+          <t>상급병원 암주치 항암방사선</t>
         </is>
       </c>
       <c r="D32" s="122" t="n"/>
@@ -3186,13 +3183,12 @@
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
     </row>
-    <row r="33" ht="25" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="181" t="n"/>
       <c r="B33" s="181" t="n"/>
       <c r="C33" s="118" t="inlineStr">
         <is>
-          <t>상급병원 암주치
-항암복합 (연 1회)</t>
+          <t>상급병원 암주치 항암복합</t>
         </is>
       </c>
       <c r="D33" s="119" t="n"/>
@@ -3222,13 +3218,12 @@
       <c r="Y33" s="4" t="n"/>
       <c r="Z33" s="4" t="n"/>
     </row>
-    <row r="34" ht="25" customHeight="1">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="182" t="n"/>
       <c r="B34" s="182" t="n"/>
       <c r="C34" s="121" t="inlineStr">
         <is>
-          <t>비급여 종합병원
-암주요치료 (연 1회)</t>
+          <t>비급여 종합병원 암주요치료</t>
         </is>
       </c>
       <c r="D34" s="122" t="n"/>
@@ -3758,7 +3753,7 @@
       <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
     </row>
-    <row r="49" ht="25" customHeight="1">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="222" t="n"/>
       <c r="B49" s="222" t="inlineStr">
         <is>
@@ -3768,8 +3763,7 @@
       </c>
       <c r="C49" s="223" t="inlineStr">
         <is>
-          <t>특정순환계 주요치료
-수술 (연 1회)</t>
+          <t>특정순환계 수술</t>
         </is>
       </c>
       <c r="D49" s="224" t="n"/>
@@ -3781,13 +3775,12 @@
       <c r="J49" s="224" t="n"/>
       <c r="K49" s="224" t="n"/>
     </row>
-    <row r="50" ht="25" customHeight="1">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
       <c r="C50" s="225" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료
-혈전용해 (연 1회)</t>
+          <t>특정순환계 혈전용해</t>
         </is>
       </c>
       <c r="D50" s="226" t="n"/>
@@ -3799,13 +3792,12 @@
       <c r="J50" s="226" t="n"/>
       <c r="K50" s="226" t="n"/>
     </row>
-    <row r="51" ht="25" customHeight="1">
+    <row r="51" ht="15" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
       <c r="C51" s="223" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료
-혈전제거 (연 1회)</t>
+          <t>특정순환계 혈전제거</t>
         </is>
       </c>
       <c r="D51" s="224" t="n"/>
@@ -3817,13 +3809,12 @@
       <c r="J51" s="224" t="n"/>
       <c r="K51" s="224" t="n"/>
     </row>
-    <row r="52" ht="25" customHeight="1">
+    <row r="52" ht="15" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
       <c r="C52" s="225" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료
-혈전복합 (연 1회)</t>
+          <t>특정순환계 혈전복합</t>
         </is>
       </c>
       <c r="D52" s="226" t="n"/>
@@ -3835,13 +3826,12 @@
       <c r="J52" s="226" t="n"/>
       <c r="K52" s="226" t="n"/>
     </row>
-    <row r="53" ht="25" customHeight="1">
+    <row r="53" ht="15" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
       <c r="C53" s="223" t="inlineStr">
         <is>
-          <t>특정순환계질환 주요치료
-중환자실 (연 1회)</t>
+          <t>특정순환계 중환자실</t>
         </is>
       </c>
       <c r="D53" s="224" t="n"/>
@@ -11032,8 +11022,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11084,10 +11074,10 @@
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.2" bottom="0.15" header="0" footer="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.2" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="84" min="0" max="16383" man="1"/>
+    <brk id="88" min="0" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -3078,7 +3078,8 @@
       <c r="A30" s="181" t="n"/>
       <c r="B30" s="118" t="inlineStr">
         <is>
-          <t>암 주요치료비</t>
+          <t>암 주요치료비
+(연 1회)</t>
         </is>
       </c>
       <c r="C30" s="121" t="inlineStr">
@@ -3758,7 +3759,8 @@
       <c r="B49" s="222" t="inlineStr">
         <is>
           <t>특정순환계질환
-주요치료비</t>
+주요치료비
+(연 1회)</t>
         </is>
       </c>
       <c r="C49" s="223" t="inlineStr">
@@ -11022,9 +11024,9 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -11025,8 +11025,8 @@
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
     <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="B57:B58"/>
@@ -11079,7 +11079,7 @@
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.2" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="88" min="0" max="16383" man="1"/>
+    <brk id="87" min="0" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -11024,8 +11024,8 @@
     <mergeCell ref="A94:B94"/>
     <mergeCell ref="I92:K92"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="E93:H93"/>
     <mergeCell ref="A88:K88"/>
@@ -11079,7 +11079,7 @@
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.2" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="87" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -1052,7 +1052,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1626,6 +1626,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2053,7 +2056,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z287"/>
+  <dimension ref="A1:Z289"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="3" customWidth="1" style="5" min="1" max="1"/>
@@ -3444,7 +3447,7 @@
       <c r="B40" s="181" t="n"/>
       <c r="C40" s="137" t="inlineStr">
         <is>
-          <t>뇌경색</t>
+          <t>뇌졸중</t>
         </is>
       </c>
       <c r="D40" s="138" t="n"/>
@@ -3479,7 +3482,7 @@
       <c r="B41" s="181" t="n"/>
       <c r="C41" s="134" t="inlineStr">
         <is>
-          <t>뇌졸중</t>
+          <t>뇌경색</t>
         </is>
       </c>
       <c r="D41" s="135" t="n"/>
@@ -3763,7 +3766,7 @@
 (연 1회)</t>
         </is>
       </c>
-      <c r="C49" s="223" t="inlineStr">
+      <c r="C49" s="222" t="inlineStr">
         <is>
           <t>특정순환계 수술</t>
         </is>
@@ -3780,7 +3783,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="227" t="n"/>
       <c r="B50" s="227" t="n"/>
-      <c r="C50" s="225" t="inlineStr">
+      <c r="C50" s="229" t="inlineStr">
         <is>
           <t>특정순환계 혈전용해</t>
         </is>
@@ -3797,7 +3800,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="227" t="n"/>
       <c r="B51" s="227" t="n"/>
-      <c r="C51" s="223" t="inlineStr">
+      <c r="C51" s="222" t="inlineStr">
         <is>
           <t>특정순환계 혈전제거</t>
         </is>
@@ -3814,7 +3817,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="227" t="n"/>
       <c r="B52" s="227" t="n"/>
-      <c r="C52" s="225" t="inlineStr">
+      <c r="C52" s="229" t="inlineStr">
         <is>
           <t>특정순환계 혈전복합</t>
         </is>
@@ -3831,7 +3834,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="228" t="n"/>
       <c r="B53" s="228" t="n"/>
-      <c r="C53" s="223" t="inlineStr">
+      <c r="C53" s="222" t="inlineStr">
         <is>
           <t>특정순환계 중환자실</t>
         </is>
@@ -3887,55 +3890,39 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="181" t="n"/>
       <c r="B55" s="181" t="n"/>
-      <c r="C55" s="137" t="inlineStr">
+      <c r="C55" s="134" t="inlineStr">
+        <is>
+          <t>재해 수술</t>
+        </is>
+      </c>
+      <c r="D55" s="135" t="n"/>
+      <c r="E55" s="135" t="n"/>
+      <c r="F55" s="135" t="n"/>
+      <c r="G55" s="135" t="n"/>
+      <c r="H55" s="135" t="n"/>
+      <c r="I55" s="135" t="n"/>
+      <c r="J55" s="135" t="n"/>
+      <c r="K55" s="135" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="181" t="n"/>
+      <c r="B56" s="181" t="n"/>
+      <c r="C56" s="137" t="inlineStr">
         <is>
           <t>질병수술비 1-5종</t>
         </is>
       </c>
-      <c r="D55" s="138" t="n"/>
-      <c r="E55" s="138" t="n"/>
-      <c r="F55" s="138" t="n"/>
-      <c r="G55" s="138" t="n"/>
-      <c r="H55" s="138" t="n"/>
-      <c r="I55" s="138" t="n"/>
-      <c r="J55" s="138" t="n"/>
-      <c r="K55" s="138">
+      <c r="D56" s="138" t="n"/>
+      <c r="E56" s="138" t="n"/>
+      <c r="F56" s="138" t="n"/>
+      <c r="G56" s="138" t="n"/>
+      <c r="H56" s="138" t="n"/>
+      <c r="I56" s="138" t="n"/>
+      <c r="J56" s="138" t="n"/>
+      <c r="K56" s="138">
         <f>SUM(D50:J50)</f>
-        <v/>
-      </c>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="4" t="n"/>
-      <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
-      <c r="R55" s="4" t="n"/>
-      <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
-      <c r="U55" s="4" t="n"/>
-      <c r="V55" s="4" t="n"/>
-      <c r="W55" s="4" t="n"/>
-      <c r="X55" s="4" t="n"/>
-      <c r="Y55" s="4" t="n"/>
-      <c r="Z55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="181" t="n"/>
-      <c r="B56" s="181" t="n"/>
-      <c r="C56" s="134" t="inlineStr">
-        <is>
-          <t>재해수술비 1-5종</t>
-        </is>
-      </c>
-      <c r="D56" s="135" t="n"/>
-      <c r="E56" s="135" t="n"/>
-      <c r="F56" s="135" t="n"/>
-      <c r="G56" s="135" t="n"/>
-      <c r="H56" s="135" t="n"/>
-      <c r="I56" s="135" t="n"/>
-      <c r="J56" s="135" t="n"/>
-      <c r="K56" s="135">
-        <f>SUM(D51:J51)</f>
         <v/>
       </c>
       <c r="L56" s="4" t="n"/>
@@ -3955,26 +3942,22 @@
       <c r="Z56" s="4" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="111" t="n"/>
-      <c r="B57" s="111" t="inlineStr">
+      <c r="A57" s="181" t="n"/>
+      <c r="B57" s="181" t="n"/>
+      <c r="C57" s="134" t="inlineStr">
         <is>
-          <t>골절 / 깁스</t>
+          <t>재해수술비 1-5종</t>
         </is>
       </c>
-      <c r="C57" s="111" t="inlineStr">
-        <is>
-          <t>골절</t>
-        </is>
-      </c>
-      <c r="D57" s="112" t="n"/>
-      <c r="E57" s="112" t="n"/>
-      <c r="F57" s="112" t="n"/>
-      <c r="G57" s="112" t="n"/>
-      <c r="H57" s="112" t="n"/>
-      <c r="I57" s="112" t="n"/>
-      <c r="J57" s="112" t="n"/>
-      <c r="K57" s="112">
-        <f>SUM(D52:J52)</f>
+      <c r="D57" s="135" t="n"/>
+      <c r="E57" s="135" t="n"/>
+      <c r="F57" s="135" t="n"/>
+      <c r="G57" s="135" t="n"/>
+      <c r="H57" s="135" t="n"/>
+      <c r="I57" s="135" t="n"/>
+      <c r="J57" s="135" t="n"/>
+      <c r="K57" s="135">
+        <f>SUM(D51:J51)</f>
         <v/>
       </c>
       <c r="L57" s="4" t="n"/>
@@ -3994,22 +3977,26 @@
       <c r="Z57" s="4" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="182" t="n"/>
-      <c r="B58" s="182" t="n"/>
-      <c r="C58" s="114" t="inlineStr">
+      <c r="A58" s="111" t="n"/>
+      <c r="B58" s="111" t="inlineStr">
         <is>
-          <t>깁스</t>
+          <t>골절 / 깁스</t>
         </is>
       </c>
-      <c r="D58" s="115" t="n"/>
-      <c r="E58" s="115" t="n"/>
-      <c r="F58" s="115" t="n"/>
-      <c r="G58" s="115" t="n"/>
-      <c r="H58" s="115" t="n"/>
-      <c r="I58" s="115" t="n"/>
-      <c r="J58" s="115" t="n"/>
-      <c r="K58" s="115">
-        <f>SUM(D53:J53)</f>
+      <c r="C58" s="111" t="inlineStr">
+        <is>
+          <t>골절</t>
+        </is>
+      </c>
+      <c r="D58" s="112" t="n"/>
+      <c r="E58" s="112" t="n"/>
+      <c r="F58" s="112" t="n"/>
+      <c r="G58" s="112" t="n"/>
+      <c r="H58" s="112" t="n"/>
+      <c r="I58" s="112" t="n"/>
+      <c r="J58" s="112" t="n"/>
+      <c r="K58" s="112">
+        <f>SUM(D52:J52)</f>
         <v/>
       </c>
       <c r="L58" s="4" t="n"/>
@@ -4029,26 +4016,22 @@
       <c r="Z58" s="4" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="111" t="n"/>
-      <c r="B59" s="111" t="inlineStr">
+      <c r="A59" s="182" t="n"/>
+      <c r="B59" s="182" t="n"/>
+      <c r="C59" s="114" t="inlineStr">
         <is>
-          <t>입원비 / 통원비</t>
+          <t>깁스</t>
         </is>
       </c>
-      <c r="C59" s="111" t="inlineStr">
-        <is>
-          <t>질병 (1일이상)</t>
-        </is>
-      </c>
-      <c r="D59" s="112" t="n"/>
-      <c r="E59" s="112" t="n"/>
-      <c r="F59" s="112" t="n"/>
-      <c r="G59" s="112" t="n"/>
-      <c r="H59" s="112" t="n"/>
-      <c r="I59" s="112" t="n"/>
-      <c r="J59" s="112" t="n"/>
-      <c r="K59" s="112">
-        <f>SUM(D54:J54)</f>
+      <c r="D59" s="115" t="n"/>
+      <c r="E59" s="115" t="n"/>
+      <c r="F59" s="115" t="n"/>
+      <c r="G59" s="115" t="n"/>
+      <c r="H59" s="115" t="n"/>
+      <c r="I59" s="115" t="n"/>
+      <c r="J59" s="115" t="n"/>
+      <c r="K59" s="115">
+        <f>SUM(D53:J53)</f>
         <v/>
       </c>
       <c r="L59" s="4" t="n"/>
@@ -4068,22 +4051,26 @@
       <c r="Z59" s="4" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="181" t="n"/>
-      <c r="B60" s="181" t="n"/>
-      <c r="C60" s="114" t="inlineStr">
+      <c r="A60" s="111" t="n"/>
+      <c r="B60" s="111" t="inlineStr">
         <is>
-          <t>재해 (1일이상)</t>
+          <t>입원비 / 통원비</t>
         </is>
       </c>
-      <c r="D60" s="115" t="n"/>
-      <c r="E60" s="115" t="n"/>
-      <c r="F60" s="115" t="n"/>
-      <c r="G60" s="115" t="n"/>
-      <c r="H60" s="115" t="n"/>
-      <c r="I60" s="115" t="n"/>
-      <c r="J60" s="115" t="n"/>
-      <c r="K60" s="115">
-        <f>SUM(D55:J55)</f>
+      <c r="C60" s="111" t="inlineStr">
+        <is>
+          <t>질병 (1일이상)</t>
+        </is>
+      </c>
+      <c r="D60" s="112" t="n"/>
+      <c r="E60" s="112" t="n"/>
+      <c r="F60" s="112" t="n"/>
+      <c r="G60" s="112" t="n"/>
+      <c r="H60" s="112" t="n"/>
+      <c r="I60" s="112" t="n"/>
+      <c r="J60" s="112" t="n"/>
+      <c r="K60" s="112">
+        <f>SUM(D54:J54)</f>
         <v/>
       </c>
       <c r="L60" s="4" t="n"/>
@@ -4105,20 +4092,20 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="181" t="n"/>
       <c r="B61" s="181" t="n"/>
-      <c r="C61" s="111" t="inlineStr">
+      <c r="C61" s="114" t="inlineStr">
         <is>
-          <t>암입원비</t>
+          <t>재해 (1일이상)</t>
         </is>
       </c>
-      <c r="D61" s="112" t="n"/>
-      <c r="E61" s="112" t="n"/>
-      <c r="F61" s="112" t="n"/>
-      <c r="G61" s="112" t="n"/>
-      <c r="H61" s="112" t="n"/>
-      <c r="I61" s="112" t="n"/>
-      <c r="J61" s="112" t="n"/>
-      <c r="K61" s="112">
-        <f>SUM(D56:J56)</f>
+      <c r="D61" s="115" t="n"/>
+      <c r="E61" s="115" t="n"/>
+      <c r="F61" s="115" t="n"/>
+      <c r="G61" s="115" t="n"/>
+      <c r="H61" s="115" t="n"/>
+      <c r="I61" s="115" t="n"/>
+      <c r="J61" s="115" t="n"/>
+      <c r="K61" s="115">
+        <f>SUM(D55:J55)</f>
         <v/>
       </c>
       <c r="L61" s="4" t="n"/>
@@ -4140,20 +4127,20 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="181" t="n"/>
       <c r="B62" s="181" t="n"/>
-      <c r="C62" s="114" t="inlineStr">
+      <c r="C62" s="111" t="inlineStr">
         <is>
-          <t>종합병원입원비1인실</t>
+          <t>암입원비</t>
         </is>
       </c>
-      <c r="D62" s="115" t="n"/>
-      <c r="E62" s="115" t="n"/>
-      <c r="F62" s="115" t="n"/>
-      <c r="G62" s="115" t="n"/>
-      <c r="H62" s="115" t="n"/>
-      <c r="I62" s="115" t="n"/>
-      <c r="J62" s="115" t="n"/>
-      <c r="K62" s="115">
-        <f>SUM(D57:J57)</f>
+      <c r="D62" s="112" t="n"/>
+      <c r="E62" s="112" t="n"/>
+      <c r="F62" s="112" t="n"/>
+      <c r="G62" s="112" t="n"/>
+      <c r="H62" s="112" t="n"/>
+      <c r="I62" s="112" t="n"/>
+      <c r="J62" s="112" t="n"/>
+      <c r="K62" s="112">
+        <f>SUM(D56:J56)</f>
         <v/>
       </c>
       <c r="L62" s="4" t="n"/>
@@ -4175,20 +4162,20 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="181" t="n"/>
       <c r="B63" s="181" t="n"/>
-      <c r="C63" s="111" t="inlineStr">
+      <c r="C63" s="114" t="inlineStr">
         <is>
-          <t>종합병원입원비2~3인실</t>
+          <t>종합병원입원비1인실</t>
         </is>
       </c>
-      <c r="D63" s="112" t="n"/>
-      <c r="E63" s="112" t="n"/>
-      <c r="F63" s="112" t="n"/>
-      <c r="G63" s="112" t="n"/>
-      <c r="H63" s="112" t="n"/>
-      <c r="I63" s="112" t="n"/>
-      <c r="J63" s="112" t="n"/>
-      <c r="K63" s="112">
-        <f>SUM(D58:J58)</f>
+      <c r="D63" s="115" t="n"/>
+      <c r="E63" s="115" t="n"/>
+      <c r="F63" s="115" t="n"/>
+      <c r="G63" s="115" t="n"/>
+      <c r="H63" s="115" t="n"/>
+      <c r="I63" s="115" t="n"/>
+      <c r="J63" s="115" t="n"/>
+      <c r="K63" s="115">
+        <f>SUM(D57:J57)</f>
         <v/>
       </c>
       <c r="L63" s="4" t="n"/>
@@ -4210,20 +4197,20 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="181" t="n"/>
       <c r="B64" s="181" t="n"/>
-      <c r="C64" s="114" t="inlineStr">
+      <c r="C64" s="111" t="inlineStr">
         <is>
-          <t>상급병원입원비1인실</t>
+          <t>종합병원입원비2~3인실</t>
         </is>
       </c>
-      <c r="D64" s="115" t="n"/>
-      <c r="E64" s="115" t="n"/>
-      <c r="F64" s="115" t="n"/>
-      <c r="G64" s="115" t="n"/>
-      <c r="H64" s="115" t="n"/>
-      <c r="I64" s="115" t="n"/>
-      <c r="J64" s="115" t="n"/>
-      <c r="K64" s="115">
-        <f>SUM(D59:J59)</f>
+      <c r="D64" s="112" t="n"/>
+      <c r="E64" s="112" t="n"/>
+      <c r="F64" s="112" t="n"/>
+      <c r="G64" s="112" t="n"/>
+      <c r="H64" s="112" t="n"/>
+      <c r="I64" s="112" t="n"/>
+      <c r="J64" s="112" t="n"/>
+      <c r="K64" s="112">
+        <f>SUM(D58:J58)</f>
         <v/>
       </c>
       <c r="L64" s="4" t="n"/>
@@ -4245,20 +4232,20 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="181" t="n"/>
       <c r="B65" s="181" t="n"/>
-      <c r="C65" s="111" t="inlineStr">
+      <c r="C65" s="114" t="inlineStr">
         <is>
-          <t>상급병원입원비2~3인실</t>
+          <t>상급병원입원비1인실</t>
         </is>
       </c>
-      <c r="D65" s="112" t="n"/>
-      <c r="E65" s="112" t="n"/>
-      <c r="F65" s="112" t="n"/>
-      <c r="G65" s="112" t="n"/>
-      <c r="H65" s="112" t="n"/>
-      <c r="I65" s="112" t="n"/>
-      <c r="J65" s="112" t="n"/>
-      <c r="K65" s="112">
-        <f>SUM(D60:J60)</f>
+      <c r="D65" s="115" t="n"/>
+      <c r="E65" s="115" t="n"/>
+      <c r="F65" s="115" t="n"/>
+      <c r="G65" s="115" t="n"/>
+      <c r="H65" s="115" t="n"/>
+      <c r="I65" s="115" t="n"/>
+      <c r="J65" s="115" t="n"/>
+      <c r="K65" s="115">
+        <f>SUM(D59:J59)</f>
         <v/>
       </c>
       <c r="L65" s="4" t="n"/>
@@ -4280,20 +4267,20 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="181" t="n"/>
       <c r="B66" s="181" t="n"/>
-      <c r="C66" s="114" t="inlineStr">
+      <c r="C66" s="111" t="inlineStr">
         <is>
-          <t>중환자실입원비</t>
+          <t>상급병원입원비2~3인실</t>
         </is>
       </c>
-      <c r="D66" s="115" t="n"/>
-      <c r="E66" s="115" t="n"/>
-      <c r="F66" s="115" t="n"/>
-      <c r="G66" s="115" t="n"/>
-      <c r="H66" s="115" t="n"/>
-      <c r="I66" s="115" t="n"/>
-      <c r="J66" s="115" t="n"/>
-      <c r="K66" s="115">
-        <f>SUM(D61:J61)</f>
+      <c r="D66" s="112" t="n"/>
+      <c r="E66" s="112" t="n"/>
+      <c r="F66" s="112" t="n"/>
+      <c r="G66" s="112" t="n"/>
+      <c r="H66" s="112" t="n"/>
+      <c r="I66" s="112" t="n"/>
+      <c r="J66" s="112" t="n"/>
+      <c r="K66" s="112">
+        <f>SUM(D60:J60)</f>
         <v/>
       </c>
       <c r="L66" s="4" t="n"/>
@@ -4315,20 +4302,20 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="181" t="n"/>
       <c r="B67" s="181" t="n"/>
-      <c r="C67" s="111" t="inlineStr">
+      <c r="C67" s="114" t="inlineStr">
         <is>
-          <t>종합병원통원비</t>
+          <t>중환자실입원비</t>
         </is>
       </c>
-      <c r="D67" s="112" t="n"/>
-      <c r="E67" s="112" t="n"/>
-      <c r="F67" s="112" t="n"/>
-      <c r="G67" s="112" t="n"/>
-      <c r="H67" s="112" t="n"/>
-      <c r="I67" s="112" t="n"/>
-      <c r="J67" s="112" t="n"/>
-      <c r="K67" s="112">
-        <f>SUM(D62:J62)</f>
+      <c r="D67" s="115" t="n"/>
+      <c r="E67" s="115" t="n"/>
+      <c r="F67" s="115" t="n"/>
+      <c r="G67" s="115" t="n"/>
+      <c r="H67" s="115" t="n"/>
+      <c r="I67" s="115" t="n"/>
+      <c r="J67" s="115" t="n"/>
+      <c r="K67" s="115">
+        <f>SUM(D61:J61)</f>
         <v/>
       </c>
       <c r="L67" s="4" t="n"/>
@@ -4350,20 +4337,20 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="181" t="n"/>
       <c r="B68" s="181" t="n"/>
-      <c r="C68" s="114" t="inlineStr">
+      <c r="C68" s="111" t="inlineStr">
         <is>
-          <t>상급종합병원통원비</t>
+          <t>종합병원통원비</t>
         </is>
       </c>
-      <c r="D68" s="115" t="n"/>
-      <c r="E68" s="115" t="n"/>
-      <c r="F68" s="115" t="n"/>
-      <c r="G68" s="115" t="n"/>
-      <c r="H68" s="115" t="n"/>
-      <c r="I68" s="115" t="n"/>
-      <c r="J68" s="115" t="n"/>
-      <c r="K68" s="115">
-        <f>SUM(D63:J63)</f>
+      <c r="D68" s="112" t="n"/>
+      <c r="E68" s="112" t="n"/>
+      <c r="F68" s="112" t="n"/>
+      <c r="G68" s="112" t="n"/>
+      <c r="H68" s="112" t="n"/>
+      <c r="I68" s="112" t="n"/>
+      <c r="J68" s="112" t="n"/>
+      <c r="K68" s="112">
+        <f>SUM(D62:J62)</f>
         <v/>
       </c>
       <c r="L68" s="4" t="n"/>
@@ -4383,22 +4370,22 @@
       <c r="Z68" s="4" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="182" t="n"/>
-      <c r="B69" s="182" t="n"/>
-      <c r="C69" s="111" t="inlineStr">
+      <c r="A69" s="181" t="n"/>
+      <c r="B69" s="181" t="n"/>
+      <c r="C69" s="114" t="inlineStr">
         <is>
-          <t>상급종합병원암통원비</t>
+          <t>상급종합병원통원비</t>
         </is>
       </c>
-      <c r="D69" s="112" t="n"/>
-      <c r="E69" s="112" t="n"/>
-      <c r="F69" s="112" t="n"/>
-      <c r="G69" s="112" t="n"/>
-      <c r="H69" s="112" t="n"/>
-      <c r="I69" s="112" t="n"/>
-      <c r="J69" s="112" t="n"/>
-      <c r="K69" s="112">
-        <f>SUM(D64:J64)</f>
+      <c r="D69" s="115" t="n"/>
+      <c r="E69" s="115" t="n"/>
+      <c r="F69" s="115" t="n"/>
+      <c r="G69" s="115" t="n"/>
+      <c r="H69" s="115" t="n"/>
+      <c r="I69" s="115" t="n"/>
+      <c r="J69" s="115" t="n"/>
+      <c r="K69" s="115">
+        <f>SUM(D63:J63)</f>
         <v/>
       </c>
       <c r="L69" s="4" t="n"/>
@@ -4418,26 +4405,22 @@
       <c r="Z69" s="4" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="184" t="n"/>
-      <c r="B70" s="184" t="inlineStr">
+      <c r="A70" s="182" t="n"/>
+      <c r="B70" s="182" t="n"/>
+      <c r="C70" s="111" t="inlineStr">
         <is>
-          <t>치매보장</t>
+          <t>상급종합병원암통원비</t>
         </is>
       </c>
-      <c r="C70" s="184" t="inlineStr">
-        <is>
-          <t>경증치매</t>
-        </is>
-      </c>
-      <c r="D70" s="185" t="n"/>
-      <c r="E70" s="185" t="n"/>
-      <c r="F70" s="185" t="n"/>
-      <c r="G70" s="185" t="n"/>
-      <c r="H70" s="185" t="n"/>
-      <c r="I70" s="185" t="n"/>
-      <c r="J70" s="185" t="n"/>
-      <c r="K70" s="185">
-        <f>SUM(D65:J65)</f>
+      <c r="D70" s="112" t="n"/>
+      <c r="E70" s="112" t="n"/>
+      <c r="F70" s="112" t="n"/>
+      <c r="G70" s="112" t="n"/>
+      <c r="H70" s="112" t="n"/>
+      <c r="I70" s="112" t="n"/>
+      <c r="J70" s="112" t="n"/>
+      <c r="K70" s="112">
+        <f>SUM(D64:J64)</f>
         <v/>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -4457,22 +4440,26 @@
       <c r="Z70" s="4" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="182" t="n"/>
-      <c r="B71" s="182" t="n"/>
-      <c r="C71" s="187" t="inlineStr">
+      <c r="A71" s="184" t="n"/>
+      <c r="B71" s="184" t="inlineStr">
         <is>
-          <t>중증치매</t>
+          <t>치매보장</t>
         </is>
       </c>
-      <c r="D71" s="188" t="n"/>
-      <c r="E71" s="188" t="n"/>
-      <c r="F71" s="188" t="n"/>
-      <c r="G71" s="188" t="n"/>
-      <c r="H71" s="188" t="n"/>
-      <c r="I71" s="188" t="n"/>
-      <c r="J71" s="188" t="n"/>
-      <c r="K71" s="188">
-        <f>SUM(D66:J66)</f>
+      <c r="C71" s="184" t="inlineStr">
+        <is>
+          <t>경증치매</t>
+        </is>
+      </c>
+      <c r="D71" s="185" t="n"/>
+      <c r="E71" s="185" t="n"/>
+      <c r="F71" s="185" t="n"/>
+      <c r="G71" s="185" t="n"/>
+      <c r="H71" s="185" t="n"/>
+      <c r="I71" s="185" t="n"/>
+      <c r="J71" s="185" t="n"/>
+      <c r="K71" s="185">
+        <f>SUM(D65:J65)</f>
         <v/>
       </c>
       <c r="L71" s="4" t="n"/>
@@ -4492,26 +4479,22 @@
       <c r="Z71" s="4" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="148" t="n"/>
-      <c r="B72" s="148" t="inlineStr">
+      <c r="A72" s="182" t="n"/>
+      <c r="B72" s="182" t="n"/>
+      <c r="C72" s="187" t="inlineStr">
         <is>
-          <t>간병비</t>
+          <t>중증치매</t>
         </is>
       </c>
-      <c r="C72" s="148" t="inlineStr">
-        <is>
-          <t>간병비(질병)</t>
-        </is>
-      </c>
-      <c r="D72" s="149" t="n"/>
-      <c r="E72" s="149" t="n"/>
-      <c r="F72" s="149" t="n"/>
-      <c r="G72" s="149" t="n"/>
-      <c r="H72" s="149" t="n"/>
-      <c r="I72" s="149" t="n"/>
-      <c r="J72" s="149" t="n"/>
-      <c r="K72" s="149">
-        <f>SUM(D67:J67)</f>
+      <c r="D72" s="188" t="n"/>
+      <c r="E72" s="188" t="n"/>
+      <c r="F72" s="188" t="n"/>
+      <c r="G72" s="188" t="n"/>
+      <c r="H72" s="188" t="n"/>
+      <c r="I72" s="188" t="n"/>
+      <c r="J72" s="188" t="n"/>
+      <c r="K72" s="188">
+        <f>SUM(D66:J66)</f>
         <v/>
       </c>
       <c r="L72" s="4" t="n"/>
@@ -4531,61 +4514,49 @@
       <c r="Z72" s="4" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="182" t="n"/>
-      <c r="B73" s="182" t="n"/>
-      <c r="C73" s="151" t="inlineStr">
+      <c r="A73" s="184" t="n"/>
+      <c r="B73" s="184" t="inlineStr">
         <is>
-          <t>간병비(상해)</t>
+          <t>복합재가</t>
         </is>
       </c>
-      <c r="D73" s="152" t="n"/>
-      <c r="E73" s="152" t="n"/>
-      <c r="F73" s="152" t="n"/>
-      <c r="G73" s="152" t="n"/>
-      <c r="H73" s="152" t="n"/>
-      <c r="I73" s="152" t="n"/>
-      <c r="J73" s="152" t="n"/>
-      <c r="K73" s="152">
-        <f>SUM(D68:J68)</f>
-        <v/>
-      </c>
+      <c r="C73" s="184" t="inlineStr">
+        <is>
+          <t>복합재가</t>
+        </is>
+      </c>
+      <c r="D73" s="185" t="n"/>
+      <c r="E73" s="185" t="n"/>
+      <c r="F73" s="185" t="n"/>
+      <c r="G73" s="185" t="n"/>
+      <c r="H73" s="185" t="n"/>
+      <c r="I73" s="185" t="n"/>
+      <c r="J73" s="185" t="n"/>
+      <c r="K73" s="185" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n"/>
-      <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n"/>
-      <c r="R73" s="4" t="n"/>
-      <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
-      <c r="U73" s="4" t="n"/>
-      <c r="V73" s="4" t="n"/>
-      <c r="W73" s="4" t="n"/>
-      <c r="X73" s="4" t="n"/>
-      <c r="Y73" s="4" t="n"/>
-      <c r="Z73" s="4" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="153" t="n"/>
-      <c r="B74" s="153" t="inlineStr">
+      <c r="A74" s="148" t="n"/>
+      <c r="B74" s="148" t="inlineStr">
         <is>
-          <t>치아</t>
+          <t>간병비</t>
         </is>
       </c>
-      <c r="C74" s="153" t="inlineStr">
+      <c r="C74" s="148" t="inlineStr">
         <is>
-          <t>치아보철치료비</t>
+          <t>간병비(질병)</t>
         </is>
       </c>
-      <c r="D74" s="154" t="n"/>
-      <c r="E74" s="154" t="n"/>
-      <c r="F74" s="154" t="n"/>
-      <c r="G74" s="154" t="n"/>
-      <c r="H74" s="154" t="n"/>
-      <c r="I74" s="154" t="n"/>
-      <c r="J74" s="154" t="n"/>
-      <c r="K74" s="154">
-        <f>SUM(D69:J69)</f>
+      <c r="D74" s="149" t="n"/>
+      <c r="E74" s="149" t="n"/>
+      <c r="F74" s="149" t="n"/>
+      <c r="G74" s="149" t="n"/>
+      <c r="H74" s="149" t="n"/>
+      <c r="I74" s="149" t="n"/>
+      <c r="J74" s="149" t="n"/>
+      <c r="K74" s="149">
+        <f>SUM(D67:J67)</f>
         <v/>
       </c>
       <c r="L74" s="4" t="n"/>
@@ -4607,20 +4578,20 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="182" t="n"/>
       <c r="B75" s="182" t="n"/>
-      <c r="C75" s="156" t="inlineStr">
+      <c r="C75" s="151" t="inlineStr">
         <is>
-          <t>치아보존치료비</t>
+          <t>간병비(상해)</t>
         </is>
       </c>
-      <c r="D75" s="157" t="n"/>
-      <c r="E75" s="157" t="n"/>
-      <c r="F75" s="157" t="n"/>
-      <c r="G75" s="157" t="n"/>
-      <c r="H75" s="157" t="n"/>
-      <c r="I75" s="157" t="n"/>
-      <c r="J75" s="157" t="n"/>
-      <c r="K75" s="157">
-        <f>SUM(D70:J70)</f>
+      <c r="D75" s="152" t="n"/>
+      <c r="E75" s="152" t="n"/>
+      <c r="F75" s="152" t="n"/>
+      <c r="G75" s="152" t="n"/>
+      <c r="H75" s="152" t="n"/>
+      <c r="I75" s="152" t="n"/>
+      <c r="J75" s="152" t="n"/>
+      <c r="K75" s="152">
+        <f>SUM(D68:J68)</f>
         <v/>
       </c>
       <c r="L75" s="4" t="n"/>
@@ -4640,26 +4611,26 @@
       <c r="Z75" s="4" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="118" t="n"/>
-      <c r="B76" s="118" t="inlineStr">
+      <c r="A76" s="153" t="n"/>
+      <c r="B76" s="153" t="inlineStr">
         <is>
-          <t>실손의료비</t>
+          <t>치아</t>
         </is>
       </c>
-      <c r="C76" s="118" t="inlineStr">
+      <c r="C76" s="153" t="inlineStr">
         <is>
-          <t>질병입원</t>
+          <t>치아보철치료비</t>
         </is>
       </c>
-      <c r="D76" s="119" t="n"/>
-      <c r="E76" s="119" t="n"/>
-      <c r="F76" s="119" t="n"/>
-      <c r="G76" s="119" t="n"/>
-      <c r="H76" s="119" t="n"/>
-      <c r="I76" s="119" t="n"/>
-      <c r="J76" s="119" t="n"/>
-      <c r="K76" s="119">
-        <f>SUM(D71:J71)</f>
+      <c r="D76" s="154" t="n"/>
+      <c r="E76" s="154" t="n"/>
+      <c r="F76" s="154" t="n"/>
+      <c r="G76" s="154" t="n"/>
+      <c r="H76" s="154" t="n"/>
+      <c r="I76" s="154" t="n"/>
+      <c r="J76" s="154" t="n"/>
+      <c r="K76" s="154">
+        <f>SUM(D69:J69)</f>
         <v/>
       </c>
       <c r="L76" s="4" t="n"/>
@@ -4679,22 +4650,22 @@
       <c r="Z76" s="4" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="181" t="n"/>
-      <c r="B77" s="181" t="n"/>
-      <c r="C77" s="121" t="inlineStr">
+      <c r="A77" s="182" t="n"/>
+      <c r="B77" s="182" t="n"/>
+      <c r="C77" s="156" t="inlineStr">
         <is>
-          <t>질병통원</t>
+          <t>치아보존치료비</t>
         </is>
       </c>
-      <c r="D77" s="122" t="n"/>
-      <c r="E77" s="122" t="n"/>
-      <c r="F77" s="122" t="n"/>
-      <c r="G77" s="122" t="n"/>
-      <c r="H77" s="122" t="n"/>
-      <c r="I77" s="122" t="n"/>
-      <c r="J77" s="122" t="n"/>
-      <c r="K77" s="122">
-        <f>SUM(D72:J72)</f>
+      <c r="D77" s="157" t="n"/>
+      <c r="E77" s="157" t="n"/>
+      <c r="F77" s="157" t="n"/>
+      <c r="G77" s="157" t="n"/>
+      <c r="H77" s="157" t="n"/>
+      <c r="I77" s="157" t="n"/>
+      <c r="J77" s="157" t="n"/>
+      <c r="K77" s="157">
+        <f>SUM(D70:J70)</f>
         <v/>
       </c>
       <c r="L77" s="4" t="n"/>
@@ -4714,11 +4685,15 @@
       <c r="Z77" s="4" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="181" t="n"/>
-      <c r="B78" s="181" t="n"/>
+      <c r="A78" s="118" t="n"/>
+      <c r="B78" s="118" t="inlineStr">
+        <is>
+          <t>실손의료비</t>
+        </is>
+      </c>
       <c r="C78" s="118" t="inlineStr">
         <is>
-          <t>상해입원</t>
+          <t>질병입원</t>
         </is>
       </c>
       <c r="D78" s="119" t="n"/>
@@ -4729,7 +4704,7 @@
       <c r="I78" s="119" t="n"/>
       <c r="J78" s="119" t="n"/>
       <c r="K78" s="119">
-        <f>SUM(D73:J73)</f>
+        <f>SUM(D71:J71)</f>
         <v/>
       </c>
       <c r="L78" s="4" t="n"/>
@@ -4749,11 +4724,11 @@
       <c r="Z78" s="4" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="182" t="n"/>
-      <c r="B79" s="182" t="n"/>
+      <c r="A79" s="181" t="n"/>
+      <c r="B79" s="181" t="n"/>
       <c r="C79" s="121" t="inlineStr">
         <is>
-          <t>상해통원</t>
+          <t>질병통원</t>
         </is>
       </c>
       <c r="D79" s="122" t="n"/>
@@ -4764,7 +4739,7 @@
       <c r="I79" s="122" t="n"/>
       <c r="J79" s="122" t="n"/>
       <c r="K79" s="122">
-        <f>SUM(D74:J74)</f>
+        <f>SUM(D72:J72)</f>
         <v/>
       </c>
       <c r="L79" s="4" t="n"/>
@@ -4784,24 +4759,22 @@
       <c r="Z79" s="4" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="158" t="n"/>
-      <c r="B80" s="159" t="inlineStr">
+      <c r="A80" s="181" t="n"/>
+      <c r="B80" s="181" t="n"/>
+      <c r="C80" s="118" t="inlineStr">
         <is>
-          <t>기납입보험료</t>
+          <t>상해입원</t>
         </is>
       </c>
-      <c r="C80" s="159" t="n"/>
-      <c r="D80" s="160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="160" t="n"/>
-      <c r="F80" s="160" t="n"/>
-      <c r="G80" s="160" t="n"/>
-      <c r="H80" s="160" t="n"/>
-      <c r="I80" s="160" t="n"/>
-      <c r="J80" s="160" t="n"/>
-      <c r="K80" s="160">
-        <f>SUM(D75:J75)</f>
+      <c r="D80" s="119" t="n"/>
+      <c r="E80" s="119" t="n"/>
+      <c r="F80" s="119" t="n"/>
+      <c r="G80" s="119" t="n"/>
+      <c r="H80" s="119" t="n"/>
+      <c r="I80" s="119" t="n"/>
+      <c r="J80" s="119" t="n"/>
+      <c r="K80" s="119">
+        <f>SUM(D73:J73)</f>
         <v/>
       </c>
       <c r="L80" s="4" t="n"/>
@@ -4821,24 +4794,22 @@
       <c r="Z80" s="4" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="181" t="n"/>
-      <c r="B81" s="162" t="inlineStr">
+      <c r="A81" s="182" t="n"/>
+      <c r="B81" s="182" t="n"/>
+      <c r="C81" s="121" t="inlineStr">
         <is>
-          <t>납입할보험료</t>
+          <t>상해통원</t>
         </is>
       </c>
-      <c r="C81" s="162" t="n"/>
-      <c r="D81" s="163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="163" t="n"/>
-      <c r="F81" s="163" t="n"/>
-      <c r="G81" s="163" t="n"/>
-      <c r="H81" s="163" t="n"/>
-      <c r="I81" s="163" t="n"/>
-      <c r="J81" s="163" t="n"/>
-      <c r="K81" s="163">
-        <f>SUM(D76:J76)</f>
+      <c r="D81" s="122" t="n"/>
+      <c r="E81" s="122" t="n"/>
+      <c r="F81" s="122" t="n"/>
+      <c r="G81" s="122" t="n"/>
+      <c r="H81" s="122" t="n"/>
+      <c r="I81" s="122" t="n"/>
+      <c r="J81" s="122" t="n"/>
+      <c r="K81" s="122">
+        <f>SUM(D74:J74)</f>
         <v/>
       </c>
       <c r="L81" s="4" t="n"/>
@@ -4858,43 +4829,24 @@
       <c r="Z81" s="4" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="182" t="n"/>
+      <c r="A82" s="158" t="n"/>
       <c r="B82" s="159" t="inlineStr">
         <is>
-          <t>총납입보험료</t>
+          <t>기납입보험료</t>
         </is>
       </c>
       <c r="C82" s="159" t="n"/>
-      <c r="D82" s="160">
-        <f>D75+D76</f>
-        <v/>
-      </c>
-      <c r="E82" s="160">
-        <f>E75+E76</f>
-        <v/>
-      </c>
-      <c r="F82" s="160">
-        <f>F75+F76</f>
-        <v/>
-      </c>
-      <c r="G82" s="160">
-        <f>G75+G76</f>
-        <v/>
-      </c>
-      <c r="H82" s="160">
-        <f>H75+H76</f>
-        <v/>
-      </c>
-      <c r="I82" s="160">
-        <f>I75+I76</f>
-        <v/>
-      </c>
-      <c r="J82" s="160">
-        <f>J75+J76</f>
-        <v/>
-      </c>
+      <c r="D82" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="160" t="n"/>
+      <c r="F82" s="160" t="n"/>
+      <c r="G82" s="160" t="n"/>
+      <c r="H82" s="160" t="n"/>
+      <c r="I82" s="160" t="n"/>
+      <c r="J82" s="160" t="n"/>
       <c r="K82" s="160">
-        <f>SUM(D77:J77)</f>
+        <f>SUM(D75:J75)</f>
         <v/>
       </c>
       <c r="L82" s="4" t="n"/>
@@ -4914,17 +4866,26 @@
       <c r="Z82" s="4" t="n"/>
     </row>
     <row r="83" ht="5" customHeight="1">
-      <c r="A83" s="48" t="n"/>
-      <c r="B83" s="49" t="n"/>
-      <c r="C83" s="49" t="n"/>
-      <c r="D83" s="165" t="n"/>
-      <c r="E83" s="165" t="n"/>
-      <c r="F83" s="165" t="n"/>
-      <c r="G83" s="165" t="n"/>
-      <c r="H83" s="165" t="n"/>
-      <c r="I83" s="165" t="n"/>
-      <c r="J83" s="165" t="n"/>
-      <c r="K83" s="165" t="n"/>
+      <c r="A83" s="181" t="n"/>
+      <c r="B83" s="162" t="inlineStr">
+        <is>
+          <t>납입할보험료</t>
+        </is>
+      </c>
+      <c r="C83" s="162" t="n"/>
+      <c r="D83" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="163" t="n"/>
+      <c r="F83" s="163" t="n"/>
+      <c r="G83" s="163" t="n"/>
+      <c r="H83" s="163" t="n"/>
+      <c r="I83" s="163" t="n"/>
+      <c r="J83" s="163" t="n"/>
+      <c r="K83" s="163">
+        <f>SUM(D76:J76)</f>
+        <v/>
+      </c>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
@@ -4942,21 +4903,48 @@
       <c r="Z83" s="4" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="208" t="inlineStr">
+      <c r="A84" s="182" t="n"/>
+      <c r="B84" s="159" t="inlineStr">
         <is>
-          <t>🔄  갱신형 / 비갱신형 구분</t>
+          <t>총납입보험료</t>
         </is>
       </c>
-      <c r="B84" s="215" t="n"/>
-      <c r="C84" s="215" t="n"/>
-      <c r="D84" s="215" t="n"/>
-      <c r="E84" s="215" t="n"/>
-      <c r="F84" s="215" t="n"/>
-      <c r="G84" s="215" t="n"/>
-      <c r="H84" s="215" t="n"/>
-      <c r="I84" s="215" t="n"/>
-      <c r="J84" s="215" t="n"/>
-      <c r="K84" s="214" t="n"/>
+      <c r="C84" s="159" t="n"/>
+      <c r="D84" s="160">
+        <f>D75+D76</f>
+        <v/>
+      </c>
+      <c r="E84" s="160">
+        <f>E75+E76</f>
+        <v/>
+      </c>
+      <c r="F84" s="160">
+        <f>F75+F76</f>
+        <v/>
+      </c>
+      <c r="G84" s="160">
+        <f>G75+G76</f>
+        <v/>
+      </c>
+      <c r="H84" s="160">
+        <f>H75+H76</f>
+        <v/>
+      </c>
+      <c r="I84" s="160">
+        <f>I75+I76</f>
+        <v/>
+      </c>
+      <c r="J84" s="160">
+        <f>J75+J76</f>
+        <v/>
+      </c>
+      <c r="K84" s="160">
+        <f>SUM(D77:J77)</f>
+        <v/>
+      </c>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
@@ -4971,21 +4959,20 @@
       <c r="Z84" s="4" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="209" t="inlineStr">
-        <is>
-          <t>갱신 구분</t>
-        </is>
-      </c>
-      <c r="B85" s="215" t="n"/>
-      <c r="C85" s="214" t="n"/>
-      <c r="D85" s="210" t="n"/>
-      <c r="E85" s="210" t="n"/>
-      <c r="F85" s="210" t="n"/>
-      <c r="G85" s="210" t="n"/>
-      <c r="H85" s="210" t="n"/>
-      <c r="I85" s="210" t="n"/>
-      <c r="J85" s="210" t="n"/>
-      <c r="K85" s="211" t="n"/>
+      <c r="A85" s="48" t="n"/>
+      <c r="B85" s="49" t="n"/>
+      <c r="C85" s="49" t="n"/>
+      <c r="D85" s="165" t="n"/>
+      <c r="E85" s="165" t="n"/>
+      <c r="F85" s="165" t="n"/>
+      <c r="G85" s="165" t="n"/>
+      <c r="H85" s="165" t="n"/>
+      <c r="I85" s="165" t="n"/>
+      <c r="J85" s="165" t="n"/>
+      <c r="K85" s="165" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
       <c r="O85" s="4" t="n"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
@@ -5000,22 +4987,11 @@
       <c r="Z85" s="4" t="n"/>
     </row>
     <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="209" t="inlineStr">
+      <c r="A86" s="208" t="inlineStr">
         <is>
-          <t>보험료
-변화 예고</t>
+          <t>🔄  갱신형 / 비갱신형 구분</t>
         </is>
       </c>
-      <c r="B86" s="215" t="n"/>
-      <c r="C86" s="214" t="n"/>
-      <c r="D86" s="210" t="n"/>
-      <c r="E86" s="210" t="n"/>
-      <c r="F86" s="210" t="n"/>
-      <c r="G86" s="210" t="n"/>
-      <c r="H86" s="210" t="n"/>
-      <c r="I86" s="210" t="n"/>
-      <c r="J86" s="210" t="n"/>
-      <c r="K86" s="211" t="n"/>
       <c r="O86" s="4" t="n"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
@@ -5030,6 +5006,19 @@
       <c r="Z86" s="4" t="n"/>
     </row>
     <row r="87" ht="7.5" customHeight="1">
+      <c r="A87" s="209" t="inlineStr">
+        <is>
+          <t>갱신 구분</t>
+        </is>
+      </c>
+      <c r="D87" s="210" t="n"/>
+      <c r="E87" s="210" t="n"/>
+      <c r="F87" s="210" t="n"/>
+      <c r="G87" s="210" t="n"/>
+      <c r="H87" s="210" t="n"/>
+      <c r="I87" s="210" t="n"/>
+      <c r="J87" s="210" t="n"/>
+      <c r="K87" s="211" t="n"/>
       <c r="O87" s="4" t="n"/>
       <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
@@ -5044,21 +5033,20 @@
       <c r="Z87" s="4" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="212" t="inlineStr">
+      <c r="A88" s="209" t="inlineStr">
         <is>
-          <t>📋  현재 유지중인 보험 리뷰</t>
+          <t>보험료
+변화 예고</t>
         </is>
       </c>
-      <c r="B88" s="215" t="n"/>
-      <c r="C88" s="215" t="n"/>
-      <c r="D88" s="215" t="n"/>
-      <c r="E88" s="215" t="n"/>
-      <c r="F88" s="215" t="n"/>
-      <c r="G88" s="215" t="n"/>
-      <c r="H88" s="215" t="n"/>
-      <c r="I88" s="215" t="n"/>
-      <c r="J88" s="215" t="n"/>
-      <c r="K88" s="214" t="n"/>
+      <c r="D88" s="210" t="n"/>
+      <c r="E88" s="210" t="n"/>
+      <c r="F88" s="210" t="n"/>
+      <c r="G88" s="210" t="n"/>
+      <c r="H88" s="210" t="n"/>
+      <c r="I88" s="210" t="n"/>
+      <c r="J88" s="210" t="n"/>
+      <c r="K88" s="211" t="n"/>
       <c r="O88" s="4" t="n"/>
       <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
@@ -5073,37 +5061,6 @@
       <c r="Z88" s="4" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="209" t="inlineStr">
-        <is>
-          <t>보험사 / 상품명</t>
-        </is>
-      </c>
-      <c r="B89" s="214" t="n"/>
-      <c r="C89" s="209" t="inlineStr">
-        <is>
-          <t>가입일 / 만기</t>
-        </is>
-      </c>
-      <c r="D89" s="209" t="inlineStr">
-        <is>
-          <t>월 보험료</t>
-        </is>
-      </c>
-      <c r="E89" s="209" t="inlineStr">
-        <is>
-          <t>주요 체크사항</t>
-        </is>
-      </c>
-      <c r="F89" s="215" t="n"/>
-      <c r="G89" s="215" t="n"/>
-      <c r="H89" s="214" t="n"/>
-      <c r="I89" s="209" t="inlineStr">
-        <is>
-          <t>특이사항 (면책기간, 보장범위 등)</t>
-        </is>
-      </c>
-      <c r="J89" s="215" t="n"/>
-      <c r="K89" s="214" t="n"/>
       <c r="O89" s="4" t="n"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
@@ -5118,17 +5075,11 @@
       <c r="Z89" s="4" t="n"/>
     </row>
     <row r="90" ht="70" customHeight="1">
-      <c r="A90" s="213" t="n"/>
-      <c r="B90" s="214" t="n"/>
-      <c r="C90" s="213" t="n"/>
-      <c r="D90" s="213" t="n"/>
-      <c r="E90" s="213" t="n"/>
-      <c r="F90" s="215" t="n"/>
-      <c r="G90" s="215" t="n"/>
-      <c r="H90" s="214" t="n"/>
-      <c r="I90" s="213" t="n"/>
-      <c r="J90" s="215" t="n"/>
-      <c r="K90" s="214" t="n"/>
+      <c r="A90" s="212" t="inlineStr">
+        <is>
+          <t>📋  현재 유지중인 보험 리뷰</t>
+        </is>
+      </c>
       <c r="O90" s="4" t="n"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
@@ -5143,17 +5094,31 @@
       <c r="Z90" s="4" t="n"/>
     </row>
     <row r="91" ht="70" customHeight="1">
-      <c r="A91" s="216" t="n"/>
-      <c r="B91" s="214" t="n"/>
-      <c r="C91" s="216" t="n"/>
-      <c r="D91" s="216" t="n"/>
-      <c r="E91" s="216" t="n"/>
-      <c r="F91" s="215" t="n"/>
-      <c r="G91" s="215" t="n"/>
-      <c r="H91" s="214" t="n"/>
-      <c r="I91" s="216" t="n"/>
-      <c r="J91" s="215" t="n"/>
-      <c r="K91" s="214" t="n"/>
+      <c r="A91" s="209" t="inlineStr">
+        <is>
+          <t>보험사 / 상품명</t>
+        </is>
+      </c>
+      <c r="C91" s="209" t="inlineStr">
+        <is>
+          <t>가입일 / 만기</t>
+        </is>
+      </c>
+      <c r="D91" s="209" t="inlineStr">
+        <is>
+          <t>월 보험료</t>
+        </is>
+      </c>
+      <c r="E91" s="209" t="inlineStr">
+        <is>
+          <t>주요 체크사항</t>
+        </is>
+      </c>
+      <c r="I91" s="209" t="inlineStr">
+        <is>
+          <t>특이사항 (면책기간, 보장범위 등)</t>
+        </is>
+      </c>
       <c r="O91" s="4" t="n"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
@@ -5168,17 +5133,11 @@
       <c r="Z91" s="4" t="n"/>
     </row>
     <row r="92" ht="70" customHeight="1">
-      <c r="A92" s="217" t="n"/>
-      <c r="B92" s="214" t="n"/>
-      <c r="C92" s="217" t="n"/>
-      <c r="D92" s="217" t="n"/>
-      <c r="E92" s="217" t="n"/>
-      <c r="F92" s="215" t="n"/>
-      <c r="G92" s="215" t="n"/>
-      <c r="H92" s="214" t="n"/>
-      <c r="I92" s="217" t="n"/>
-      <c r="J92" s="215" t="n"/>
-      <c r="K92" s="214" t="n"/>
+      <c r="A92" s="213" t="n"/>
+      <c r="C92" s="213" t="n"/>
+      <c r="D92" s="213" t="n"/>
+      <c r="E92" s="213" t="n"/>
+      <c r="I92" s="213" t="n"/>
       <c r="O92" s="4" t="n"/>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
@@ -5193,17 +5152,11 @@
       <c r="Z92" s="4" t="n"/>
     </row>
     <row r="93" ht="70" customHeight="1">
-      <c r="A93" s="218" t="n"/>
-      <c r="B93" s="214" t="n"/>
-      <c r="C93" s="218" t="n"/>
-      <c r="D93" s="218" t="n"/>
-      <c r="E93" s="218" t="n"/>
-      <c r="F93" s="215" t="n"/>
-      <c r="G93" s="215" t="n"/>
-      <c r="H93" s="214" t="n"/>
-      <c r="I93" s="218" t="n"/>
-      <c r="J93" s="215" t="n"/>
-      <c r="K93" s="214" t="n"/>
+      <c r="A93" s="216" t="n"/>
+      <c r="C93" s="216" t="n"/>
+      <c r="D93" s="216" t="n"/>
+      <c r="E93" s="216" t="n"/>
+      <c r="I93" s="216" t="n"/>
       <c r="O93" s="4" t="n"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
@@ -5218,17 +5171,11 @@
       <c r="Z93" s="4" t="n"/>
     </row>
     <row r="94" ht="70" customHeight="1">
-      <c r="A94" s="219" t="n"/>
-      <c r="B94" s="214" t="n"/>
-      <c r="C94" s="219" t="n"/>
-      <c r="D94" s="219" t="n"/>
-      <c r="E94" s="219" t="n"/>
-      <c r="F94" s="215" t="n"/>
-      <c r="G94" s="215" t="n"/>
-      <c r="H94" s="214" t="n"/>
-      <c r="I94" s="219" t="n"/>
-      <c r="J94" s="215" t="n"/>
-      <c r="K94" s="214" t="n"/>
+      <c r="A94" s="217" t="n"/>
+      <c r="C94" s="217" t="n"/>
+      <c r="D94" s="217" t="n"/>
+      <c r="E94" s="217" t="n"/>
+      <c r="I94" s="217" t="n"/>
       <c r="O94" s="4" t="n"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
@@ -5243,17 +5190,11 @@
       <c r="Z94" s="4" t="n"/>
     </row>
     <row r="95" ht="70" customHeight="1">
-      <c r="A95" s="220" t="n"/>
-      <c r="B95" s="214" t="n"/>
-      <c r="C95" s="220" t="n"/>
-      <c r="D95" s="220" t="n"/>
-      <c r="E95" s="220" t="n"/>
-      <c r="F95" s="215" t="n"/>
-      <c r="G95" s="215" t="n"/>
-      <c r="H95" s="214" t="n"/>
-      <c r="I95" s="220" t="n"/>
-      <c r="J95" s="215" t="n"/>
-      <c r="K95" s="214" t="n"/>
+      <c r="A95" s="218" t="n"/>
+      <c r="C95" s="218" t="n"/>
+      <c r="D95" s="218" t="n"/>
+      <c r="E95" s="218" t="n"/>
+      <c r="I95" s="218" t="n"/>
       <c r="O95" s="4" t="n"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
@@ -5268,17 +5209,11 @@
       <c r="Z95" s="4" t="n"/>
     </row>
     <row r="96" ht="70" customHeight="1">
-      <c r="A96" s="221" t="n"/>
-      <c r="B96" s="214" t="n"/>
-      <c r="C96" s="221" t="n"/>
-      <c r="D96" s="221" t="n"/>
-      <c r="E96" s="221" t="n"/>
-      <c r="F96" s="215" t="n"/>
-      <c r="G96" s="215" t="n"/>
-      <c r="H96" s="214" t="n"/>
-      <c r="I96" s="221" t="n"/>
-      <c r="J96" s="215" t="n"/>
-      <c r="K96" s="214" t="n"/>
+      <c r="A96" s="219" t="n"/>
+      <c r="C96" s="219" t="n"/>
+      <c r="D96" s="219" t="n"/>
+      <c r="E96" s="219" t="n"/>
+      <c r="I96" s="219" t="n"/>
       <c r="O96" s="4" t="n"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
@@ -5293,6 +5228,11 @@
       <c r="Z96" s="4" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="220" t="n"/>
+      <c r="C97" s="220" t="n"/>
+      <c r="D97" s="220" t="n"/>
+      <c r="E97" s="220" t="n"/>
+      <c r="I97" s="220" t="n"/>
       <c r="O97" s="4" t="n"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
@@ -5307,6 +5247,11 @@
       <c r="Z97" s="4" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="221" t="n"/>
+      <c r="C98" s="221" t="n"/>
+      <c r="D98" s="221" t="n"/>
+      <c r="E98" s="221" t="n"/>
+      <c r="I98" s="221" t="n"/>
       <c r="O98" s="4" t="n"/>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
@@ -5629,20 +5574,6 @@
       <c r="Z120" s="4" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="4" t="n"/>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="4" t="n"/>
-      <c r="H121" s="4" t="n"/>
-      <c r="I121" s="4" t="n"/>
-      <c r="J121" s="4" t="n"/>
-      <c r="K121" s="4" t="n"/>
-      <c r="L121" s="4" t="n"/>
-      <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="n"/>
       <c r="P121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
@@ -5657,20 +5588,6 @@
       <c r="Z121" s="4" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="4" t="n"/>
-      <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="n"/>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
-      <c r="I122" s="4" t="n"/>
-      <c r="J122" s="4" t="n"/>
-      <c r="K122" s="4" t="n"/>
-      <c r="L122" s="4" t="n"/>
-      <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="n"/>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
@@ -10304,8 +10221,62 @@
       <c r="Y287" s="4" t="n"/>
       <c r="Z287" s="4" t="n"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="A288" s="4" t="n"/>
+      <c r="B288" s="4" t="n"/>
+      <c r="C288" s="4" t="n"/>
+      <c r="D288" s="4" t="n"/>
+      <c r="E288" s="4" t="n"/>
+      <c r="F288" s="4" t="n"/>
+      <c r="G288" s="4" t="n"/>
+      <c r="H288" s="4" t="n"/>
+      <c r="I288" s="4" t="n"/>
+      <c r="J288" s="4" t="n"/>
+      <c r="K288" s="4" t="n"/>
+      <c r="L288" s="4" t="n"/>
+      <c r="M288" s="4" t="n"/>
+      <c r="N288" s="4" t="n"/>
+      <c r="O288" s="4" t="n"/>
+      <c r="P288" s="4" t="n"/>
+      <c r="Q288" s="4" t="n"/>
+      <c r="R288" s="4" t="n"/>
+      <c r="S288" s="4" t="n"/>
+      <c r="T288" s="4" t="n"/>
+      <c r="U288" s="4" t="n"/>
+      <c r="V288" s="4" t="n"/>
+      <c r="W288" s="4" t="n"/>
+      <c r="X288" s="4" t="n"/>
+      <c r="Y288" s="4" t="n"/>
+      <c r="Z288" s="4" t="n"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="A289" s="4" t="n"/>
+      <c r="B289" s="4" t="n"/>
+      <c r="C289" s="4" t="n"/>
+      <c r="D289" s="4" t="n"/>
+      <c r="E289" s="4" t="n"/>
+      <c r="F289" s="4" t="n"/>
+      <c r="G289" s="4" t="n"/>
+      <c r="H289" s="4" t="n"/>
+      <c r="I289" s="4" t="n"/>
+      <c r="J289" s="4" t="n"/>
+      <c r="K289" s="4" t="n"/>
+      <c r="L289" s="4" t="n"/>
+      <c r="M289" s="4" t="n"/>
+      <c r="N289" s="4" t="n"/>
+      <c r="O289" s="4" t="n"/>
+      <c r="P289" s="4" t="n"/>
+      <c r="Q289" s="4" t="n"/>
+      <c r="R289" s="4" t="n"/>
+      <c r="S289" s="4" t="n"/>
+      <c r="T289" s="4" t="n"/>
+      <c r="U289" s="4" t="n"/>
+      <c r="V289" s="4" t="n"/>
+      <c r="W289" s="4" t="n"/>
+      <c r="X289" s="4" t="n"/>
+      <c r="Y289" s="4" t="n"/>
+      <c r="Z289" s="4" t="n"/>
+    </row>
     <row r="290" ht="15.75" customHeight="1"/>
     <row r="291" ht="15.75" customHeight="1"/>
     <row r="292" ht="15.75" customHeight="1"/>
@@ -11013,66 +10984,40 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I93:K93"/>
+  <mergeCells count="34">
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="A60:A70"/>
+    <mergeCell ref="A78:A81"/>
     <mergeCell ref="A2:A8"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B58:B59"/>
     <mergeCell ref="A9:A16"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="B49:B53"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="A88:K88"/>
-    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="A71:A72"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="A17:A34"/>
     <mergeCell ref="A39:A48"/>
+    <mergeCell ref="B60:B70"/>
     <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A76:A77"/>
     <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A76:A79"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="B78:B81"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B39:B48"/>
     <mergeCell ref="B74:B75"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A82:A84"/>
     <mergeCell ref="A54:A56"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="A59:A69"/>
-    <mergeCell ref="I90:K90"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="B76:B77"/>
     <mergeCell ref="B21:B29"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="B59:B69"/>
+    <mergeCell ref="A58:A59"/>
     <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="B35:B38"/>
-    <mergeCell ref="E89:H89"/>
     <mergeCell ref="K2:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -2056,7 +2056,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z289"/>
+  <dimension ref="A1:Z287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col hidden="1" width="3" customWidth="1" style="5" min="1" max="1"/>
@@ -3778,7 +3778,10 @@
       <c r="H49" s="224" t="n"/>
       <c r="I49" s="224" t="n"/>
       <c r="J49" s="224" t="n"/>
-      <c r="K49" s="224" t="n"/>
+      <c r="K49" s="224">
+        <f>SUM(D49:J49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="227" t="n"/>
@@ -3795,7 +3798,10 @@
       <c r="H50" s="226" t="n"/>
       <c r="I50" s="226" t="n"/>
       <c r="J50" s="226" t="n"/>
-      <c r="K50" s="226" t="n"/>
+      <c r="K50" s="226">
+        <f>SUM(D50:J50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="227" t="n"/>
@@ -3812,7 +3818,10 @@
       <c r="H51" s="224" t="n"/>
       <c r="I51" s="224" t="n"/>
       <c r="J51" s="224" t="n"/>
-      <c r="K51" s="224" t="n"/>
+      <c r="K51" s="224">
+        <f>SUM(D51:J51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="227" t="n"/>
@@ -3829,7 +3838,10 @@
       <c r="H52" s="226" t="n"/>
       <c r="I52" s="226" t="n"/>
       <c r="J52" s="226" t="n"/>
-      <c r="K52" s="226" t="n"/>
+      <c r="K52" s="226">
+        <f>SUM(D52:J52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="228" t="n"/>
@@ -3846,7 +3858,10 @@
       <c r="H53" s="224" t="n"/>
       <c r="I53" s="224" t="n"/>
       <c r="J53" s="224" t="n"/>
-      <c r="K53" s="224" t="n"/>
+      <c r="K53" s="224">
+        <f>SUM(D53:J53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="141" t="n"/>
@@ -3868,7 +3883,7 @@
       <c r="I54" s="135" t="n"/>
       <c r="J54" s="135" t="n"/>
       <c r="K54" s="135">
-        <f>SUM(D49:J49)</f>
+        <f>SUM(D54:J54)</f>
         <v/>
       </c>
       <c r="L54" s="4" t="n"/>
@@ -3902,9 +3917,25 @@
       <c r="H55" s="135" t="n"/>
       <c r="I55" s="135" t="n"/>
       <c r="J55" s="135" t="n"/>
-      <c r="K55" s="135" t="n"/>
+      <c r="K55" s="135">
+        <f>SUM(D55:J55)</f>
+        <v/>
+      </c>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+      <c r="R55" s="4" t="n"/>
+      <c r="S55" s="4" t="n"/>
+      <c r="T55" s="4" t="n"/>
+      <c r="U55" s="4" t="n"/>
+      <c r="V55" s="4" t="n"/>
+      <c r="W55" s="4" t="n"/>
+      <c r="X55" s="4" t="n"/>
+      <c r="Y55" s="4" t="n"/>
+      <c r="Z55" s="4" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="181" t="n"/>
@@ -3922,7 +3953,7 @@
       <c r="I56" s="138" t="n"/>
       <c r="J56" s="138" t="n"/>
       <c r="K56" s="138">
-        <f>SUM(D50:J50)</f>
+        <f>SUM(D56:J56)</f>
         <v/>
       </c>
       <c r="L56" s="4" t="n"/>
@@ -3957,7 +3988,7 @@
       <c r="I57" s="135" t="n"/>
       <c r="J57" s="135" t="n"/>
       <c r="K57" s="135">
-        <f>SUM(D51:J51)</f>
+        <f>SUM(D57:J57)</f>
         <v/>
       </c>
       <c r="L57" s="4" t="n"/>
@@ -3996,7 +4027,7 @@
       <c r="I58" s="112" t="n"/>
       <c r="J58" s="112" t="n"/>
       <c r="K58" s="112">
-        <f>SUM(D52:J52)</f>
+        <f>SUM(D58:J58)</f>
         <v/>
       </c>
       <c r="L58" s="4" t="n"/>
@@ -4031,7 +4062,7 @@
       <c r="I59" s="115" t="n"/>
       <c r="J59" s="115" t="n"/>
       <c r="K59" s="115">
-        <f>SUM(D53:J53)</f>
+        <f>SUM(D59:J59)</f>
         <v/>
       </c>
       <c r="L59" s="4" t="n"/>
@@ -4070,7 +4101,7 @@
       <c r="I60" s="112" t="n"/>
       <c r="J60" s="112" t="n"/>
       <c r="K60" s="112">
-        <f>SUM(D54:J54)</f>
+        <f>SUM(D60:J60)</f>
         <v/>
       </c>
       <c r="L60" s="4" t="n"/>
@@ -4105,7 +4136,7 @@
       <c r="I61" s="115" t="n"/>
       <c r="J61" s="115" t="n"/>
       <c r="K61" s="115">
-        <f>SUM(D55:J55)</f>
+        <f>SUM(D61:J61)</f>
         <v/>
       </c>
       <c r="L61" s="4" t="n"/>
@@ -4140,7 +4171,7 @@
       <c r="I62" s="112" t="n"/>
       <c r="J62" s="112" t="n"/>
       <c r="K62" s="112">
-        <f>SUM(D56:J56)</f>
+        <f>SUM(D62:J62)</f>
         <v/>
       </c>
       <c r="L62" s="4" t="n"/>
@@ -4175,7 +4206,7 @@
       <c r="I63" s="115" t="n"/>
       <c r="J63" s="115" t="n"/>
       <c r="K63" s="115">
-        <f>SUM(D57:J57)</f>
+        <f>SUM(D63:J63)</f>
         <v/>
       </c>
       <c r="L63" s="4" t="n"/>
@@ -4210,7 +4241,7 @@
       <c r="I64" s="112" t="n"/>
       <c r="J64" s="112" t="n"/>
       <c r="K64" s="112">
-        <f>SUM(D58:J58)</f>
+        <f>SUM(D64:J64)</f>
         <v/>
       </c>
       <c r="L64" s="4" t="n"/>
@@ -4245,7 +4276,7 @@
       <c r="I65" s="115" t="n"/>
       <c r="J65" s="115" t="n"/>
       <c r="K65" s="115">
-        <f>SUM(D59:J59)</f>
+        <f>SUM(D65:J65)</f>
         <v/>
       </c>
       <c r="L65" s="4" t="n"/>
@@ -4280,7 +4311,7 @@
       <c r="I66" s="112" t="n"/>
       <c r="J66" s="112" t="n"/>
       <c r="K66" s="112">
-        <f>SUM(D60:J60)</f>
+        <f>SUM(D66:J66)</f>
         <v/>
       </c>
       <c r="L66" s="4" t="n"/>
@@ -4315,7 +4346,7 @@
       <c r="I67" s="115" t="n"/>
       <c r="J67" s="115" t="n"/>
       <c r="K67" s="115">
-        <f>SUM(D61:J61)</f>
+        <f>SUM(D67:J67)</f>
         <v/>
       </c>
       <c r="L67" s="4" t="n"/>
@@ -4350,7 +4381,7 @@
       <c r="I68" s="112" t="n"/>
       <c r="J68" s="112" t="n"/>
       <c r="K68" s="112">
-        <f>SUM(D62:J62)</f>
+        <f>SUM(D68:J68)</f>
         <v/>
       </c>
       <c r="L68" s="4" t="n"/>
@@ -4385,7 +4416,7 @@
       <c r="I69" s="115" t="n"/>
       <c r="J69" s="115" t="n"/>
       <c r="K69" s="115">
-        <f>SUM(D63:J63)</f>
+        <f>SUM(D69:J69)</f>
         <v/>
       </c>
       <c r="L69" s="4" t="n"/>
@@ -4420,7 +4451,7 @@
       <c r="I70" s="112" t="n"/>
       <c r="J70" s="112" t="n"/>
       <c r="K70" s="112">
-        <f>SUM(D64:J64)</f>
+        <f>SUM(D70:J70)</f>
         <v/>
       </c>
       <c r="L70" s="4" t="n"/>
@@ -4459,7 +4490,7 @@
       <c r="I71" s="185" t="n"/>
       <c r="J71" s="185" t="n"/>
       <c r="K71" s="185">
-        <f>SUM(D65:J65)</f>
+        <f>SUM(D71:J71)</f>
         <v/>
       </c>
       <c r="L71" s="4" t="n"/>
@@ -4494,7 +4525,7 @@
       <c r="I72" s="188" t="n"/>
       <c r="J72" s="188" t="n"/>
       <c r="K72" s="188">
-        <f>SUM(D66:J66)</f>
+        <f>SUM(D72:J72)</f>
         <v/>
       </c>
       <c r="L72" s="4" t="n"/>
@@ -4532,9 +4563,25 @@
       <c r="H73" s="185" t="n"/>
       <c r="I73" s="185" t="n"/>
       <c r="J73" s="185" t="n"/>
-      <c r="K73" s="185" t="n"/>
+      <c r="K73" s="185">
+        <f>SUM(D73:J73)</f>
+        <v/>
+      </c>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n"/>
+      <c r="R73" s="4" t="n"/>
+      <c r="S73" s="4" t="n"/>
+      <c r="T73" s="4" t="n"/>
+      <c r="U73" s="4" t="n"/>
+      <c r="V73" s="4" t="n"/>
+      <c r="W73" s="4" t="n"/>
+      <c r="X73" s="4" t="n"/>
+      <c r="Y73" s="4" t="n"/>
+      <c r="Z73" s="4" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="148" t="n"/>
@@ -4556,7 +4603,7 @@
       <c r="I74" s="149" t="n"/>
       <c r="J74" s="149" t="n"/>
       <c r="K74" s="149">
-        <f>SUM(D67:J67)</f>
+        <f>SUM(D74:J74)</f>
         <v/>
       </c>
       <c r="L74" s="4" t="n"/>
@@ -4591,7 +4638,7 @@
       <c r="I75" s="152" t="n"/>
       <c r="J75" s="152" t="n"/>
       <c r="K75" s="152">
-        <f>SUM(D68:J68)</f>
+        <f>SUM(D75:J75)</f>
         <v/>
       </c>
       <c r="L75" s="4" t="n"/>
@@ -4630,7 +4677,7 @@
       <c r="I76" s="154" t="n"/>
       <c r="J76" s="154" t="n"/>
       <c r="K76" s="154">
-        <f>SUM(D69:J69)</f>
+        <f>SUM(D76:J76)</f>
         <v/>
       </c>
       <c r="L76" s="4" t="n"/>
@@ -4665,7 +4712,7 @@
       <c r="I77" s="157" t="n"/>
       <c r="J77" s="157" t="n"/>
       <c r="K77" s="157">
-        <f>SUM(D70:J70)</f>
+        <f>SUM(D77:J77)</f>
         <v/>
       </c>
       <c r="L77" s="4" t="n"/>
@@ -4704,7 +4751,7 @@
       <c r="I78" s="119" t="n"/>
       <c r="J78" s="119" t="n"/>
       <c r="K78" s="119">
-        <f>SUM(D71:J71)</f>
+        <f>SUM(D78:J78)</f>
         <v/>
       </c>
       <c r="L78" s="4" t="n"/>
@@ -4739,7 +4786,7 @@
       <c r="I79" s="122" t="n"/>
       <c r="J79" s="122" t="n"/>
       <c r="K79" s="122">
-        <f>SUM(D72:J72)</f>
+        <f>SUM(D79:J79)</f>
         <v/>
       </c>
       <c r="L79" s="4" t="n"/>
@@ -4774,7 +4821,7 @@
       <c r="I80" s="119" t="n"/>
       <c r="J80" s="119" t="n"/>
       <c r="K80" s="119">
-        <f>SUM(D73:J73)</f>
+        <f>SUM(D80:J80)</f>
         <v/>
       </c>
       <c r="L80" s="4" t="n"/>
@@ -4809,7 +4856,7 @@
       <c r="I81" s="122" t="n"/>
       <c r="J81" s="122" t="n"/>
       <c r="K81" s="122">
-        <f>SUM(D74:J74)</f>
+        <f>SUM(D81:J81)</f>
         <v/>
       </c>
       <c r="L81" s="4" t="n"/>
@@ -4846,7 +4893,7 @@
       <c r="I82" s="160" t="n"/>
       <c r="J82" s="160" t="n"/>
       <c r="K82" s="160">
-        <f>SUM(D75:J75)</f>
+        <f>SUM(D82:J82)</f>
         <v/>
       </c>
       <c r="L82" s="4" t="n"/>
@@ -4865,7 +4912,7 @@
       <c r="Y82" s="4" t="n"/>
       <c r="Z82" s="4" t="n"/>
     </row>
-    <row r="83" ht="5" customHeight="1">
+    <row r="83" ht="15" customHeight="1">
       <c r="A83" s="181" t="n"/>
       <c r="B83" s="162" t="inlineStr">
         <is>
@@ -4883,7 +4930,7 @@
       <c r="I83" s="163" t="n"/>
       <c r="J83" s="163" t="n"/>
       <c r="K83" s="163">
-        <f>SUM(D76:J76)</f>
+        <f>SUM(D83:J83)</f>
         <v/>
       </c>
       <c r="L83" s="4" t="n"/>
@@ -4902,7 +4949,7 @@
       <c r="Y83" s="4" t="n"/>
       <c r="Z83" s="4" t="n"/>
     </row>
-    <row r="84" ht="28" customHeight="1">
+    <row r="84" ht="15" customHeight="1">
       <c r="A84" s="182" t="n"/>
       <c r="B84" s="159" t="inlineStr">
         <is>
@@ -4911,40 +4958,39 @@
       </c>
       <c r="C84" s="159" t="n"/>
       <c r="D84" s="160">
-        <f>D75+D76</f>
+        <f>D82+D83</f>
         <v/>
       </c>
       <c r="E84" s="160">
-        <f>E75+E76</f>
+        <f>E82+E83</f>
         <v/>
       </c>
       <c r="F84" s="160">
-        <f>F75+F76</f>
+        <f>F82+F83</f>
         <v/>
       </c>
       <c r="G84" s="160">
-        <f>G75+G76</f>
+        <f>G82+G83</f>
         <v/>
       </c>
       <c r="H84" s="160">
-        <f>H75+H76</f>
+        <f>H82+H83</f>
         <v/>
       </c>
       <c r="I84" s="160">
-        <f>I75+I76</f>
+        <f>I82+I83</f>
         <v/>
       </c>
       <c r="J84" s="160">
-        <f>J75+J76</f>
+        <f>J82+J83</f>
         <v/>
       </c>
       <c r="K84" s="160">
-        <f>SUM(D77:J77)</f>
+        <f>SUM(D84:J84)</f>
         <v/>
       </c>
       <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
-      <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
@@ -4958,7 +5004,7 @@
       <c r="Y84" s="4" t="n"/>
       <c r="Z84" s="4" t="n"/>
     </row>
-    <row r="85" ht="20" customHeight="1">
+    <row r="85" ht="5" customHeight="1">
       <c r="A85" s="48" t="n"/>
       <c r="B85" s="49" t="n"/>
       <c r="C85" s="49" t="n"/>
@@ -4972,7 +5018,6 @@
       <c r="K85" s="165" t="n"/>
       <c r="L85" s="4" t="n"/>
       <c r="M85" s="4" t="n"/>
-      <c r="N85" s="4" t="n"/>
       <c r="O85" s="4" t="n"/>
       <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
@@ -4986,12 +5031,22 @@
       <c r="Y85" s="4" t="n"/>
       <c r="Z85" s="4" t="n"/>
     </row>
-    <row r="86" ht="26" customHeight="1">
+    <row r="86" ht="28" customHeight="1">
       <c r="A86" s="208" t="inlineStr">
         <is>
           <t>🔄  갱신형 / 비갱신형 구분</t>
         </is>
       </c>
+      <c r="B86" s="215" t="n"/>
+      <c r="C86" s="215" t="n"/>
+      <c r="D86" s="215" t="n"/>
+      <c r="E86" s="215" t="n"/>
+      <c r="F86" s="215" t="n"/>
+      <c r="G86" s="215" t="n"/>
+      <c r="H86" s="215" t="n"/>
+      <c r="I86" s="215" t="n"/>
+      <c r="J86" s="215" t="n"/>
+      <c r="K86" s="214" t="n"/>
       <c r="O86" s="4" t="n"/>
       <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
@@ -5005,12 +5060,14 @@
       <c r="Y86" s="4" t="n"/>
       <c r="Z86" s="4" t="n"/>
     </row>
-    <row r="87" ht="7.5" customHeight="1">
+    <row r="87" ht="20" customHeight="1">
       <c r="A87" s="209" t="inlineStr">
         <is>
           <t>갱신 구분</t>
         </is>
       </c>
+      <c r="B87" s="215" t="n"/>
+      <c r="C87" s="214" t="n"/>
       <c r="D87" s="210" t="n"/>
       <c r="E87" s="210" t="n"/>
       <c r="F87" s="210" t="n"/>
@@ -5032,13 +5089,15 @@
       <c r="Y87" s="4" t="n"/>
       <c r="Z87" s="4" t="n"/>
     </row>
-    <row r="88" ht="28" customHeight="1">
+    <row r="88" ht="26" customHeight="1">
       <c r="A88" s="209" t="inlineStr">
         <is>
           <t>보험료
 변화 예고</t>
         </is>
       </c>
+      <c r="B88" s="215" t="n"/>
+      <c r="C88" s="214" t="n"/>
       <c r="D88" s="210" t="n"/>
       <c r="E88" s="210" t="n"/>
       <c r="F88" s="210" t="n"/>
@@ -5060,7 +5119,7 @@
       <c r="Y88" s="4" t="n"/>
       <c r="Z88" s="4" t="n"/>
     </row>
-    <row r="89" ht="20" customHeight="1">
+    <row r="89" ht="7.5" customHeight="1">
       <c r="O89" s="4" t="n"/>
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
@@ -5074,12 +5133,22 @@
       <c r="Y89" s="4" t="n"/>
       <c r="Z89" s="4" t="n"/>
     </row>
-    <row r="90" ht="70" customHeight="1">
+    <row r="90" ht="28" customHeight="1">
       <c r="A90" s="212" t="inlineStr">
         <is>
           <t>📋  현재 유지중인 보험 리뷰</t>
         </is>
       </c>
+      <c r="B90" s="215" t="n"/>
+      <c r="C90" s="215" t="n"/>
+      <c r="D90" s="215" t="n"/>
+      <c r="E90" s="215" t="n"/>
+      <c r="F90" s="215" t="n"/>
+      <c r="G90" s="215" t="n"/>
+      <c r="H90" s="215" t="n"/>
+      <c r="I90" s="215" t="n"/>
+      <c r="J90" s="215" t="n"/>
+      <c r="K90" s="214" t="n"/>
       <c r="O90" s="4" t="n"/>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
@@ -5093,12 +5162,13 @@
       <c r="Y90" s="4" t="n"/>
       <c r="Z90" s="4" t="n"/>
     </row>
-    <row r="91" ht="70" customHeight="1">
+    <row r="91" ht="20" customHeight="1">
       <c r="A91" s="209" t="inlineStr">
         <is>
           <t>보험사 / 상품명</t>
         </is>
       </c>
+      <c r="B91" s="214" t="n"/>
       <c r="C91" s="209" t="inlineStr">
         <is>
           <t>가입일 / 만기</t>
@@ -5114,11 +5184,16 @@
           <t>주요 체크사항</t>
         </is>
       </c>
+      <c r="F91" s="215" t="n"/>
+      <c r="G91" s="215" t="n"/>
+      <c r="H91" s="214" t="n"/>
       <c r="I91" s="209" t="inlineStr">
         <is>
           <t>특이사항 (면책기간, 보장범위 등)</t>
         </is>
       </c>
+      <c r="J91" s="215" t="n"/>
+      <c r="K91" s="214" t="n"/>
       <c r="O91" s="4" t="n"/>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
@@ -5134,10 +5209,16 @@
     </row>
     <row r="92" ht="70" customHeight="1">
       <c r="A92" s="213" t="n"/>
+      <c r="B92" s="214" t="n"/>
       <c r="C92" s="213" t="n"/>
       <c r="D92" s="213" t="n"/>
       <c r="E92" s="213" t="n"/>
+      <c r="F92" s="215" t="n"/>
+      <c r="G92" s="215" t="n"/>
+      <c r="H92" s="214" t="n"/>
       <c r="I92" s="213" t="n"/>
+      <c r="J92" s="215" t="n"/>
+      <c r="K92" s="214" t="n"/>
       <c r="O92" s="4" t="n"/>
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
@@ -5153,10 +5234,16 @@
     </row>
     <row r="93" ht="70" customHeight="1">
       <c r="A93" s="216" t="n"/>
+      <c r="B93" s="214" t="n"/>
       <c r="C93" s="216" t="n"/>
       <c r="D93" s="216" t="n"/>
       <c r="E93" s="216" t="n"/>
+      <c r="F93" s="215" t="n"/>
+      <c r="G93" s="215" t="n"/>
+      <c r="H93" s="214" t="n"/>
       <c r="I93" s="216" t="n"/>
+      <c r="J93" s="215" t="n"/>
+      <c r="K93" s="214" t="n"/>
       <c r="O93" s="4" t="n"/>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
@@ -5172,10 +5259,16 @@
     </row>
     <row r="94" ht="70" customHeight="1">
       <c r="A94" s="217" t="n"/>
+      <c r="B94" s="214" t="n"/>
       <c r="C94" s="217" t="n"/>
       <c r="D94" s="217" t="n"/>
       <c r="E94" s="217" t="n"/>
+      <c r="F94" s="215" t="n"/>
+      <c r="G94" s="215" t="n"/>
+      <c r="H94" s="214" t="n"/>
       <c r="I94" s="217" t="n"/>
+      <c r="J94" s="215" t="n"/>
+      <c r="K94" s="214" t="n"/>
       <c r="O94" s="4" t="n"/>
       <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
@@ -5191,10 +5284,16 @@
     </row>
     <row r="95" ht="70" customHeight="1">
       <c r="A95" s="218" t="n"/>
+      <c r="B95" s="214" t="n"/>
       <c r="C95" s="218" t="n"/>
       <c r="D95" s="218" t="n"/>
       <c r="E95" s="218" t="n"/>
+      <c r="F95" s="215" t="n"/>
+      <c r="G95" s="215" t="n"/>
+      <c r="H95" s="214" t="n"/>
       <c r="I95" s="218" t="n"/>
+      <c r="J95" s="215" t="n"/>
+      <c r="K95" s="214" t="n"/>
       <c r="O95" s="4" t="n"/>
       <c r="P95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
@@ -5210,10 +5309,16 @@
     </row>
     <row r="96" ht="70" customHeight="1">
       <c r="A96" s="219" t="n"/>
+      <c r="B96" s="214" t="n"/>
       <c r="C96" s="219" t="n"/>
       <c r="D96" s="219" t="n"/>
       <c r="E96" s="219" t="n"/>
+      <c r="F96" s="215" t="n"/>
+      <c r="G96" s="215" t="n"/>
+      <c r="H96" s="214" t="n"/>
       <c r="I96" s="219" t="n"/>
+      <c r="J96" s="215" t="n"/>
+      <c r="K96" s="214" t="n"/>
       <c r="O96" s="4" t="n"/>
       <c r="P96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
@@ -5227,12 +5332,18 @@
       <c r="Y96" s="4" t="n"/>
       <c r="Z96" s="4" t="n"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="70" customHeight="1">
       <c r="A97" s="220" t="n"/>
+      <c r="B97" s="214" t="n"/>
       <c r="C97" s="220" t="n"/>
       <c r="D97" s="220" t="n"/>
       <c r="E97" s="220" t="n"/>
+      <c r="F97" s="215" t="n"/>
+      <c r="G97" s="215" t="n"/>
+      <c r="H97" s="214" t="n"/>
       <c r="I97" s="220" t="n"/>
+      <c r="J97" s="215" t="n"/>
+      <c r="K97" s="214" t="n"/>
       <c r="O97" s="4" t="n"/>
       <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
@@ -5246,12 +5357,18 @@
       <c r="Y97" s="4" t="n"/>
       <c r="Z97" s="4" t="n"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="70" customHeight="1">
       <c r="A98" s="221" t="n"/>
+      <c r="B98" s="214" t="n"/>
       <c r="C98" s="221" t="n"/>
       <c r="D98" s="221" t="n"/>
       <c r="E98" s="221" t="n"/>
+      <c r="F98" s="215" t="n"/>
+      <c r="G98" s="215" t="n"/>
+      <c r="H98" s="214" t="n"/>
       <c r="I98" s="221" t="n"/>
+      <c r="J98" s="215" t="n"/>
+      <c r="K98" s="214" t="n"/>
       <c r="O98" s="4" t="n"/>
       <c r="P98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
@@ -5574,6 +5691,20 @@
       <c r="Z120" s="4" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="4" t="n"/>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="n"/>
       <c r="P121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
@@ -5588,6 +5719,20 @@
       <c r="Z121" s="4" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="4" t="n"/>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="n"/>
       <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
@@ -10221,62 +10366,8 @@
       <c r="Y287" s="4" t="n"/>
       <c r="Z287" s="4" t="n"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="4" t="n"/>
-      <c r="B288" s="4" t="n"/>
-      <c r="C288" s="4" t="n"/>
-      <c r="D288" s="4" t="n"/>
-      <c r="E288" s="4" t="n"/>
-      <c r="F288" s="4" t="n"/>
-      <c r="G288" s="4" t="n"/>
-      <c r="H288" s="4" t="n"/>
-      <c r="I288" s="4" t="n"/>
-      <c r="J288" s="4" t="n"/>
-      <c r="K288" s="4" t="n"/>
-      <c r="L288" s="4" t="n"/>
-      <c r="M288" s="4" t="n"/>
-      <c r="N288" s="4" t="n"/>
-      <c r="O288" s="4" t="n"/>
-      <c r="P288" s="4" t="n"/>
-      <c r="Q288" s="4" t="n"/>
-      <c r="R288" s="4" t="n"/>
-      <c r="S288" s="4" t="n"/>
-      <c r="T288" s="4" t="n"/>
-      <c r="U288" s="4" t="n"/>
-      <c r="V288" s="4" t="n"/>
-      <c r="W288" s="4" t="n"/>
-      <c r="X288" s="4" t="n"/>
-      <c r="Y288" s="4" t="n"/>
-      <c r="Z288" s="4" t="n"/>
-    </row>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="4" t="n"/>
-      <c r="B289" s="4" t="n"/>
-      <c r="C289" s="4" t="n"/>
-      <c r="D289" s="4" t="n"/>
-      <c r="E289" s="4" t="n"/>
-      <c r="F289" s="4" t="n"/>
-      <c r="G289" s="4" t="n"/>
-      <c r="H289" s="4" t="n"/>
-      <c r="I289" s="4" t="n"/>
-      <c r="J289" s="4" t="n"/>
-      <c r="K289" s="4" t="n"/>
-      <c r="L289" s="4" t="n"/>
-      <c r="M289" s="4" t="n"/>
-      <c r="N289" s="4" t="n"/>
-      <c r="O289" s="4" t="n"/>
-      <c r="P289" s="4" t="n"/>
-      <c r="Q289" s="4" t="n"/>
-      <c r="R289" s="4" t="n"/>
-      <c r="S289" s="4" t="n"/>
-      <c r="T289" s="4" t="n"/>
-      <c r="U289" s="4" t="n"/>
-      <c r="V289" s="4" t="n"/>
-      <c r="W289" s="4" t="n"/>
-      <c r="X289" s="4" t="n"/>
-      <c r="Y289" s="4" t="n"/>
-      <c r="Z289" s="4" t="n"/>
-    </row>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
     <row r="290" ht="15.75" customHeight="1"/>
     <row r="291" ht="15.75" customHeight="1"/>
     <row r="292" ht="15.75" customHeight="1"/>
@@ -10984,38 +11075,64 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="60">
+    <mergeCell ref="A92:B92"/>
     <mergeCell ref="B71:B72"/>
     <mergeCell ref="A60:A70"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="E91:H91"/>
     <mergeCell ref="A78:A81"/>
+    <mergeCell ref="I93:K93"/>
     <mergeCell ref="A2:A8"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="B58:B59"/>
     <mergeCell ref="A9:A16"/>
+    <mergeCell ref="I92:K92"/>
     <mergeCell ref="B49:B53"/>
-    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E93:H93"/>
     <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="B30:B34"/>
-    <mergeCell ref="B17:B20"/>
     <mergeCell ref="A17:A34"/>
     <mergeCell ref="A39:A48"/>
     <mergeCell ref="B60:B70"/>
     <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="A90:K90"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="A49:A53"/>
+    <mergeCell ref="E98:H98"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="E92:H92"/>
     <mergeCell ref="B78:B81"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B39:B48"/>
     <mergeCell ref="B74:B75"/>
+    <mergeCell ref="A86:K86"/>
     <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="E94:H94"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B76:B77"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="A88:C88"/>
     <mergeCell ref="B21:B29"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="A35:A38"/>
+    <mergeCell ref="E95:H95"/>
     <mergeCell ref="B54:B57"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="K2:K6"/>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -1365,7 +1365,7 @@
       <c r="Y1" s="2" t="n"/>
       <c r="Z1" s="2" t="n"/>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="77" t="n"/>
       <c r="B2" s="97" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="78" t="n"/>
       <c r="B3" s="74" t="n"/>
       <c r="C3" s="5" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="78" t="n"/>
       <c r="B4" s="74" t="n"/>
       <c r="C4" s="97" t="inlineStr">
@@ -1533,7 +1533,7 @@
       <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="78" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="73" t="n"/>
       <c r="B9" s="73" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="74" t="n"/>
       <c r="B10" s="74" t="n"/>
       <c r="C10" s="9" t="inlineStr">
@@ -1670,7 +1670,7 @@
       <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="74" t="n"/>
       <c r="B11" s="74" t="n"/>
       <c r="C11" s="73" t="inlineStr">
@@ -1705,7 +1705,7 @@
       <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="74" t="n"/>
       <c r="B12" s="70" t="n"/>
       <c r="C12" s="9" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="74" t="n"/>
       <c r="B13" s="73" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       <c r="Y13" s="2" t="n"/>
       <c r="Z13" s="2" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="74" t="n"/>
       <c r="B14" s="74" t="n"/>
       <c r="C14" s="9" t="inlineStr">
@@ -1814,7 +1814,7 @@
       <c r="Y14" s="2" t="n"/>
       <c r="Z14" s="2" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="74" t="n"/>
       <c r="B15" s="74" t="n"/>
       <c r="C15" s="73" t="inlineStr">
@@ -1849,7 +1849,7 @@
       <c r="Y15" s="2" t="n"/>
       <c r="Z15" s="2" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="70" t="n"/>
       <c r="B16" s="70" t="n"/>
       <c r="C16" s="9" t="inlineStr">
@@ -1884,7 +1884,7 @@
       <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="76" t="n"/>
       <c r="B17" s="90" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="74" t="n"/>
       <c r="B18" s="74" t="n"/>
       <c r="C18" s="13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="Y18" s="2" t="n"/>
       <c r="Z18" s="2" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="74" t="n"/>
       <c r="B19" s="74" t="n"/>
       <c r="C19" s="76" t="inlineStr">
@@ -1993,7 +1993,7 @@
       <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="74" t="n"/>
       <c r="B20" s="70" t="n"/>
       <c r="C20" s="13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="74" t="n"/>
       <c r="B21" s="76" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="74" t="n"/>
       <c r="B22" s="74" t="n"/>
       <c r="C22" s="13" t="inlineStr">
@@ -2103,7 +2103,7 @@
       <c r="Y22" s="2" t="n"/>
       <c r="Z22" s="2" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="74" t="n"/>
       <c r="B23" s="74" t="n"/>
       <c r="C23" s="76" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="Y23" s="2" t="n"/>
       <c r="Z23" s="2" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="74" t="n"/>
       <c r="B24" s="74" t="n"/>
       <c r="C24" s="13" t="inlineStr">
@@ -2173,7 +2173,7 @@
       <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="74" t="n"/>
       <c r="B25" s="74" t="n"/>
       <c r="C25" s="76" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="Y25" s="2" t="n"/>
       <c r="Z25" s="2" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="74" t="n"/>
       <c r="B26" s="74" t="n"/>
       <c r="C26" s="13" t="inlineStr">
@@ -2243,7 +2243,7 @@
       <c r="Y26" s="2" t="n"/>
       <c r="Z26" s="2" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="74" t="n"/>
       <c r="B27" s="74" t="n"/>
       <c r="C27" s="76" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="Y27" s="2" t="n"/>
       <c r="Z27" s="2" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="74" t="n"/>
       <c r="B28" s="74" t="n"/>
       <c r="C28" s="13" t="inlineStr">
@@ -2313,7 +2313,7 @@
       <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="74" t="n"/>
       <c r="B29" s="70" t="n"/>
       <c r="C29" s="76" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="Y29" s="2" t="n"/>
       <c r="Z29" s="2" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="74" t="n"/>
       <c r="B30" s="76" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
       <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="74" t="n"/>
       <c r="B31" s="74" t="n"/>
       <c r="C31" s="76" t="inlineStr">
@@ -2423,7 +2423,7 @@
       <c r="Y31" s="2" t="n"/>
       <c r="Z31" s="2" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="A32" s="74" t="n"/>
       <c r="B32" s="74" t="n"/>
       <c r="C32" s="13" t="inlineStr">
@@ -2458,7 +2458,7 @@
       <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="74" t="n"/>
       <c r="B33" s="74" t="n"/>
       <c r="C33" s="76" t="inlineStr">
@@ -2493,7 +2493,7 @@
       <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="70" t="n"/>
       <c r="B34" s="70" t="n"/>
       <c r="C34" s="13" t="inlineStr">
@@ -2528,7 +2528,7 @@
       <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="100" t="n"/>
       <c r="B35" s="99" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="74" t="n"/>
       <c r="B36" s="74" t="n"/>
       <c r="C36" s="17" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="Y36" s="2" t="n"/>
       <c r="Z36" s="2" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="74" t="n"/>
       <c r="B37" s="74" t="n"/>
       <c r="C37" s="15" t="inlineStr">
@@ -2637,7 +2637,7 @@
       <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38" ht="18" customHeight="1">
       <c r="A38" s="74" t="n"/>
       <c r="B38" s="70" t="n"/>
       <c r="C38" s="17" t="inlineStr">
@@ -2672,7 +2672,7 @@
       <c r="Y38" s="2" t="n"/>
       <c r="Z38" s="2" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="89" t="n"/>
       <c r="B39" s="95" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       <c r="Y39" s="2" t="n"/>
       <c r="Z39" s="2" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="74" t="n"/>
       <c r="B40" s="74" t="n"/>
       <c r="C40" s="21" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="Y40" s="2" t="n"/>
       <c r="Z40" s="2" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="A41" s="74" t="n"/>
       <c r="B41" s="74" t="n"/>
       <c r="C41" s="89" t="inlineStr">
@@ -2783,7 +2783,7 @@
       <c r="Y41" s="2" t="n"/>
       <c r="Z41" s="2" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="A42" s="74" t="n"/>
       <c r="B42" s="74" t="n"/>
       <c r="C42" s="21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="74" t="n"/>
       <c r="B43" s="74" t="n"/>
       <c r="C43" s="89" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="74" t="n"/>
       <c r="B44" s="74" t="n"/>
       <c r="C44" s="21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45" ht="18" customHeight="1">
       <c r="A45" s="74" t="n"/>
       <c r="B45" s="74" t="n"/>
       <c r="C45" s="89" t="inlineStr">
@@ -2923,7 +2923,7 @@
       <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="74" t="n"/>
       <c r="B46" s="74" t="n"/>
       <c r="C46" s="21" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="74" t="n"/>
       <c r="B47" s="74" t="n"/>
       <c r="C47" s="89" t="inlineStr">
@@ -2993,7 +2993,7 @@
       <c r="Y47" s="2" t="n"/>
       <c r="Z47" s="2" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1">
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="70" t="n"/>
       <c r="B48" s="70" t="n"/>
       <c r="C48" s="21" t="inlineStr">
@@ -3028,7 +3028,7 @@
       <c r="Y48" s="2" t="n"/>
       <c r="Z48" s="2" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="84" t="n"/>
       <c r="B49" s="84" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="85" t="n"/>
       <c r="B50" s="85" t="n"/>
       <c r="C50" s="44" t="inlineStr">
@@ -3076,7 +3076,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="85" t="n"/>
       <c r="B51" s="85" t="n"/>
       <c r="C51" s="84" t="inlineStr">
@@ -3097,7 +3097,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="85" t="n"/>
       <c r="B52" s="85" t="n"/>
       <c r="C52" s="44" t="inlineStr">
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="A53" s="86" t="n"/>
       <c r="B53" s="86" t="n"/>
       <c r="C53" s="84" t="inlineStr">
@@ -3139,7 +3139,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
+    <row r="54" ht="18" customHeight="1">
       <c r="A54" s="81" t="n"/>
       <c r="B54" s="93" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1">
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="74" t="n"/>
       <c r="B55" s="74" t="n"/>
       <c r="C55" s="89" t="inlineStr">
@@ -3213,7 +3213,7 @@
       <c r="Y55" s="2" t="n"/>
       <c r="Z55" s="2" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1">
+    <row r="56" ht="18" customHeight="1">
       <c r="A56" s="74" t="n"/>
       <c r="B56" s="74" t="n"/>
       <c r="C56" s="21" t="inlineStr">
@@ -3248,7 +3248,7 @@
       <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="n"/>
     </row>
-    <row r="57" ht="15" customHeight="1">
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="74" t="n"/>
       <c r="B57" s="74" t="n"/>
       <c r="C57" s="89" t="inlineStr">
@@ -3283,7 +3283,7 @@
       <c r="Y57" s="2" t="n"/>
       <c r="Z57" s="2" t="n"/>
     </row>
-    <row r="58" ht="15" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="73" t="n"/>
       <c r="B58" s="80" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       <c r="Y58" s="2" t="n"/>
       <c r="Z58" s="2" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1">
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="70" t="n"/>
       <c r="B59" s="70" t="n"/>
       <c r="C59" s="9" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="Y59" s="2" t="n"/>
       <c r="Z59" s="2" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1">
+    <row r="60" ht="18" customHeight="1">
       <c r="A60" s="73" t="n"/>
       <c r="B60" s="73" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       <c r="Y60" s="2" t="n"/>
       <c r="Z60" s="2" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1">
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="74" t="n"/>
       <c r="B61" s="74" t="n"/>
       <c r="C61" s="9" t="inlineStr">
@@ -3431,7 +3431,7 @@
       <c r="Y61" s="2" t="n"/>
       <c r="Z61" s="2" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="74" t="n"/>
       <c r="B62" s="74" t="n"/>
       <c r="C62" s="73" t="inlineStr">
@@ -3466,7 +3466,7 @@
       <c r="Y62" s="2" t="n"/>
       <c r="Z62" s="2" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="A63" s="74" t="n"/>
       <c r="B63" s="74" t="n"/>
       <c r="C63" s="9" t="inlineStr">
@@ -3501,7 +3501,7 @@
       <c r="Y63" s="2" t="n"/>
       <c r="Z63" s="2" t="n"/>
     </row>
-    <row r="64" ht="15" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="74" t="n"/>
       <c r="B64" s="74" t="n"/>
       <c r="C64" s="73" t="inlineStr">
@@ -3536,7 +3536,7 @@
       <c r="Y64" s="2" t="n"/>
       <c r="Z64" s="2" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1">
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="74" t="n"/>
       <c r="B65" s="74" t="n"/>
       <c r="C65" s="9" t="inlineStr">
@@ -3571,7 +3571,7 @@
       <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="74" t="n"/>
       <c r="B66" s="74" t="n"/>
       <c r="C66" s="73" t="inlineStr">
@@ -3606,7 +3606,7 @@
       <c r="Y66" s="2" t="n"/>
       <c r="Z66" s="2" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1">
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="74" t="n"/>
       <c r="B67" s="74" t="n"/>
       <c r="C67" s="9" t="inlineStr">
@@ -3641,7 +3641,7 @@
       <c r="Y67" s="2" t="n"/>
       <c r="Z67" s="2" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1">
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="74" t="n"/>
       <c r="B68" s="74" t="n"/>
       <c r="C68" s="73" t="inlineStr">
@@ -3676,7 +3676,7 @@
       <c r="Y68" s="2" t="n"/>
       <c r="Z68" s="2" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="74" t="n"/>
       <c r="B69" s="74" t="n"/>
       <c r="C69" s="9" t="inlineStr">
@@ -3711,7 +3711,7 @@
       <c r="Y69" s="2" t="n"/>
       <c r="Z69" s="2" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1">
+    <row r="70" ht="18" customHeight="1">
       <c r="A70" s="70" t="n"/>
       <c r="B70" s="70" t="n"/>
       <c r="C70" s="73" t="inlineStr">
@@ -3746,7 +3746,7 @@
       <c r="Y70" s="2" t="n"/>
       <c r="Z70" s="2" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1">
+    <row r="71" ht="18" customHeight="1">
       <c r="A71" s="87" t="n"/>
       <c r="B71" s="69" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1">
+    <row r="72" ht="18" customHeight="1">
       <c r="A72" s="70" t="n"/>
       <c r="B72" s="70" t="n"/>
       <c r="C72" s="37" t="inlineStr">
@@ -3820,7 +3820,7 @@
       <c r="Y72" s="2" t="n"/>
       <c r="Z72" s="2" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1">
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="87" t="n"/>
       <c r="B73" s="87" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="91" t="n"/>
       <c r="B74" s="91" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       <c r="Y74" s="2" t="n"/>
       <c r="Z74" s="2" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1">
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="70" t="n"/>
       <c r="B75" s="70" t="n"/>
       <c r="C75" s="25" t="inlineStr">
@@ -3933,7 +3933,7 @@
       <c r="Y75" s="2" t="n"/>
       <c r="Z75" s="2" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1">
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="94" t="n"/>
       <c r="B76" s="94" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
       <c r="Y76" s="2" t="n"/>
       <c r="Z76" s="2" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1">
+    <row r="77" ht="18" customHeight="1">
       <c r="A77" s="70" t="n"/>
       <c r="B77" s="70" t="n"/>
       <c r="C77" s="29" t="inlineStr">
@@ -4007,7 +4007,7 @@
       <c r="Y77" s="2" t="n"/>
       <c r="Z77" s="2" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1">
+    <row r="78" ht="18" customHeight="1">
       <c r="A78" s="76" t="n"/>
       <c r="B78" s="90" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       <c r="Y78" s="2" t="n"/>
       <c r="Z78" s="2" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1">
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="74" t="n"/>
       <c r="B79" s="74" t="n"/>
       <c r="C79" s="13" t="inlineStr">
@@ -4081,7 +4081,7 @@
       <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="74" t="n"/>
       <c r="B80" s="74" t="n"/>
       <c r="C80" s="76" t="inlineStr">
@@ -4116,7 +4116,7 @@
       <c r="Y80" s="2" t="n"/>
       <c r="Z80" s="2" t="n"/>
     </row>
-    <row r="81" ht="15" customHeight="1">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="70" t="n"/>
       <c r="B81" s="70" t="n"/>
       <c r="C81" s="13" t="inlineStr">
@@ -4151,7 +4151,7 @@
       <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="96" t="n"/>
       <c r="B82" s="56" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       <c r="Y82" s="2" t="n"/>
       <c r="Z82" s="2" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1">
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="74" t="n"/>
       <c r="B83" s="33" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="Y83" s="2" t="n"/>
       <c r="Z83" s="2" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1">
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="70" t="n"/>
       <c r="B84" s="31" t="inlineStr">
         <is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -1365,7 +1365,7 @@
       <c r="Y1" s="2" t="n"/>
       <c r="Z1" s="2" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="17" customHeight="1">
       <c r="A2" s="77" t="n"/>
       <c r="B2" s="97" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="17" customHeight="1">
       <c r="A3" s="78" t="n"/>
       <c r="B3" s="74" t="n"/>
       <c r="C3" s="5" t="inlineStr">
@@ -1437,7 +1437,7 @@
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="78" t="n"/>
       <c r="B4" s="74" t="n"/>
       <c r="C4" s="97" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="17" customHeight="1">
       <c r="A5" s="78" t="n"/>
       <c r="B5" s="74" t="n"/>
       <c r="C5" s="5" t="inlineStr">
@@ -1501,7 +1501,7 @@
       <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="17" customHeight="1">
       <c r="A6" s="78" t="n"/>
       <c r="B6" s="70" t="n"/>
       <c r="C6" s="97" t="inlineStr">
@@ -1533,7 +1533,7 @@
       <c r="Y6" s="2" t="n"/>
       <c r="Z6" s="2" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="17" customHeight="1">
       <c r="A7" s="78" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
       <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="17" customHeight="1">
       <c r="A9" s="73" t="n"/>
       <c r="B9" s="73" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="17" customHeight="1">
       <c r="A10" s="74" t="n"/>
       <c r="B10" s="74" t="n"/>
       <c r="C10" s="9" t="inlineStr">
@@ -1670,7 +1670,7 @@
       <c r="Y10" s="2" t="n"/>
       <c r="Z10" s="2" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="17" customHeight="1">
       <c r="A11" s="74" t="n"/>
       <c r="B11" s="74" t="n"/>
       <c r="C11" s="73" t="inlineStr">
@@ -1705,7 +1705,7 @@
       <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="17" customHeight="1">
       <c r="A12" s="74" t="n"/>
       <c r="B12" s="70" t="n"/>
       <c r="C12" s="9" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="17" customHeight="1">
       <c r="A13" s="74" t="n"/>
       <c r="B13" s="73" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       <c r="Y13" s="2" t="n"/>
       <c r="Z13" s="2" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="17" customHeight="1">
       <c r="A14" s="74" t="n"/>
       <c r="B14" s="74" t="n"/>
       <c r="C14" s="9" t="inlineStr">
@@ -1814,7 +1814,7 @@
       <c r="Y14" s="2" t="n"/>
       <c r="Z14" s="2" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="17" customHeight="1">
       <c r="A15" s="74" t="n"/>
       <c r="B15" s="74" t="n"/>
       <c r="C15" s="73" t="inlineStr">
@@ -1849,7 +1849,7 @@
       <c r="Y15" s="2" t="n"/>
       <c r="Z15" s="2" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="17" customHeight="1">
       <c r="A16" s="70" t="n"/>
       <c r="B16" s="70" t="n"/>
       <c r="C16" s="9" t="inlineStr">
@@ -1884,7 +1884,7 @@
       <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="17" customHeight="1">
       <c r="A17" s="76" t="n"/>
       <c r="B17" s="90" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       <c r="Y17" s="2" t="n"/>
       <c r="Z17" s="2" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="17" customHeight="1">
       <c r="A18" s="74" t="n"/>
       <c r="B18" s="74" t="n"/>
       <c r="C18" s="13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="Y18" s="2" t="n"/>
       <c r="Z18" s="2" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="17" customHeight="1">
       <c r="A19" s="74" t="n"/>
       <c r="B19" s="74" t="n"/>
       <c r="C19" s="76" t="inlineStr">
@@ -1993,7 +1993,7 @@
       <c r="Y19" s="2" t="n"/>
       <c r="Z19" s="2" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="17" customHeight="1">
       <c r="A20" s="74" t="n"/>
       <c r="B20" s="70" t="n"/>
       <c r="C20" s="13" t="inlineStr">
@@ -2028,7 +2028,7 @@
       <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="17" customHeight="1">
       <c r="A21" s="74" t="n"/>
       <c r="B21" s="76" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="17" customHeight="1">
       <c r="A22" s="74" t="n"/>
       <c r="B22" s="74" t="n"/>
       <c r="C22" s="13" t="inlineStr">
@@ -2103,7 +2103,7 @@
       <c r="Y22" s="2" t="n"/>
       <c r="Z22" s="2" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="17" customHeight="1">
       <c r="A23" s="74" t="n"/>
       <c r="B23" s="74" t="n"/>
       <c r="C23" s="76" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="Y23" s="2" t="n"/>
       <c r="Z23" s="2" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="17" customHeight="1">
       <c r="A24" s="74" t="n"/>
       <c r="B24" s="74" t="n"/>
       <c r="C24" s="13" t="inlineStr">
@@ -2173,7 +2173,7 @@
       <c r="Y24" s="2" t="n"/>
       <c r="Z24" s="2" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="17" customHeight="1">
       <c r="A25" s="74" t="n"/>
       <c r="B25" s="74" t="n"/>
       <c r="C25" s="76" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="Y25" s="2" t="n"/>
       <c r="Z25" s="2" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="17" customHeight="1">
       <c r="A26" s="74" t="n"/>
       <c r="B26" s="74" t="n"/>
       <c r="C26" s="13" t="inlineStr">
@@ -2243,7 +2243,7 @@
       <c r="Y26" s="2" t="n"/>
       <c r="Z26" s="2" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="17" customHeight="1">
       <c r="A27" s="74" t="n"/>
       <c r="B27" s="74" t="n"/>
       <c r="C27" s="76" t="inlineStr">
@@ -2278,7 +2278,7 @@
       <c r="Y27" s="2" t="n"/>
       <c r="Z27" s="2" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="17" customHeight="1">
       <c r="A28" s="74" t="n"/>
       <c r="B28" s="74" t="n"/>
       <c r="C28" s="13" t="inlineStr">
@@ -2313,7 +2313,7 @@
       <c r="Y28" s="2" t="n"/>
       <c r="Z28" s="2" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="17" customHeight="1">
       <c r="A29" s="74" t="n"/>
       <c r="B29" s="70" t="n"/>
       <c r="C29" s="76" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="Y29" s="2" t="n"/>
       <c r="Z29" s="2" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="17" customHeight="1">
       <c r="A30" s="74" t="n"/>
       <c r="B30" s="76" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
       <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="17" customHeight="1">
       <c r="A31" s="74" t="n"/>
       <c r="B31" s="74" t="n"/>
       <c r="C31" s="76" t="inlineStr">
@@ -2423,7 +2423,7 @@
       <c r="Y31" s="2" t="n"/>
       <c r="Z31" s="2" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="17" customHeight="1">
       <c r="A32" s="74" t="n"/>
       <c r="B32" s="74" t="n"/>
       <c r="C32" s="13" t="inlineStr">
@@ -2458,7 +2458,7 @@
       <c r="Y32" s="2" t="n"/>
       <c r="Z32" s="2" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="17" customHeight="1">
       <c r="A33" s="74" t="n"/>
       <c r="B33" s="74" t="n"/>
       <c r="C33" s="76" t="inlineStr">
@@ -2493,7 +2493,7 @@
       <c r="Y33" s="2" t="n"/>
       <c r="Z33" s="2" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="17" customHeight="1">
       <c r="A34" s="70" t="n"/>
       <c r="B34" s="70" t="n"/>
       <c r="C34" s="13" t="inlineStr">
@@ -2528,7 +2528,7 @@
       <c r="Y34" s="2" t="n"/>
       <c r="Z34" s="2" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="17" customHeight="1">
       <c r="A35" s="100" t="n"/>
       <c r="B35" s="99" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="17" customHeight="1">
       <c r="A36" s="74" t="n"/>
       <c r="B36" s="74" t="n"/>
       <c r="C36" s="17" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="Y36" s="2" t="n"/>
       <c r="Z36" s="2" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
+    <row r="37" ht="17" customHeight="1">
       <c r="A37" s="74" t="n"/>
       <c r="B37" s="74" t="n"/>
       <c r="C37" s="15" t="inlineStr">
@@ -2637,7 +2637,7 @@
       <c r="Y37" s="2" t="n"/>
       <c r="Z37" s="2" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="17" customHeight="1">
       <c r="A38" s="74" t="n"/>
       <c r="B38" s="70" t="n"/>
       <c r="C38" s="17" t="inlineStr">
@@ -2672,7 +2672,7 @@
       <c r="Y38" s="2" t="n"/>
       <c r="Z38" s="2" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="17" customHeight="1">
       <c r="A39" s="89" t="n"/>
       <c r="B39" s="95" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       <c r="Y39" s="2" t="n"/>
       <c r="Z39" s="2" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="17" customHeight="1">
       <c r="A40" s="74" t="n"/>
       <c r="B40" s="74" t="n"/>
       <c r="C40" s="21" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="Y40" s="2" t="n"/>
       <c r="Z40" s="2" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="17" customHeight="1">
       <c r="A41" s="74" t="n"/>
       <c r="B41" s="74" t="n"/>
       <c r="C41" s="89" t="inlineStr">
@@ -2783,7 +2783,7 @@
       <c r="Y41" s="2" t="n"/>
       <c r="Z41" s="2" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="17" customHeight="1">
       <c r="A42" s="74" t="n"/>
       <c r="B42" s="74" t="n"/>
       <c r="C42" s="21" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="Y42" s="2" t="n"/>
       <c r="Z42" s="2" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="17" customHeight="1">
       <c r="A43" s="74" t="n"/>
       <c r="B43" s="74" t="n"/>
       <c r="C43" s="89" t="inlineStr">
@@ -2853,7 +2853,7 @@
       <c r="Y43" s="2" t="n"/>
       <c r="Z43" s="2" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="17" customHeight="1">
       <c r="A44" s="74" t="n"/>
       <c r="B44" s="74" t="n"/>
       <c r="C44" s="21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       <c r="Y44" s="2" t="n"/>
       <c r="Z44" s="2" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="17" customHeight="1">
       <c r="A45" s="74" t="n"/>
       <c r="B45" s="74" t="n"/>
       <c r="C45" s="89" t="inlineStr">
@@ -2923,7 +2923,7 @@
       <c r="Y45" s="2" t="n"/>
       <c r="Z45" s="2" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="17" customHeight="1">
       <c r="A46" s="74" t="n"/>
       <c r="B46" s="74" t="n"/>
       <c r="C46" s="21" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="17" customHeight="1">
       <c r="A47" s="74" t="n"/>
       <c r="B47" s="74" t="n"/>
       <c r="C47" s="89" t="inlineStr">
@@ -2993,7 +2993,7 @@
       <c r="Y47" s="2" t="n"/>
       <c r="Z47" s="2" t="n"/>
     </row>
-    <row r="48" ht="18" customHeight="1">
+    <row r="48" ht="17" customHeight="1">
       <c r="A48" s="70" t="n"/>
       <c r="B48" s="70" t="n"/>
       <c r="C48" s="21" t="inlineStr">
@@ -3028,7 +3028,7 @@
       <c r="Y48" s="2" t="n"/>
       <c r="Z48" s="2" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="17" customHeight="1">
       <c r="A49" s="84" t="n"/>
       <c r="B49" s="84" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="17" customHeight="1">
       <c r="A50" s="85" t="n"/>
       <c r="B50" s="85" t="n"/>
       <c r="C50" s="44" t="inlineStr">
@@ -3076,7 +3076,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="17" customHeight="1">
       <c r="A51" s="85" t="n"/>
       <c r="B51" s="85" t="n"/>
       <c r="C51" s="84" t="inlineStr">
@@ -3097,7 +3097,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="17" customHeight="1">
       <c r="A52" s="85" t="n"/>
       <c r="B52" s="85" t="n"/>
       <c r="C52" s="44" t="inlineStr">
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="17" customHeight="1">
       <c r="A53" s="86" t="n"/>
       <c r="B53" s="86" t="n"/>
       <c r="C53" s="84" t="inlineStr">
@@ -3139,7 +3139,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
+    <row r="54" ht="17" customHeight="1">
       <c r="A54" s="81" t="n"/>
       <c r="B54" s="93" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="17" customHeight="1">
       <c r="A55" s="74" t="n"/>
       <c r="B55" s="74" t="n"/>
       <c r="C55" s="89" t="inlineStr">
@@ -3213,7 +3213,7 @@
       <c r="Y55" s="2" t="n"/>
       <c r="Z55" s="2" t="n"/>
     </row>
-    <row r="56" ht="18" customHeight="1">
+    <row r="56" ht="17" customHeight="1">
       <c r="A56" s="74" t="n"/>
       <c r="B56" s="74" t="n"/>
       <c r="C56" s="21" t="inlineStr">
@@ -3248,7 +3248,7 @@
       <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="17" customHeight="1">
       <c r="A57" s="74" t="n"/>
       <c r="B57" s="74" t="n"/>
       <c r="C57" s="89" t="inlineStr">
@@ -3283,7 +3283,7 @@
       <c r="Y57" s="2" t="n"/>
       <c r="Z57" s="2" t="n"/>
     </row>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="17" customHeight="1">
       <c r="A58" s="73" t="n"/>
       <c r="B58" s="80" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       <c r="Y58" s="2" t="n"/>
       <c r="Z58" s="2" t="n"/>
     </row>
-    <row r="59" ht="18" customHeight="1">
+    <row r="59" ht="17" customHeight="1">
       <c r="A59" s="70" t="n"/>
       <c r="B59" s="70" t="n"/>
       <c r="C59" s="9" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="Y59" s="2" t="n"/>
       <c r="Z59" s="2" t="n"/>
     </row>
-    <row r="60" ht="18" customHeight="1">
+    <row r="60" ht="17" customHeight="1">
       <c r="A60" s="73" t="n"/>
       <c r="B60" s="73" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       <c r="Y60" s="2" t="n"/>
       <c r="Z60" s="2" t="n"/>
     </row>
-    <row r="61" ht="18" customHeight="1">
+    <row r="61" ht="17" customHeight="1">
       <c r="A61" s="74" t="n"/>
       <c r="B61" s="74" t="n"/>
       <c r="C61" s="9" t="inlineStr">
@@ -3431,7 +3431,7 @@
       <c r="Y61" s="2" t="n"/>
       <c r="Z61" s="2" t="n"/>
     </row>
-    <row r="62" ht="18" customHeight="1">
+    <row r="62" ht="17" customHeight="1">
       <c r="A62" s="74" t="n"/>
       <c r="B62" s="74" t="n"/>
       <c r="C62" s="73" t="inlineStr">
@@ -3466,7 +3466,7 @@
       <c r="Y62" s="2" t="n"/>
       <c r="Z62" s="2" t="n"/>
     </row>
-    <row r="63" ht="18" customHeight="1">
+    <row r="63" ht="17" customHeight="1">
       <c r="A63" s="74" t="n"/>
       <c r="B63" s="74" t="n"/>
       <c r="C63" s="9" t="inlineStr">
@@ -3501,7 +3501,7 @@
       <c r="Y63" s="2" t="n"/>
       <c r="Z63" s="2" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1">
+    <row r="64" ht="17" customHeight="1">
       <c r="A64" s="74" t="n"/>
       <c r="B64" s="74" t="n"/>
       <c r="C64" s="73" t="inlineStr">
@@ -3536,7 +3536,7 @@
       <c r="Y64" s="2" t="n"/>
       <c r="Z64" s="2" t="n"/>
     </row>
-    <row r="65" ht="18" customHeight="1">
+    <row r="65" ht="17" customHeight="1">
       <c r="A65" s="74" t="n"/>
       <c r="B65" s="74" t="n"/>
       <c r="C65" s="9" t="inlineStr">
@@ -3571,7 +3571,7 @@
       <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1">
+    <row r="66" ht="17" customHeight="1">
       <c r="A66" s="74" t="n"/>
       <c r="B66" s="74" t="n"/>
       <c r="C66" s="73" t="inlineStr">
@@ -3606,7 +3606,7 @@
       <c r="Y66" s="2" t="n"/>
       <c r="Z66" s="2" t="n"/>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67" ht="17" customHeight="1">
       <c r="A67" s="74" t="n"/>
       <c r="B67" s="74" t="n"/>
       <c r="C67" s="9" t="inlineStr">
@@ -3641,7 +3641,7 @@
       <c r="Y67" s="2" t="n"/>
       <c r="Z67" s="2" t="n"/>
     </row>
-    <row r="68" ht="18" customHeight="1">
+    <row r="68" ht="17" customHeight="1">
       <c r="A68" s="74" t="n"/>
       <c r="B68" s="74" t="n"/>
       <c r="C68" s="73" t="inlineStr">
@@ -3676,7 +3676,7 @@
       <c r="Y68" s="2" t="n"/>
       <c r="Z68" s="2" t="n"/>
     </row>
-    <row r="69" ht="18" customHeight="1">
+    <row r="69" ht="17" customHeight="1">
       <c r="A69" s="74" t="n"/>
       <c r="B69" s="74" t="n"/>
       <c r="C69" s="9" t="inlineStr">
@@ -3711,7 +3711,7 @@
       <c r="Y69" s="2" t="n"/>
       <c r="Z69" s="2" t="n"/>
     </row>
-    <row r="70" ht="18" customHeight="1">
+    <row r="70" ht="17" customHeight="1">
       <c r="A70" s="70" t="n"/>
       <c r="B70" s="70" t="n"/>
       <c r="C70" s="73" t="inlineStr">
@@ -3746,7 +3746,7 @@
       <c r="Y70" s="2" t="n"/>
       <c r="Z70" s="2" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1">
+    <row r="71" ht="17" customHeight="1">
       <c r="A71" s="87" t="n"/>
       <c r="B71" s="69" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
     </row>
-    <row r="72" ht="18" customHeight="1">
+    <row r="72" ht="17" customHeight="1">
       <c r="A72" s="70" t="n"/>
       <c r="B72" s="70" t="n"/>
       <c r="C72" s="37" t="inlineStr">
@@ -3820,7 +3820,7 @@
       <c r="Y72" s="2" t="n"/>
       <c r="Z72" s="2" t="n"/>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="17" customHeight="1">
       <c r="A73" s="87" t="n"/>
       <c r="B73" s="87" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
     </row>
-    <row r="74" ht="18" customHeight="1">
+    <row r="74" ht="17" customHeight="1">
       <c r="A74" s="91" t="n"/>
       <c r="B74" s="91" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       <c r="Y74" s="2" t="n"/>
       <c r="Z74" s="2" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1">
+    <row r="75" ht="17" customHeight="1">
       <c r="A75" s="70" t="n"/>
       <c r="B75" s="70" t="n"/>
       <c r="C75" s="25" t="inlineStr">
@@ -3933,7 +3933,7 @@
       <c r="Y75" s="2" t="n"/>
       <c r="Z75" s="2" t="n"/>
     </row>
-    <row r="76" ht="18" customHeight="1">
+    <row r="76" ht="17" customHeight="1">
       <c r="A76" s="94" t="n"/>
       <c r="B76" s="94" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
       <c r="Y76" s="2" t="n"/>
       <c r="Z76" s="2" t="n"/>
     </row>
-    <row r="77" ht="18" customHeight="1">
+    <row r="77" ht="17" customHeight="1">
       <c r="A77" s="70" t="n"/>
       <c r="B77" s="70" t="n"/>
       <c r="C77" s="29" t="inlineStr">
@@ -4007,7 +4007,7 @@
       <c r="Y77" s="2" t="n"/>
       <c r="Z77" s="2" t="n"/>
     </row>
-    <row r="78" ht="18" customHeight="1">
+    <row r="78" ht="17" customHeight="1">
       <c r="A78" s="76" t="n"/>
       <c r="B78" s="90" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       <c r="Y78" s="2" t="n"/>
       <c r="Z78" s="2" t="n"/>
     </row>
-    <row r="79" ht="18" customHeight="1">
+    <row r="79" ht="17" customHeight="1">
       <c r="A79" s="74" t="n"/>
       <c r="B79" s="74" t="n"/>
       <c r="C79" s="13" t="inlineStr">
@@ -4081,7 +4081,7 @@
       <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
     </row>
-    <row r="80" ht="18" customHeight="1">
+    <row r="80" ht="17" customHeight="1">
       <c r="A80" s="74" t="n"/>
       <c r="B80" s="74" t="n"/>
       <c r="C80" s="76" t="inlineStr">
@@ -4116,7 +4116,7 @@
       <c r="Y80" s="2" t="n"/>
       <c r="Z80" s="2" t="n"/>
     </row>
-    <row r="81" ht="18" customHeight="1">
+    <row r="81" ht="17" customHeight="1">
       <c r="A81" s="70" t="n"/>
       <c r="B81" s="70" t="n"/>
       <c r="C81" s="13" t="inlineStr">
@@ -4151,7 +4151,7 @@
       <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
     </row>
-    <row r="82" ht="18" customHeight="1">
+    <row r="82" ht="17" customHeight="1">
       <c r="A82" s="96" t="n"/>
       <c r="B82" s="56" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       <c r="Y82" s="2" t="n"/>
       <c r="Z82" s="2" t="n"/>
     </row>
-    <row r="83" ht="18" customHeight="1">
+    <row r="83" ht="17" customHeight="1">
       <c r="A83" s="74" t="n"/>
       <c r="B83" s="33" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="Y83" s="2" t="n"/>
       <c r="Z83" s="2" t="n"/>
     </row>
-    <row r="84" ht="18" customHeight="1">
+    <row r="84" ht="17" customHeight="1">
       <c r="A84" s="70" t="n"/>
       <c r="B84" s="31" t="inlineStr">
         <is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -19,7 +19,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;&quot;&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -126,6 +126,11 @@
       <charset val="129"/>
       <b val="1"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -541,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -908,6 +913,12 @@
     </xf>
     <xf numFmtId="165" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3029,15 +3040,15 @@
       <c r="Z48" s="2" t="n"/>
     </row>
     <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="84" t="n"/>
-      <c r="B49" s="84" t="inlineStr">
+      <c r="A49" s="131" t="n"/>
+      <c r="B49" s="131" t="inlineStr">
         <is>
           <t>특정순환계질환
 주요치료비
 (연 1회)</t>
         </is>
       </c>
-      <c r="C49" s="84" t="inlineStr">
+      <c r="C49" s="131" t="inlineStr">
         <is>
           <t>특정순환계 수술</t>
         </is>
@@ -3058,7 +3069,7 @@
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="85" t="n"/>
       <c r="B50" s="85" t="n"/>
-      <c r="C50" s="44" t="inlineStr">
+      <c r="C50" s="132" t="inlineStr">
         <is>
           <t>특정순환계 혈전용해</t>
         </is>
@@ -3079,7 +3090,7 @@
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="85" t="n"/>
       <c r="B51" s="85" t="n"/>
-      <c r="C51" s="84" t="inlineStr">
+      <c r="C51" s="131" t="inlineStr">
         <is>
           <t>특정순환계 혈전제거</t>
         </is>
@@ -3100,7 +3111,7 @@
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="85" t="n"/>
       <c r="B52" s="85" t="n"/>
-      <c r="C52" s="44" t="inlineStr">
+      <c r="C52" s="132" t="inlineStr">
         <is>
           <t>특정순환계 혈전복합</t>
         </is>
@@ -3121,7 +3132,7 @@
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="86" t="n"/>
       <c r="B53" s="86" t="n"/>
-      <c r="C53" s="84" t="inlineStr">
+      <c r="C53" s="131" t="inlineStr">
         <is>
           <t>특정순환계 중환자실</t>
         </is>

--- a/templates/master_template.xlsx
+++ b/templates/master_template.xlsx
@@ -1353,7 +1353,14 @@
     <col hidden="1" width="3" customWidth="1" style="83" min="1" max="1"/>
     <col width="15.88671875" customWidth="1" style="83" min="2" max="2"/>
     <col width="23" customWidth="1" style="83" min="3" max="3"/>
-    <col width="15.109375" customWidth="1" style="83" min="4" max="11"/>
+    <col width="15" customWidth="1" style="83" min="4" max="11"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="17.88671875" customWidth="1" style="83" min="12" max="12"/>
     <col width="17.88671875" customWidth="1" style="83" min="13" max="16384"/>
   </cols>
